--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884115</v>
+        <v>128884097</v>
       </c>
       <c r="B4" t="n">
-        <v>80185</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515019</v>
+        <v>515184</v>
       </c>
       <c r="R4" t="n">
-        <v>6981238</v>
+        <v>6981392</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,48 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884097</v>
+        <v>128890092</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515184</v>
+        <v>515067</v>
       </c>
       <c r="R5" t="n">
-        <v>6981392</v>
+        <v>6981353</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,19 +1064,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:19</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128890092</v>
+        <v>128884115</v>
       </c>
       <c r="B6" t="n">
-        <v>80261</v>
+        <v>80185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,37 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515067</v>
+        <v>515019</v>
       </c>
       <c r="R6" t="n">
-        <v>6981353</v>
+        <v>6981238</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,14 +1166,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,12 +1193,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1208,7 +1208,7 @@
         <v>128890079</v>
       </c>
       <c r="B7" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884087</v>
+        <v>128884093</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>105680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515217</v>
+        <v>515174</v>
       </c>
       <c r="R9" t="n">
-        <v>6981406</v>
+        <v>6981416</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,32 +1516,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128884093</v>
+        <v>128884087</v>
       </c>
       <c r="B10" t="n">
-        <v>105673</v>
+        <v>80225</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515174</v>
+        <v>515217</v>
       </c>
       <c r="R10" t="n">
-        <v>6981416</v>
+        <v>6981406</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,7 +1723,7 @@
         <v>128890100</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128890039</v>
+        <v>128884116</v>
       </c>
       <c r="B14" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,37 +1930,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515123</v>
+        <v>515030</v>
       </c>
       <c r="R14" t="n">
-        <v>6981380</v>
+        <v>6981199</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,9 +1987,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,22 +2014,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128884116</v>
+        <v>128890039</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,37 +2037,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515030</v>
+        <v>515123</v>
       </c>
       <c r="R15" t="n">
-        <v>6981199</v>
+        <v>6981380</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2084,19 +2094,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,22 +2111,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128884105</v>
+        <v>128890028</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>80091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515069</v>
+        <v>515039</v>
       </c>
       <c r="R16" t="n">
-        <v>6981348</v>
+        <v>6981285</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,49 +2191,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128884079</v>
+        <v>128890081</v>
       </c>
       <c r="B17" t="n">
-        <v>78097</v>
+        <v>80091</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,37 +2232,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>388</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515240</v>
+        <v>515203</v>
       </c>
       <c r="R17" t="n">
-        <v>6981445</v>
+        <v>6981449</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2298,19 +2289,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,22 +2311,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128890028</v>
+        <v>128884105</v>
       </c>
       <c r="B18" t="n">
-        <v>80091</v>
+        <v>80225</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,37 +2334,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515039</v>
+        <v>515069</v>
       </c>
       <c r="R18" t="n">
-        <v>6981285</v>
+        <v>6981348</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2405,40 +2391,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128890081</v>
+        <v>128884079</v>
       </c>
       <c r="B19" t="n">
-        <v>80091</v>
+        <v>78097</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,37 +2441,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>388</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515203</v>
+        <v>515240</v>
       </c>
       <c r="R19" t="n">
-        <v>6981449</v>
+        <v>6981445</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,14 +2498,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,22 +2525,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128890095</v>
+        <v>128884110</v>
       </c>
       <c r="B20" t="n">
-        <v>92299</v>
+        <v>80091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,37 +2548,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515145</v>
+        <v>515038</v>
       </c>
       <c r="R20" t="n">
-        <v>6981384</v>
+        <v>6981305</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2605,14 +2605,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,22 +2632,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128890026</v>
+        <v>128890095</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>92304</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,34 +2655,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2014</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515052</v>
+        <v>515145</v>
       </c>
       <c r="R21" t="n">
-        <v>6981331</v>
+        <v>6981384</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2714,7 +2719,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2729,12 +2734,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2945,10 +2950,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884107</v>
+        <v>128890026</v>
       </c>
       <c r="B24" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,37 +2961,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515060</v>
+        <v>515052</v>
       </c>
       <c r="R24" t="n">
-        <v>6981336</v>
+        <v>6981331</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3013,19 +3018,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:40</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3040,22 +3040,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884084</v>
+        <v>128884107</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515227</v>
+        <v>515060</v>
       </c>
       <c r="R25" t="n">
-        <v>6981418</v>
+        <v>6981336</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3159,10 +3159,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884110</v>
+        <v>128884084</v>
       </c>
       <c r="B26" t="n">
-        <v>80091</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515038</v>
+        <v>515227</v>
       </c>
       <c r="R26" t="n">
-        <v>6981305</v>
+        <v>6981418</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3266,48 +3266,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128884103</v>
+        <v>128890094</v>
       </c>
       <c r="B27" t="n">
-        <v>80254</v>
+        <v>80092</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>385</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515108</v>
+        <v>515188</v>
       </c>
       <c r="R27" t="n">
-        <v>6981358</v>
+        <v>6981440</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3334,19 +3334,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3361,44 +3356,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128884108</v>
+        <v>128884103</v>
       </c>
       <c r="B28" t="n">
-        <v>98625</v>
+        <v>80254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3408,10 +3403,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515059</v>
+        <v>515108</v>
       </c>
       <c r="R28" t="n">
-        <v>6981319</v>
+        <v>6981358</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3443,7 +3438,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3453,12 +3448,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>nr 10</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3587,10 +3577,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128890094</v>
+        <v>128884108</v>
       </c>
       <c r="B30" t="n">
-        <v>80092</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3598,37 +3588,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>385</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515188</v>
+        <v>515059</v>
       </c>
       <c r="R30" t="n">
-        <v>6981440</v>
+        <v>6981319</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3655,14 +3645,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>nr 10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,44 +3677,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128890043</v>
+        <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>80225</v>
+        <v>92206</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515166</v>
+        <v>515089</v>
       </c>
       <c r="R31" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,32 +3786,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128890029</v>
+        <v>128890043</v>
       </c>
       <c r="B32" t="n">
-        <v>92201</v>
+        <v>80225</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515089</v>
+        <v>515166</v>
       </c>
       <c r="R32" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128884098</v>
+        <v>128884083</v>
       </c>
       <c r="B36" t="n">
-        <v>79376</v>
+        <v>91504</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>515158</v>
+        <v>515231</v>
       </c>
       <c r="R36" t="n">
-        <v>6981406</v>
+        <v>6981417</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4286,32 +4286,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128884083</v>
+        <v>128884098</v>
       </c>
       <c r="B37" t="n">
-        <v>91499</v>
+        <v>79376</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>515231</v>
+        <v>515158</v>
       </c>
       <c r="R37" t="n">
-        <v>6981417</v>
+        <v>6981406</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128884082</v>
+        <v>128890022</v>
       </c>
       <c r="B41" t="n">
-        <v>91795</v>
+        <v>96878</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515231</v>
+        <v>515029</v>
       </c>
       <c r="R41" t="n">
-        <v>6981417</v>
+        <v>6981199</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,19 +4767,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4794,22 +4784,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128890022</v>
+        <v>128884082</v>
       </c>
       <c r="B42" t="n">
-        <v>96871</v>
+        <v>91800</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4817,37 +4807,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515029</v>
+        <v>515231</v>
       </c>
       <c r="R42" t="n">
-        <v>6981199</v>
+        <v>6981417</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4874,9 +4864,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,22 +4891,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128890045</v>
+        <v>128890031</v>
       </c>
       <c r="B43" t="n">
-        <v>80185</v>
+        <v>80129</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4914,21 +4914,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515170</v>
+        <v>515039</v>
       </c>
       <c r="R43" t="n">
-        <v>6981451</v>
+        <v>6981314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5000,10 +5000,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128890031</v>
+        <v>128890045</v>
       </c>
       <c r="B44" t="n">
-        <v>80129</v>
+        <v>80185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515039</v>
+        <v>515170</v>
       </c>
       <c r="R44" t="n">
-        <v>6981314</v>
+        <v>6981451</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5097,45 +5097,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890024</v>
+        <v>128890104</v>
       </c>
       <c r="B45" t="n">
-        <v>91499</v>
+        <v>75188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515219</v>
+        <v>515070</v>
       </c>
       <c r="R45" t="n">
-        <v>6981419</v>
+        <v>6981365</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,6 +5170,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5182,60 +5187,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890104</v>
+        <v>128884117</v>
       </c>
       <c r="B46" t="n">
-        <v>75188</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R46" t="n">
-        <v>6981365</v>
+        <v>6981204</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5262,14 +5267,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,44 +5294,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128890103</v>
+        <v>128890090</v>
       </c>
       <c r="B47" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5331,10 +5341,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515126</v>
+        <v>515013</v>
       </c>
       <c r="R47" t="n">
-        <v>6981385</v>
+        <v>6981245</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,7 +5381,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5398,7 +5408,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890090</v>
+        <v>128884114</v>
       </c>
       <c r="B48" t="n">
         <v>80225</v>
@@ -5429,17 +5439,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515013</v>
+        <v>515018</v>
       </c>
       <c r="R48" t="n">
-        <v>6981245</v>
+        <v>6981240</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5466,14 +5476,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,60 +5503,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128884117</v>
+        <v>128890103</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515013</v>
+        <v>515126</v>
       </c>
       <c r="R49" t="n">
-        <v>6981204</v>
+        <v>6981385</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5568,19 +5583,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5595,22 +5605,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128884114</v>
+        <v>128890024</v>
       </c>
       <c r="B50" t="n">
-        <v>80225</v>
+        <v>91504</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5618,37 +5628,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515018</v>
+        <v>515219</v>
       </c>
       <c r="R50" t="n">
-        <v>6981240</v>
+        <v>6981419</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5675,19 +5685,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5702,60 +5702,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128884086</v>
+        <v>128890034</v>
       </c>
       <c r="B51" t="n">
-        <v>58086</v>
+        <v>91800</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515225</v>
+        <v>515231</v>
       </c>
       <c r="R51" t="n">
-        <v>6981406</v>
+        <v>6981432</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5782,19 +5782,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5809,60 +5799,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884080</v>
+        <v>128890098</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515239</v>
+        <v>515031</v>
       </c>
       <c r="R52" t="n">
-        <v>6981443</v>
+        <v>6981292</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5889,19 +5879,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5916,22 +5901,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890034</v>
+        <v>128890041</v>
       </c>
       <c r="B53" t="n">
-        <v>91795</v>
+        <v>80225</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5939,21 +5924,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5963,10 +5948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515231</v>
+        <v>515196</v>
       </c>
       <c r="R53" t="n">
-        <v>6981432</v>
+        <v>6981428</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6025,48 +6010,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128890098</v>
+        <v>128884080</v>
       </c>
       <c r="B54" t="n">
-        <v>98625</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515031</v>
+        <v>515239</v>
       </c>
       <c r="R54" t="n">
-        <v>6981292</v>
+        <v>6981443</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6093,14 +6078,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6115,60 +6105,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128890041</v>
+        <v>128884086</v>
       </c>
       <c r="B55" t="n">
-        <v>80225</v>
+        <v>58086</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515196</v>
+        <v>515225</v>
       </c>
       <c r="R55" t="n">
-        <v>6981428</v>
+        <v>6981406</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6195,9 +6185,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6212,22 +6212,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128890105</v>
+        <v>128890025</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6235,34 +6235,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515054</v>
+        <v>515214</v>
       </c>
       <c r="R56" t="n">
-        <v>6981307</v>
+        <v>6981426</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6297,11 +6297,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6314,22 +6309,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128890025</v>
+        <v>128890105</v>
       </c>
       <c r="B57" t="n">
-        <v>91499</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6337,34 +6332,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515214</v>
+        <v>515054</v>
       </c>
       <c r="R57" t="n">
-        <v>6981426</v>
+        <v>6981308</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6399,6 +6394,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6411,44 +6411,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884100</v>
+        <v>128884119</v>
       </c>
       <c r="B58" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515158</v>
+        <v>515196</v>
       </c>
       <c r="R58" t="n">
-        <v>6981405</v>
+        <v>6981382</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6530,7 +6530,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884119</v>
+        <v>128884090</v>
       </c>
       <c r="B59" t="n">
         <v>79120</v>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515196</v>
+        <v>515210</v>
       </c>
       <c r="R59" t="n">
-        <v>6981382</v>
+        <v>6981412</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6637,32 +6637,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884090</v>
+        <v>128884100</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515210</v>
+        <v>515158</v>
       </c>
       <c r="R60" t="n">
-        <v>6981412</v>
+        <v>6981405</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6851,48 +6851,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884099</v>
+        <v>128890082</v>
       </c>
       <c r="B62" t="n">
-        <v>80225</v>
+        <v>79206</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515158</v>
+        <v>515014</v>
       </c>
       <c r="R62" t="n">
-        <v>6981406</v>
+        <v>6981245</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6919,19 +6919,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6946,12 +6941,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7182,10 +7177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128890023</v>
+        <v>128884099</v>
       </c>
       <c r="B65" t="n">
-        <v>91499</v>
+        <v>80225</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7193,37 +7188,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515081</v>
+        <v>515158</v>
       </c>
       <c r="R65" t="n">
-        <v>6981324</v>
+        <v>6981406</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7250,9 +7245,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7267,22 +7272,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128890027</v>
+        <v>128890023</v>
       </c>
       <c r="B66" t="n">
-        <v>57716</v>
+        <v>91504</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7290,21 +7295,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7314,10 +7319,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515073</v>
+        <v>515081</v>
       </c>
       <c r="R66" t="n">
-        <v>6981343</v>
+        <v>6981324</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7350,11 +7355,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7381,45 +7381,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128890082</v>
+        <v>128890027</v>
       </c>
       <c r="B67" t="n">
-        <v>79206</v>
+        <v>57716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6450</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515014</v>
+        <v>515073</v>
       </c>
       <c r="R67" t="n">
-        <v>6981245</v>
+        <v>6981343</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt på lodyta</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7471,57 +7471,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890032</v>
+        <v>128890080</v>
       </c>
       <c r="B68" t="n">
-        <v>91953</v>
+        <v>80091</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515210</v>
+        <v>515188</v>
       </c>
       <c r="R68" t="n">
-        <v>6981426</v>
+        <v>6981440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,6 +7556,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7568,44 +7573,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890077</v>
+        <v>128890075</v>
       </c>
       <c r="B69" t="n">
-        <v>75205</v>
+        <v>105680</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7615,10 +7620,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515057</v>
+        <v>515124</v>
       </c>
       <c r="R69" t="n">
-        <v>6981333</v>
+        <v>6981387</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7655,7 +7660,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7682,45 +7687,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890080</v>
+        <v>128890032</v>
       </c>
       <c r="B70" t="n">
-        <v>80091</v>
+        <v>91958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515188</v>
+        <v>515210</v>
       </c>
       <c r="R70" t="n">
-        <v>6981440</v>
+        <v>6981426</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7755,11 +7760,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7772,44 +7772,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890075</v>
+        <v>128890077</v>
       </c>
       <c r="B71" t="n">
-        <v>105673</v>
+        <v>75205</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515124</v>
+        <v>515057</v>
       </c>
       <c r="R71" t="n">
-        <v>6981387</v>
+        <v>6981333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7889,7 +7889,7 @@
         <v>128890097</v>
       </c>
       <c r="B72" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>128890101</v>
       </c>
       <c r="B73" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128890084</v>
+        <v>128884111</v>
       </c>
       <c r="B74" t="n">
-        <v>91795</v>
+        <v>79120</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8101,37 +8101,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515029</v>
+        <v>515033</v>
       </c>
       <c r="R74" t="n">
-        <v>6981276</v>
+        <v>6981298</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8158,14 +8158,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8180,19 +8185,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884111</v>
+        <v>128884094</v>
       </c>
       <c r="B75" t="n">
         <v>79120</v>
@@ -8227,10 +8232,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>515033</v>
+        <v>515181</v>
       </c>
       <c r="R75" t="n">
-        <v>6981298</v>
+        <v>6981416</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -8262,7 +8267,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8272,7 +8277,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8299,10 +8304,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884094</v>
+        <v>128890084</v>
       </c>
       <c r="B76" t="n">
-        <v>79120</v>
+        <v>91800</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8310,37 +8315,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515181</v>
+        <v>515029</v>
       </c>
       <c r="R76" t="n">
-        <v>6981416</v>
+        <v>6981276</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8367,19 +8372,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,19 +8394,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128884102</v>
+        <v>128890037</v>
       </c>
       <c r="B77" t="n">
         <v>80225</v>
@@ -8437,17 +8437,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515111</v>
+        <v>515026</v>
       </c>
       <c r="R77" t="n">
-        <v>6981360</v>
+        <v>6981261</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8474,19 +8474,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8501,19 +8491,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128890037</v>
+        <v>128884102</v>
       </c>
       <c r="B78" t="n">
         <v>80225</v>
@@ -8544,17 +8534,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515026</v>
+        <v>515111</v>
       </c>
       <c r="R78" t="n">
-        <v>6981261</v>
+        <v>6981360</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8581,9 +8571,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8598,12 +8598,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8613,7 +8613,7 @@
         <v>128890085</v>
       </c>
       <c r="B79" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8712,48 +8712,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128884081</v>
+        <v>128890093</v>
       </c>
       <c r="B80" t="n">
-        <v>91499</v>
+        <v>80092</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>385</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515230</v>
+        <v>515053</v>
       </c>
       <c r="R80" t="n">
-        <v>6981431</v>
+        <v>6981314</v>
       </c>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8780,19 +8780,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8807,22 +8802,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884091</v>
+        <v>128884081</v>
       </c>
       <c r="B81" t="n">
-        <v>80225</v>
+        <v>91504</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8830,21 +8825,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8854,10 +8849,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515199</v>
+        <v>515230</v>
       </c>
       <c r="R81" t="n">
-        <v>6981419</v>
+        <v>6981431</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -8889,7 +8884,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8899,7 +8894,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8926,48 +8921,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128890087</v>
+        <v>128884091</v>
       </c>
       <c r="B82" t="n">
-        <v>80253</v>
+        <v>80225</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515014</v>
+        <v>515199</v>
       </c>
       <c r="R82" t="n">
-        <v>6981245</v>
+        <v>6981419</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8994,14 +8989,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På lodyta</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9016,44 +9016,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890099</v>
+        <v>128890091</v>
       </c>
       <c r="B83" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515054</v>
+        <v>515069</v>
       </c>
       <c r="R83" t="n">
-        <v>6981307</v>
+        <v>6981349</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9130,45 +9130,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890096</v>
+        <v>128890038</v>
       </c>
       <c r="B84" t="n">
-        <v>80185</v>
+        <v>80225</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515014</v>
+        <v>515041</v>
       </c>
       <c r="R84" t="n">
-        <v>6981245</v>
+        <v>6981296</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9203,11 +9203,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9220,44 +9215,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890091</v>
+        <v>128890087</v>
       </c>
       <c r="B85" t="n">
-        <v>80225</v>
+        <v>80253</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9267,10 +9262,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515069</v>
+        <v>515014</v>
       </c>
       <c r="R85" t="n">
-        <v>6981349</v>
+        <v>6981245</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9307,7 +9302,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9334,45 +9329,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890038</v>
+        <v>128890096</v>
       </c>
       <c r="B86" t="n">
-        <v>80225</v>
+        <v>80185</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515041</v>
+        <v>515014</v>
       </c>
       <c r="R86" t="n">
-        <v>6981296</v>
+        <v>6981245</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9407,6 +9402,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9419,22 +9419,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890093</v>
+        <v>128890099</v>
       </c>
       <c r="B87" t="n">
-        <v>80092</v>
+        <v>98632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>385</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515053</v>
+        <v>515054</v>
       </c>
       <c r="R87" t="n">
-        <v>6981314</v>
+        <v>6981308</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884109</v>
+        <v>128890092</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>80261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515053</v>
+        <v>515067</v>
       </c>
       <c r="R2" t="n">
-        <v>6981306</v>
+        <v>6981353</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:44</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884101</v>
+        <v>128884097</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515135</v>
+        <v>515184</v>
       </c>
       <c r="R3" t="n">
-        <v>6981381</v>
+        <v>6981392</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884097</v>
+        <v>128884109</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515184</v>
+        <v>515053</v>
       </c>
       <c r="R4" t="n">
-        <v>6981392</v>
+        <v>6981306</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -959,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,48 +991,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128890092</v>
+        <v>128884101</v>
       </c>
       <c r="B5" t="n">
-        <v>80261</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515067</v>
+        <v>515135</v>
       </c>
       <c r="R5" t="n">
-        <v>6981353</v>
+        <v>6981381</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,14 +1059,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,12 +1086,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1409,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884093</v>
+        <v>128884087</v>
       </c>
       <c r="B9" t="n">
-        <v>105680</v>
+        <v>80225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515174</v>
+        <v>515217</v>
       </c>
       <c r="R9" t="n">
-        <v>6981416</v>
+        <v>6981406</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128884087</v>
+        <v>128890036</v>
       </c>
       <c r="B10" t="n">
         <v>80225</v>
@@ -1547,17 +1547,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515217</v>
+        <v>515018</v>
       </c>
       <c r="R10" t="n">
-        <v>6981406</v>
+        <v>6981217</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,19 +1584,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,60 +1601,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128890036</v>
+        <v>128884093</v>
       </c>
       <c r="B11" t="n">
-        <v>80225</v>
+        <v>105680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515018</v>
+        <v>515174</v>
       </c>
       <c r="R11" t="n">
-        <v>6981217</v>
+        <v>6981416</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,9 +1681,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,57 +1708,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890100</v>
+        <v>128890033</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>75015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515060</v>
+        <v>515018</v>
       </c>
       <c r="R12" t="n">
-        <v>6981326</v>
+        <v>6981215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,11 +1793,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1810,44 +1805,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890033</v>
+        <v>128890039</v>
       </c>
       <c r="B13" t="n">
-        <v>75015</v>
+        <v>80225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515018</v>
+        <v>515123</v>
       </c>
       <c r="R13" t="n">
-        <v>6981215</v>
+        <v>6981380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,48 +1914,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128884116</v>
+        <v>128890100</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515030</v>
+        <v>515060</v>
       </c>
       <c r="R14" t="n">
-        <v>6981199</v>
+        <v>6981326</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,19 +1982,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:07</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128890039</v>
+        <v>128884116</v>
       </c>
       <c r="B15" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,37 +2027,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515123</v>
+        <v>515030</v>
       </c>
       <c r="R15" t="n">
-        <v>6981380</v>
+        <v>6981199</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2094,9 +2084,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2644,48 +2644,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128890095</v>
+        <v>128884089</v>
       </c>
       <c r="B21" t="n">
-        <v>92304</v>
+        <v>80254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2014</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515145</v>
+        <v>515218</v>
       </c>
       <c r="R21" t="n">
-        <v>6981384</v>
+        <v>6981412</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,14 +2712,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2734,22 +2739,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128890030</v>
+        <v>128884107</v>
       </c>
       <c r="B22" t="n">
-        <v>80226</v>
+        <v>80225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2757,37 +2762,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515032</v>
+        <v>515060</v>
       </c>
       <c r="R22" t="n">
-        <v>6981265</v>
+        <v>6981336</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,9 +2819,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2831,60 +2846,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128884089</v>
+        <v>128890095</v>
       </c>
       <c r="B23" t="n">
-        <v>80254</v>
+        <v>92304</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2014</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515218</v>
+        <v>515145</v>
       </c>
       <c r="R23" t="n">
-        <v>6981412</v>
+        <v>6981384</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2911,19 +2926,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:09</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2938,22 +2948,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128890026</v>
+        <v>128884084</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,37 +2971,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515052</v>
+        <v>515227</v>
       </c>
       <c r="R24" t="n">
-        <v>6981331</v>
+        <v>6981418</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,14 +3028,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3040,22 +3055,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884107</v>
+        <v>128890030</v>
       </c>
       <c r="B25" t="n">
-        <v>80225</v>
+        <v>80226</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,37 +3078,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515060</v>
+        <v>515032</v>
       </c>
       <c r="R25" t="n">
-        <v>6981336</v>
+        <v>6981265</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3120,19 +3135,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3147,22 +3152,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884084</v>
+        <v>128890026</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3170,37 +3175,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515227</v>
+        <v>515052</v>
       </c>
       <c r="R26" t="n">
-        <v>6981418</v>
+        <v>6981331</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3227,19 +3232,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:05</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,12 +3254,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128884117</v>
+        <v>128890090</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5210,37 +5210,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>515013</v>
       </c>
       <c r="R46" t="n">
-        <v>6981204</v>
+        <v>6981245</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5267,19 +5267,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5294,19 +5289,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128890090</v>
+        <v>128884114</v>
       </c>
       <c r="B47" t="n">
         <v>80225</v>
@@ -5337,17 +5332,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515013</v>
+        <v>515018</v>
       </c>
       <c r="R47" t="n">
-        <v>6981245</v>
+        <v>6981240</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5374,14 +5369,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,22 +5396,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128884114</v>
+        <v>128884117</v>
       </c>
       <c r="B48" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,21 +5419,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515018</v>
+        <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981240</v>
+        <v>6981204</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5515,45 +5515,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890103</v>
+        <v>128890024</v>
       </c>
       <c r="B49" t="n">
-        <v>98632</v>
+        <v>91504</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515126</v>
+        <v>515219</v>
       </c>
       <c r="R49" t="n">
-        <v>6981385</v>
+        <v>6981419</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5588,11 +5588,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5605,57 +5600,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890024</v>
+        <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>91504</v>
+        <v>98632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515219</v>
+        <v>515126</v>
       </c>
       <c r="R50" t="n">
-        <v>6981419</v>
+        <v>6981385</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5690,6 +5685,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5702,22 +5702,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890034</v>
+        <v>128890041</v>
       </c>
       <c r="B51" t="n">
-        <v>91800</v>
+        <v>80225</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515231</v>
+        <v>515196</v>
       </c>
       <c r="R51" t="n">
-        <v>6981432</v>
+        <v>6981428</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5811,48 +5811,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890098</v>
+        <v>128884080</v>
       </c>
       <c r="B52" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515031</v>
+        <v>515239</v>
       </c>
       <c r="R52" t="n">
-        <v>6981292</v>
+        <v>6981443</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5879,14 +5879,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5901,57 +5906,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890041</v>
+        <v>128890098</v>
       </c>
       <c r="B53" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515196</v>
+        <v>515031</v>
       </c>
       <c r="R53" t="n">
-        <v>6981428</v>
+        <v>6981292</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5986,6 +5991,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5998,22 +6008,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884080</v>
+        <v>128890034</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>91800</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6021,37 +6031,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515239</v>
+        <v>515231</v>
       </c>
       <c r="R54" t="n">
-        <v>6981443</v>
+        <v>6981432</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6078,19 +6088,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6105,12 +6105,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6224,48 +6224,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128890025</v>
+        <v>128884100</v>
       </c>
       <c r="B56" t="n">
-        <v>91504</v>
+        <v>80254</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515214</v>
+        <v>515158</v>
       </c>
       <c r="R56" t="n">
-        <v>6981426</v>
+        <v>6981405</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6292,9 +6292,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6309,22 +6319,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128890105</v>
+        <v>128890025</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6332,34 +6342,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515054</v>
+        <v>515214</v>
       </c>
       <c r="R57" t="n">
-        <v>6981308</v>
+        <v>6981426</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6394,11 +6404,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6411,19 +6416,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884119</v>
+        <v>128890105</v>
       </c>
       <c r="B58" t="n">
         <v>79120</v>
@@ -6454,17 +6459,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515196</v>
+        <v>515054</v>
       </c>
       <c r="R58" t="n">
-        <v>6981382</v>
+        <v>6981308</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6491,19 +6496,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>16:26</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6518,19 +6518,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884090</v>
+        <v>128884119</v>
       </c>
       <c r="B59" t="n">
         <v>79120</v>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515210</v>
+        <v>515196</v>
       </c>
       <c r="R59" t="n">
-        <v>6981412</v>
+        <v>6981382</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6637,32 +6637,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884100</v>
+        <v>128884090</v>
       </c>
       <c r="B60" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515158</v>
+        <v>515210</v>
       </c>
       <c r="R60" t="n">
-        <v>6981405</v>
+        <v>6981412</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6851,48 +6851,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128890082</v>
+        <v>128884095</v>
       </c>
       <c r="B62" t="n">
-        <v>79206</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515014</v>
+        <v>515183</v>
       </c>
       <c r="R62" t="n">
-        <v>6981245</v>
+        <v>6981391</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6919,14 +6919,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt på lodyta</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,19 +6951,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884095</v>
+        <v>128884113</v>
       </c>
       <c r="B63" t="n">
         <v>79120</v>
@@ -6988,10 +6998,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515183</v>
+        <v>515021</v>
       </c>
       <c r="R63" t="n">
-        <v>6981391</v>
+        <v>6981285</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7023,7 +7033,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7033,7 +7043,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7065,48 +7075,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884113</v>
+        <v>128890082</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>79206</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515021</v>
+        <v>515014</v>
       </c>
       <c r="R64" t="n">
-        <v>6981285</v>
+        <v>6981245</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7133,24 +7143,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7165,12 +7165,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7585,32 +7585,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890075</v>
+        <v>128890077</v>
       </c>
       <c r="B69" t="n">
-        <v>105680</v>
+        <v>75205</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515124</v>
+        <v>515057</v>
       </c>
       <c r="R69" t="n">
-        <v>6981387</v>
+        <v>6981333</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7784,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890077</v>
+        <v>128890097</v>
       </c>
       <c r="B71" t="n">
-        <v>75205</v>
+        <v>98632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515057</v>
+        <v>515060</v>
       </c>
       <c r="R71" t="n">
-        <v>6981333</v>
+        <v>6981339</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890097</v>
+        <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>98632</v>
+        <v>105680</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515060</v>
+        <v>515124</v>
       </c>
       <c r="R72" t="n">
-        <v>6981339</v>
+        <v>6981387</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,32 +7988,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128890101</v>
+        <v>128890084</v>
       </c>
       <c r="B73" t="n">
-        <v>98632</v>
+        <v>91800</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>515108</v>
+        <v>515029</v>
       </c>
       <c r="R73" t="n">
-        <v>6981372</v>
+        <v>6981276</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>16 plantor på marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8304,32 +8304,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128890084</v>
+        <v>128890101</v>
       </c>
       <c r="B76" t="n">
-        <v>91800</v>
+        <v>98632</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515029</v>
+        <v>515108</v>
       </c>
       <c r="R76" t="n">
-        <v>6981276</v>
+        <v>6981372</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8406,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890037</v>
+        <v>128890085</v>
       </c>
       <c r="B77" t="n">
-        <v>80225</v>
+        <v>91800</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515026</v>
+        <v>515034</v>
       </c>
       <c r="R77" t="n">
-        <v>6981261</v>
+        <v>6981293</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,6 +8479,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8491,19 +8496,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884102</v>
+        <v>128890037</v>
       </c>
       <c r="B78" t="n">
         <v>80225</v>
@@ -8534,17 +8539,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515111</v>
+        <v>515026</v>
       </c>
       <c r="R78" t="n">
-        <v>6981360</v>
+        <v>6981261</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8571,19 +8576,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8598,22 +8593,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128890085</v>
+        <v>128884102</v>
       </c>
       <c r="B79" t="n">
-        <v>91800</v>
+        <v>80225</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8621,37 +8616,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515034</v>
+        <v>515111</v>
       </c>
       <c r="R79" t="n">
-        <v>6981293</v>
+        <v>6981360</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8678,14 +8673,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,12 +8700,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8921,48 +8921,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884091</v>
+        <v>128890087</v>
       </c>
       <c r="B82" t="n">
-        <v>80225</v>
+        <v>80253</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515199</v>
+        <v>515014</v>
       </c>
       <c r="R82" t="n">
-        <v>6981419</v>
+        <v>6981245</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8989,19 +8989,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9016,19 +9011,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890091</v>
+        <v>128884091</v>
       </c>
       <c r="B83" t="n">
         <v>80225</v>
@@ -9059,17 +9054,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515069</v>
+        <v>515199</v>
       </c>
       <c r="R83" t="n">
-        <v>6981349</v>
+        <v>6981419</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9096,14 +9091,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9118,19 +9118,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890038</v>
+        <v>128890091</v>
       </c>
       <c r="B84" t="n">
         <v>80225</v>
@@ -9161,14 +9161,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515041</v>
+        <v>515069</v>
       </c>
       <c r="R84" t="n">
-        <v>6981296</v>
+        <v>6981349</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9203,6 +9203,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9215,57 +9220,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890087</v>
+        <v>128890038</v>
       </c>
       <c r="B85" t="n">
-        <v>80253</v>
+        <v>80225</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515014</v>
+        <v>515041</v>
       </c>
       <c r="R85" t="n">
-        <v>6981245</v>
+        <v>6981296</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9300,11 +9305,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På lodyta</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9317,44 +9317,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890096</v>
+        <v>128890099</v>
       </c>
       <c r="B86" t="n">
-        <v>80185</v>
+        <v>98632</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515014</v>
+        <v>515054</v>
       </c>
       <c r="R86" t="n">
-        <v>6981245</v>
+        <v>6981308</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9431,32 +9431,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890099</v>
+        <v>128890096</v>
       </c>
       <c r="B87" t="n">
-        <v>98632</v>
+        <v>80185</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515054</v>
+        <v>515014</v>
       </c>
       <c r="R87" t="n">
-        <v>6981308</v>
+        <v>6981245</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128890092</v>
+        <v>128884109</v>
       </c>
       <c r="B2" t="n">
-        <v>80261</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515067</v>
+        <v>515053</v>
       </c>
       <c r="R2" t="n">
-        <v>6981353</v>
+        <v>6981306</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +743,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884097</v>
+        <v>128884101</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515184</v>
+        <v>515135</v>
       </c>
       <c r="R3" t="n">
-        <v>6981392</v>
+        <v>6981381</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,48 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884109</v>
+        <v>128890092</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>80261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515053</v>
+        <v>515067</v>
       </c>
       <c r="R4" t="n">
-        <v>6981306</v>
+        <v>6981353</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,19 +957,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:44</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884101</v>
+        <v>128884097</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515135</v>
+        <v>515184</v>
       </c>
       <c r="R5" t="n">
-        <v>6981381</v>
+        <v>6981392</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1720,32 +1720,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890033</v>
+        <v>128890039</v>
       </c>
       <c r="B12" t="n">
-        <v>75015</v>
+        <v>80225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515018</v>
+        <v>515123</v>
       </c>
       <c r="R12" t="n">
-        <v>6981215</v>
+        <v>6981380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,32 +1817,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890039</v>
+        <v>128890033</v>
       </c>
       <c r="B13" t="n">
-        <v>80225</v>
+        <v>75015</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515123</v>
+        <v>515018</v>
       </c>
       <c r="R13" t="n">
-        <v>6981380</v>
+        <v>6981215</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,48 +1914,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128890100</v>
+        <v>128884116</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515060</v>
+        <v>515030</v>
       </c>
       <c r="R14" t="n">
-        <v>6981326</v>
+        <v>6981199</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,14 +1982,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,60 +2009,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128884116</v>
+        <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515030</v>
+        <v>515060</v>
       </c>
       <c r="R15" t="n">
-        <v>6981199</v>
+        <v>6981326</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2084,19 +2089,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:07</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884084</v>
+        <v>128890030</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>80226</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515227</v>
+        <v>515032</v>
       </c>
       <c r="R24" t="n">
-        <v>6981418</v>
+        <v>6981265</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3028,19 +3028,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3055,22 +3045,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128890030</v>
+        <v>128890026</v>
       </c>
       <c r="B25" t="n">
-        <v>80226</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,21 +3068,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3102,10 +3092,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515032</v>
+        <v>515052</v>
       </c>
       <c r="R25" t="n">
-        <v>6981265</v>
+        <v>6981331</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,6 +3128,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3164,10 +3159,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128890026</v>
+        <v>128884084</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,37 +3170,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515052</v>
+        <v>515227</v>
       </c>
       <c r="R26" t="n">
-        <v>6981331</v>
+        <v>6981418</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3232,14 +3227,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,12 +3254,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3368,48 +3368,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128884103</v>
+        <v>128890088</v>
       </c>
       <c r="B28" t="n">
-        <v>80254</v>
+        <v>79591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>1797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515108</v>
+        <v>515103</v>
       </c>
       <c r="R28" t="n">
-        <v>6981358</v>
+        <v>6981364</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3436,19 +3436,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3463,60 +3458,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128890088</v>
+        <v>128884103</v>
       </c>
       <c r="B29" t="n">
-        <v>79591</v>
+        <v>80254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1797</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515103</v>
+        <v>515108</v>
       </c>
       <c r="R29" t="n">
-        <v>6981364</v>
+        <v>6981358</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3543,14 +3538,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3565,12 +3565,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5097,32 +5097,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890104</v>
+        <v>128890103</v>
       </c>
       <c r="B45" t="n">
-        <v>75188</v>
+        <v>98632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515070</v>
+        <v>515126</v>
       </c>
       <c r="R45" t="n">
-        <v>6981365</v>
+        <v>6981385</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5408,48 +5408,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128884117</v>
+        <v>128890104</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>75188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515013</v>
+        <v>515070</v>
       </c>
       <c r="R48" t="n">
-        <v>6981204</v>
+        <v>6981365</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5476,19 +5476,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5503,22 +5498,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890024</v>
+        <v>128884117</v>
       </c>
       <c r="B49" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5526,37 +5521,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515219</v>
+        <v>515013</v>
       </c>
       <c r="R49" t="n">
-        <v>6981419</v>
+        <v>6981204</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5583,9 +5578,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5600,57 +5605,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890103</v>
+        <v>128890024</v>
       </c>
       <c r="B50" t="n">
-        <v>98632</v>
+        <v>91504</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515126</v>
+        <v>515219</v>
       </c>
       <c r="R50" t="n">
-        <v>6981385</v>
+        <v>6981419</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5685,11 +5690,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5702,22 +5702,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890041</v>
+        <v>128890034</v>
       </c>
       <c r="B51" t="n">
-        <v>80225</v>
+        <v>91800</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515196</v>
+        <v>515231</v>
       </c>
       <c r="R51" t="n">
-        <v>6981428</v>
+        <v>6981432</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884080</v>
+        <v>128890041</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5822,37 +5822,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515239</v>
+        <v>515196</v>
       </c>
       <c r="R52" t="n">
-        <v>6981443</v>
+        <v>6981428</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5879,19 +5879,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5906,60 +5896,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890098</v>
+        <v>128884080</v>
       </c>
       <c r="B53" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515031</v>
+        <v>515239</v>
       </c>
       <c r="R53" t="n">
-        <v>6981292</v>
+        <v>6981443</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5986,14 +5976,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6008,60 +6003,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128890034</v>
+        <v>128884086</v>
       </c>
       <c r="B54" t="n">
-        <v>91800</v>
+        <v>58086</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515231</v>
+        <v>515225</v>
       </c>
       <c r="R54" t="n">
-        <v>6981432</v>
+        <v>6981406</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6088,9 +6083,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6105,60 +6110,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128884086</v>
+        <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>58086</v>
+        <v>98632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515225</v>
+        <v>515031</v>
       </c>
       <c r="R55" t="n">
-        <v>6981406</v>
+        <v>6981292</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6185,19 +6190,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:07</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6212,60 +6212,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884100</v>
+        <v>128890025</v>
       </c>
       <c r="B56" t="n">
-        <v>80254</v>
+        <v>91504</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515158</v>
+        <v>515214</v>
       </c>
       <c r="R56" t="n">
-        <v>6981405</v>
+        <v>6981426</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6292,19 +6292,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6319,60 +6309,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128890025</v>
+        <v>128884100</v>
       </c>
       <c r="B57" t="n">
-        <v>91504</v>
+        <v>80254</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515214</v>
+        <v>515158</v>
       </c>
       <c r="R57" t="n">
-        <v>6981426</v>
+        <v>6981405</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6399,9 +6389,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6416,12 +6416,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884104</v>
+        <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6755,37 +6755,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515104</v>
+        <v>515081</v>
       </c>
       <c r="R61" t="n">
-        <v>6981353</v>
+        <v>6981324</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,19 +6812,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6839,60 +6829,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884095</v>
+        <v>128890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>79206</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515183</v>
+        <v>515014</v>
       </c>
       <c r="R62" t="n">
-        <v>6981391</v>
+        <v>6981245</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6919,24 +6909,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6951,22 +6931,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884113</v>
+        <v>128884099</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6974,21 +6954,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6998,10 +6978,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515021</v>
+        <v>515158</v>
       </c>
       <c r="R63" t="n">
-        <v>6981285</v>
+        <v>6981406</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7033,7 +7013,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7043,12 +7023,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7075,48 +7050,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128890082</v>
+        <v>128884104</v>
       </c>
       <c r="B64" t="n">
-        <v>79206</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515014</v>
+        <v>515104</v>
       </c>
       <c r="R64" t="n">
-        <v>6981245</v>
+        <v>6981353</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7143,14 +7118,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7165,22 +7145,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884099</v>
+        <v>128884095</v>
       </c>
       <c r="B65" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7188,21 +7168,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7212,10 +7192,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515158</v>
+        <v>515183</v>
       </c>
       <c r="R65" t="n">
-        <v>6981406</v>
+        <v>6981391</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7247,7 +7227,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7257,7 +7237,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7284,10 +7269,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128890023</v>
+        <v>128884113</v>
       </c>
       <c r="B66" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7295,37 +7280,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515081</v>
+        <v>515021</v>
       </c>
       <c r="R66" t="n">
-        <v>6981324</v>
+        <v>6981285</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7352,9 +7337,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7369,12 +7369,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7483,32 +7483,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890080</v>
+        <v>128890075</v>
       </c>
       <c r="B68" t="n">
-        <v>80091</v>
+        <v>105680</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>388</v>
+        <v>221725</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515188</v>
+        <v>515124</v>
       </c>
       <c r="R68" t="n">
-        <v>6981440</v>
+        <v>6981387</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7585,32 +7585,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890077</v>
+        <v>128890097</v>
       </c>
       <c r="B69" t="n">
-        <v>75205</v>
+        <v>98632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515057</v>
+        <v>515060</v>
       </c>
       <c r="R69" t="n">
-        <v>6981333</v>
+        <v>6981339</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7784,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890097</v>
+        <v>128890080</v>
       </c>
       <c r="B71" t="n">
-        <v>98632</v>
+        <v>80091</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515060</v>
+        <v>515188</v>
       </c>
       <c r="R71" t="n">
-        <v>6981339</v>
+        <v>6981440</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890075</v>
+        <v>128890077</v>
       </c>
       <c r="B72" t="n">
-        <v>105680</v>
+        <v>75205</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515124</v>
+        <v>515057</v>
       </c>
       <c r="R72" t="n">
-        <v>6981387</v>
+        <v>6981333</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8406,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890085</v>
+        <v>128890037</v>
       </c>
       <c r="B77" t="n">
-        <v>91800</v>
+        <v>80225</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515034</v>
+        <v>515026</v>
       </c>
       <c r="R77" t="n">
-        <v>6981293</v>
+        <v>6981261</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,11 +8479,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8496,19 +8491,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128890037</v>
+        <v>128884102</v>
       </c>
       <c r="B78" t="n">
         <v>80225</v>
@@ -8539,17 +8534,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515026</v>
+        <v>515111</v>
       </c>
       <c r="R78" t="n">
-        <v>6981261</v>
+        <v>6981360</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8576,9 +8571,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8593,22 +8598,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884102</v>
+        <v>128890085</v>
       </c>
       <c r="B79" t="n">
-        <v>80225</v>
+        <v>91800</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8616,37 +8621,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515111</v>
+        <v>515034</v>
       </c>
       <c r="R79" t="n">
-        <v>6981360</v>
+        <v>6981293</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8673,19 +8678,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,12 +8700,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9329,32 +9329,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890099</v>
+        <v>128890096</v>
       </c>
       <c r="B86" t="n">
-        <v>98632</v>
+        <v>80185</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515054</v>
+        <v>515014</v>
       </c>
       <c r="R86" t="n">
-        <v>6981308</v>
+        <v>6981245</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9431,32 +9431,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890096</v>
+        <v>128890099</v>
       </c>
       <c r="B87" t="n">
-        <v>80185</v>
+        <v>98632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515014</v>
+        <v>515054</v>
       </c>
       <c r="R87" t="n">
-        <v>6981245</v>
+        <v>6981308</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884109</v>
+        <v>128884101</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515053</v>
+        <v>515135</v>
       </c>
       <c r="R2" t="n">
-        <v>6981306</v>
+        <v>6981381</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884101</v>
+        <v>128890092</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>80265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515135</v>
+        <v>515067</v>
       </c>
       <c r="R3" t="n">
-        <v>6981381</v>
+        <v>6981353</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +850,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:29</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,60 +872,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128890092</v>
+        <v>128884097</v>
       </c>
       <c r="B4" t="n">
-        <v>80261</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515067</v>
+        <v>515184</v>
       </c>
       <c r="R4" t="n">
-        <v>6981353</v>
+        <v>6981392</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,14 +952,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884097</v>
+        <v>128884109</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515184</v>
+        <v>515053</v>
       </c>
       <c r="R5" t="n">
-        <v>6981392</v>
+        <v>6981306</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,7 +1101,7 @@
         <v>128884115</v>
       </c>
       <c r="B6" t="n">
-        <v>80185</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128890079</v>
+        <v>128890102</v>
       </c>
       <c r="B7" t="n">
-        <v>91469</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515071</v>
+        <v>515229</v>
       </c>
       <c r="R7" t="n">
-        <v>6981351</v>
+        <v>6981403</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>50 plantor i i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128890102</v>
+        <v>128890079</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>91473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515229</v>
+        <v>515071</v>
       </c>
       <c r="R8" t="n">
-        <v>6981403</v>
+        <v>6981351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>50 plantor i i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884087</v>
+        <v>128884093</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>105684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515217</v>
+        <v>515174</v>
       </c>
       <c r="R9" t="n">
-        <v>6981406</v>
+        <v>6981416</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128890036</v>
+        <v>128884087</v>
       </c>
       <c r="B10" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,17 +1547,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515018</v>
+        <v>515217</v>
       </c>
       <c r="R10" t="n">
-        <v>6981217</v>
+        <v>6981406</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,9 +1584,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,60 +1611,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128884093</v>
+        <v>128890036</v>
       </c>
       <c r="B11" t="n">
-        <v>105680</v>
+        <v>80229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515174</v>
+        <v>515018</v>
       </c>
       <c r="R11" t="n">
-        <v>6981416</v>
+        <v>6981217</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1681,19 +1691,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,44 +1708,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890039</v>
+        <v>128890033</v>
       </c>
       <c r="B12" t="n">
-        <v>80225</v>
+        <v>75019</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515123</v>
+        <v>515018</v>
       </c>
       <c r="R12" t="n">
-        <v>6981380</v>
+        <v>6981215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,48 +1817,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890033</v>
+        <v>128884116</v>
       </c>
       <c r="B13" t="n">
-        <v>75015</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515018</v>
+        <v>515030</v>
       </c>
       <c r="R13" t="n">
-        <v>6981215</v>
+        <v>6981199</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,9 +1885,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128884116</v>
+        <v>128890039</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,37 +1935,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515030</v>
+        <v>515123</v>
       </c>
       <c r="R14" t="n">
-        <v>6981199</v>
+        <v>6981380</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,19 +1992,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,12 +2009,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
         <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>128890028</v>
       </c>
       <c r="B16" t="n">
-        <v>80091</v>
+        <v>80095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>128890081</v>
       </c>
       <c r="B17" t="n">
-        <v>80091</v>
+        <v>80095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128884105</v>
       </c>
       <c r="B18" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128884079</v>
       </c>
       <c r="B19" t="n">
-        <v>78097</v>
+        <v>78101</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>128884110</v>
       </c>
       <c r="B20" t="n">
-        <v>80091</v>
+        <v>80095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2644,48 +2644,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128884089</v>
+        <v>128890095</v>
       </c>
       <c r="B21" t="n">
-        <v>80254</v>
+        <v>92308</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>2014</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515218</v>
+        <v>515145</v>
       </c>
       <c r="R21" t="n">
-        <v>6981412</v>
+        <v>6981384</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,19 +2712,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:09</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2739,22 +2734,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884107</v>
+        <v>128890030</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>80230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,37 +2757,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515060</v>
+        <v>515032</v>
       </c>
       <c r="R22" t="n">
-        <v>6981336</v>
+        <v>6981265</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2819,19 +2814,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2846,22 +2831,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128890095</v>
+        <v>128890026</v>
       </c>
       <c r="B23" t="n">
-        <v>92304</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2869,34 +2854,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2014</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515145</v>
+        <v>515052</v>
       </c>
       <c r="R23" t="n">
-        <v>6981384</v>
+        <v>6981331</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2933,7 +2918,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gråalslåga i gransumpskog</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2948,60 +2933,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128890030</v>
+        <v>128884089</v>
       </c>
       <c r="B24" t="n">
-        <v>80226</v>
+        <v>80258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515032</v>
+        <v>515218</v>
       </c>
       <c r="R24" t="n">
-        <v>6981265</v>
+        <v>6981412</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3028,9 +3013,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3045,22 +3040,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128890026</v>
+        <v>128884107</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>80229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3068,37 +3063,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515052</v>
+        <v>515060</v>
       </c>
       <c r="R25" t="n">
-        <v>6981331</v>
+        <v>6981336</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3125,14 +3120,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3147,12 +3147,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3162,7 +3162,7 @@
         <v>128884084</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3266,48 +3266,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128890094</v>
+        <v>128884103</v>
       </c>
       <c r="B27" t="n">
-        <v>80092</v>
+        <v>80258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>385</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515188</v>
+        <v>515108</v>
       </c>
       <c r="R27" t="n">
-        <v>6981440</v>
+        <v>6981358</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3334,14 +3334,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,60 +3361,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128890088</v>
+        <v>128884108</v>
       </c>
       <c r="B28" t="n">
-        <v>79591</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1797</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515103</v>
+        <v>515059</v>
       </c>
       <c r="R28" t="n">
-        <v>6981364</v>
+        <v>6981319</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3436,14 +3441,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+          <t>nr 10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3458,60 +3473,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128884103</v>
+        <v>128890094</v>
       </c>
       <c r="B29" t="n">
-        <v>80254</v>
+        <v>80096</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>385</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515108</v>
+        <v>515188</v>
       </c>
       <c r="R29" t="n">
-        <v>6981358</v>
+        <v>6981440</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3538,19 +3553,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3565,60 +3575,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128884108</v>
+        <v>128890088</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>79595</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515059</v>
+        <v>515103</v>
       </c>
       <c r="R30" t="n">
-        <v>6981319</v>
+        <v>6981364</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3645,24 +3655,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>nr 10</t>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,12 +3677,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
         <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>128890043</v>
       </c>
       <c r="B32" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>128890042</v>
       </c>
       <c r="B33" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>128890076</v>
       </c>
       <c r="B34" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128890035</v>
       </c>
       <c r="B35" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128884083</v>
+        <v>128884098</v>
       </c>
       <c r="B36" t="n">
-        <v>91504</v>
+        <v>79380</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>515231</v>
+        <v>515158</v>
       </c>
       <c r="R36" t="n">
-        <v>6981417</v>
+        <v>6981406</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4286,32 +4286,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128884098</v>
+        <v>128884092</v>
       </c>
       <c r="B37" t="n">
-        <v>79376</v>
+        <v>80229</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>515158</v>
+        <v>515180</v>
       </c>
       <c r="R37" t="n">
-        <v>6981406</v>
+        <v>6981435</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4393,10 +4393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128884092</v>
+        <v>128884083</v>
       </c>
       <c r="B38" t="n">
-        <v>80225</v>
+        <v>91508</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>515180</v>
+        <v>515231</v>
       </c>
       <c r="R38" t="n">
-        <v>6981435</v>
+        <v>6981417</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4503,7 +4503,7 @@
         <v>128890083</v>
       </c>
       <c r="B39" t="n">
-        <v>80129</v>
+        <v>80133</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>128890040</v>
       </c>
       <c r="B40" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128890022</v>
+        <v>128884082</v>
       </c>
       <c r="B41" t="n">
-        <v>96878</v>
+        <v>91804</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515029</v>
+        <v>515231</v>
       </c>
       <c r="R41" t="n">
-        <v>6981199</v>
+        <v>6981417</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,9 +4767,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4784,60 +4794,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128884082</v>
+        <v>128890031</v>
       </c>
       <c r="B42" t="n">
-        <v>91800</v>
+        <v>80133</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515231</v>
+        <v>515039</v>
       </c>
       <c r="R42" t="n">
-        <v>6981417</v>
+        <v>6981314</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4864,19 +4874,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,22 +4891,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128890031</v>
+        <v>128890045</v>
       </c>
       <c r="B43" t="n">
-        <v>80129</v>
+        <v>80189</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4914,21 +4914,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515039</v>
+        <v>515170</v>
       </c>
       <c r="R43" t="n">
-        <v>6981314</v>
+        <v>6981451</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5000,32 +5000,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128890045</v>
+        <v>128890022</v>
       </c>
       <c r="B44" t="n">
-        <v>80185</v>
+        <v>96882</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515170</v>
+        <v>515029</v>
       </c>
       <c r="R44" t="n">
-        <v>6981451</v>
+        <v>6981199</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5097,45 +5097,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890103</v>
+        <v>128890024</v>
       </c>
       <c r="B45" t="n">
-        <v>98632</v>
+        <v>91508</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515126</v>
+        <v>515219</v>
       </c>
       <c r="R45" t="n">
-        <v>6981385</v>
+        <v>6981419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,11 +5170,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5187,44 +5182,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890090</v>
+        <v>128890104</v>
       </c>
       <c r="B46" t="n">
-        <v>80225</v>
+        <v>75192</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5234,10 +5229,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515013</v>
+        <v>515070</v>
       </c>
       <c r="R46" t="n">
-        <v>6981245</v>
+        <v>6981365</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,7 +5269,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5301,10 +5296,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128884114</v>
+        <v>128884117</v>
       </c>
       <c r="B47" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5312,21 +5307,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5336,10 +5331,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515018</v>
+        <v>515013</v>
       </c>
       <c r="R47" t="n">
-        <v>6981240</v>
+        <v>6981204</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5371,7 +5366,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5381,7 +5376,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5408,32 +5403,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890104</v>
+        <v>128890090</v>
       </c>
       <c r="B48" t="n">
-        <v>75188</v>
+        <v>80229</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5438,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981365</v>
+        <v>6981245</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5483,7 +5478,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5510,10 +5505,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128884117</v>
+        <v>128884114</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5521,21 +5516,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5545,10 +5540,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515013</v>
+        <v>515018</v>
       </c>
       <c r="R49" t="n">
-        <v>6981204</v>
+        <v>6981240</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -5580,7 +5575,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5590,7 +5585,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5617,45 +5612,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890024</v>
+        <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>91504</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515219</v>
+        <v>515126</v>
       </c>
       <c r="R50" t="n">
-        <v>6981419</v>
+        <v>6981385</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5690,6 +5685,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5702,12 +5702,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5717,7 +5717,7 @@
         <v>128890034</v>
       </c>
       <c r="B51" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>128890041</v>
       </c>
       <c r="B52" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>128884080</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>128884086</v>
       </c>
       <c r="B54" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>128890025</v>
       </c>
       <c r="B56" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>128884100</v>
       </c>
       <c r="B57" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>128890105</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>128884119</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>128884090</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6841,48 +6841,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128890082</v>
+        <v>128884104</v>
       </c>
       <c r="B62" t="n">
-        <v>79206</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515014</v>
+        <v>515104</v>
       </c>
       <c r="R62" t="n">
-        <v>6981245</v>
+        <v>6981353</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6909,14 +6909,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6931,60 +6936,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884099</v>
+        <v>128890082</v>
       </c>
       <c r="B63" t="n">
-        <v>80225</v>
+        <v>79210</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515158</v>
+        <v>515014</v>
       </c>
       <c r="R63" t="n">
-        <v>6981406</v>
+        <v>6981245</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7011,19 +7016,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7038,22 +7038,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884104</v>
+        <v>128884099</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515104</v>
+        <v>515158</v>
       </c>
       <c r="R64" t="n">
-        <v>6981353</v>
+        <v>6981406</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7160,7 +7160,7 @@
         <v>128884095</v>
       </c>
       <c r="B65" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>128884113</v>
       </c>
       <c r="B66" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>128890027</v>
       </c>
       <c r="B67" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>128890075</v>
       </c>
       <c r="B68" t="n">
-        <v>105680</v>
+        <v>105684</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7585,32 +7585,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890097</v>
+        <v>128890080</v>
       </c>
       <c r="B69" t="n">
-        <v>98632</v>
+        <v>80095</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515060</v>
+        <v>515188</v>
       </c>
       <c r="R69" t="n">
-        <v>6981339</v>
+        <v>6981440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7690,7 +7690,7 @@
         <v>128890032</v>
       </c>
       <c r="B70" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7784,10 +7784,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890080</v>
+        <v>128890077</v>
       </c>
       <c r="B71" t="n">
-        <v>80091</v>
+        <v>75209</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7795,21 +7795,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>388</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515188</v>
+        <v>515057</v>
       </c>
       <c r="R71" t="n">
-        <v>6981440</v>
+        <v>6981333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890077</v>
+        <v>128890097</v>
       </c>
       <c r="B72" t="n">
-        <v>75205</v>
+        <v>98636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515057</v>
+        <v>515060</v>
       </c>
       <c r="R72" t="n">
-        <v>6981333</v>
+        <v>6981339</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,10 +7988,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128890084</v>
+        <v>128884111</v>
       </c>
       <c r="B73" t="n">
-        <v>91800</v>
+        <v>79124</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7999,37 +7999,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>515029</v>
+        <v>515033</v>
       </c>
       <c r="R73" t="n">
-        <v>6981276</v>
+        <v>6981298</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8056,14 +8056,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8078,22 +8083,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128884111</v>
+        <v>128884094</v>
       </c>
       <c r="B74" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8125,10 +8130,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515033</v>
+        <v>515181</v>
       </c>
       <c r="R74" t="n">
-        <v>6981298</v>
+        <v>6981416</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -8160,7 +8165,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8170,7 +8175,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8197,10 +8202,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884094</v>
+        <v>128890084</v>
       </c>
       <c r="B75" t="n">
-        <v>79120</v>
+        <v>91804</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8208,37 +8213,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>515181</v>
+        <v>515029</v>
       </c>
       <c r="R75" t="n">
-        <v>6981416</v>
+        <v>6981276</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8265,19 +8270,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8292,12 +8292,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8307,7 +8307,7 @@
         <v>128890101</v>
       </c>
       <c r="B76" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8406,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890037</v>
+        <v>128890085</v>
       </c>
       <c r="B77" t="n">
-        <v>80225</v>
+        <v>91804</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515026</v>
+        <v>515034</v>
       </c>
       <c r="R77" t="n">
-        <v>6981261</v>
+        <v>6981293</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,6 +8479,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8491,22 +8496,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884102</v>
+        <v>128890037</v>
       </c>
       <c r="B78" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8534,17 +8539,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515111</v>
+        <v>515026</v>
       </c>
       <c r="R78" t="n">
-        <v>6981360</v>
+        <v>6981261</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8571,19 +8576,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8598,22 +8593,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128890085</v>
+        <v>128884102</v>
       </c>
       <c r="B79" t="n">
-        <v>91800</v>
+        <v>80229</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8621,37 +8616,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515034</v>
+        <v>515111</v>
       </c>
       <c r="R79" t="n">
-        <v>6981293</v>
+        <v>6981360</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8678,14 +8673,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,12 +8700,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8715,7 +8715,7 @@
         <v>128890093</v>
       </c>
       <c r="B80" t="n">
-        <v>80092</v>
+        <v>80096</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>128884081</v>
       </c>
       <c r="B81" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>128890087</v>
       </c>
       <c r="B82" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>128884091</v>
       </c>
       <c r="B83" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>128890091</v>
       </c>
       <c r="B84" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>128890038</v>
       </c>
       <c r="B85" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>128890096</v>
       </c>
       <c r="B86" t="n">
-        <v>80185</v>
+        <v>80189</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>128890099</v>
       </c>
       <c r="B87" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884101</v>
+        <v>128884109</v>
       </c>
       <c r="B2" t="n">
         <v>79124</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515135</v>
+        <v>515053</v>
       </c>
       <c r="R2" t="n">
-        <v>6981381</v>
+        <v>6981306</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128890092</v>
+        <v>128884101</v>
       </c>
       <c r="B3" t="n">
-        <v>80265</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515067</v>
+        <v>515135</v>
       </c>
       <c r="R3" t="n">
-        <v>6981353</v>
+        <v>6981381</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +850,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,60 +877,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884097</v>
+        <v>128890092</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515184</v>
+        <v>515067</v>
       </c>
       <c r="R4" t="n">
-        <v>6981392</v>
+        <v>6981353</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,19 +957,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:19</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884109</v>
+        <v>128884097</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515053</v>
+        <v>515184</v>
       </c>
       <c r="R5" t="n">
-        <v>6981306</v>
+        <v>6981392</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1409,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884093</v>
+        <v>128884087</v>
       </c>
       <c r="B9" t="n">
-        <v>105684</v>
+        <v>80229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515174</v>
+        <v>515217</v>
       </c>
       <c r="R9" t="n">
-        <v>6981416</v>
+        <v>6981406</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128884087</v>
+        <v>128890036</v>
       </c>
       <c r="B10" t="n">
         <v>80229</v>
@@ -1547,17 +1547,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515217</v>
+        <v>515018</v>
       </c>
       <c r="R10" t="n">
-        <v>6981406</v>
+        <v>6981217</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,19 +1584,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,60 +1601,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128890036</v>
+        <v>128884093</v>
       </c>
       <c r="B11" t="n">
-        <v>80229</v>
+        <v>105684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515018</v>
+        <v>515174</v>
       </c>
       <c r="R11" t="n">
-        <v>6981217</v>
+        <v>6981416</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,9 +1681,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,12 +1708,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128890028</v>
+        <v>128884105</v>
       </c>
       <c r="B16" t="n">
-        <v>80095</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515039</v>
+        <v>515069</v>
       </c>
       <c r="R16" t="n">
-        <v>6981285</v>
+        <v>6981348</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,40 +2191,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890081</v>
+        <v>128884079</v>
       </c>
       <c r="B17" t="n">
-        <v>80095</v>
+        <v>78101</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,37 +2241,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>388</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515203</v>
+        <v>515240</v>
       </c>
       <c r="R17" t="n">
-        <v>6981449</v>
+        <v>6981445</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2289,14 +2298,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2311,22 +2325,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128884105</v>
+        <v>128890028</v>
       </c>
       <c r="B18" t="n">
-        <v>80229</v>
+        <v>80095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2334,37 +2348,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515069</v>
+        <v>515039</v>
       </c>
       <c r="R18" t="n">
-        <v>6981348</v>
+        <v>6981285</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2391,49 +2405,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128884079</v>
+        <v>128890081</v>
       </c>
       <c r="B19" t="n">
-        <v>78101</v>
+        <v>80095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,37 +2446,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515240</v>
+        <v>515203</v>
       </c>
       <c r="R19" t="n">
-        <v>6981445</v>
+        <v>6981449</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2498,19 +2503,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,22 +2525,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128884110</v>
+        <v>128884084</v>
       </c>
       <c r="B20" t="n">
-        <v>80095</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,21 +2548,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515038</v>
+        <v>515227</v>
       </c>
       <c r="R20" t="n">
-        <v>6981305</v>
+        <v>6981418</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,48 +2843,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128890026</v>
+        <v>128884089</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>80258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515052</v>
+        <v>515218</v>
       </c>
       <c r="R23" t="n">
-        <v>6981331</v>
+        <v>6981412</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2911,14 +2911,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2933,44 +2938,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884089</v>
+        <v>128884107</v>
       </c>
       <c r="B24" t="n">
-        <v>80258</v>
+        <v>80229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2980,10 +2985,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515218</v>
+        <v>515060</v>
       </c>
       <c r="R24" t="n">
-        <v>6981412</v>
+        <v>6981336</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3015,7 +3020,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3025,7 +3030,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3052,10 +3057,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884107</v>
+        <v>128884110</v>
       </c>
       <c r="B25" t="n">
-        <v>80229</v>
+        <v>80095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,21 +3068,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3087,10 +3092,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515060</v>
+        <v>515038</v>
       </c>
       <c r="R25" t="n">
-        <v>6981336</v>
+        <v>6981305</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3132,7 +3137,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3159,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884084</v>
+        <v>128890026</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3170,37 +3175,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515227</v>
+        <v>515052</v>
       </c>
       <c r="R26" t="n">
-        <v>6981418</v>
+        <v>6981331</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3227,19 +3232,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:05</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,12 +3254,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128884108</v>
+        <v>128890094</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>80096</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,37 +3384,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>385</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515059</v>
+        <v>515188</v>
       </c>
       <c r="R28" t="n">
-        <v>6981319</v>
+        <v>6981440</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3441,24 +3441,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>nr 10</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3473,44 +3463,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128890094</v>
+        <v>128890088</v>
       </c>
       <c r="B29" t="n">
-        <v>80096</v>
+        <v>79595</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>385</v>
+        <v>1797</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3510,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515188</v>
+        <v>515103</v>
       </c>
       <c r="R29" t="n">
-        <v>6981440</v>
+        <v>6981364</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3560,7 +3550,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3587,48 +3577,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128890088</v>
+        <v>128884108</v>
       </c>
       <c r="B30" t="n">
-        <v>79595</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1797</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515103</v>
+        <v>515059</v>
       </c>
       <c r="R30" t="n">
-        <v>6981364</v>
+        <v>6981319</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3655,14 +3645,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+          <t>nr 10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,44 +3677,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128890029</v>
+        <v>128890043</v>
       </c>
       <c r="B31" t="n">
-        <v>92210</v>
+        <v>80229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515089</v>
+        <v>515166</v>
       </c>
       <c r="R31" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,32 +3786,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128890043</v>
+        <v>128890029</v>
       </c>
       <c r="B32" t="n">
-        <v>80229</v>
+        <v>92210</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515166</v>
+        <v>515089</v>
       </c>
       <c r="R32" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128890042</v>
+        <v>128890076</v>
       </c>
       <c r="B33" t="n">
-        <v>80229</v>
+        <v>75209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>515180</v>
+        <v>514973</v>
       </c>
       <c r="R33" t="n">
-        <v>6981428</v>
+        <v>6981271</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3956,6 +3956,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3968,22 +3973,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128890076</v>
+        <v>128890042</v>
       </c>
       <c r="B34" t="n">
-        <v>75209</v>
+        <v>80229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3991,34 +3996,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514973</v>
+        <v>515180</v>
       </c>
       <c r="R34" t="n">
-        <v>6981271</v>
+        <v>6981428</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,11 +4058,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4070,12 +4070,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128884098</v>
+        <v>128884083</v>
       </c>
       <c r="B36" t="n">
-        <v>79380</v>
+        <v>91508</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>515158</v>
+        <v>515231</v>
       </c>
       <c r="R36" t="n">
-        <v>6981406</v>
+        <v>6981417</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4286,32 +4286,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128884092</v>
+        <v>128884098</v>
       </c>
       <c r="B37" t="n">
-        <v>80229</v>
+        <v>79380</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>515180</v>
+        <v>515158</v>
       </c>
       <c r="R37" t="n">
-        <v>6981435</v>
+        <v>6981406</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4393,10 +4393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128884083</v>
+        <v>128884092</v>
       </c>
       <c r="B38" t="n">
-        <v>91508</v>
+        <v>80229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>515231</v>
+        <v>515180</v>
       </c>
       <c r="R38" t="n">
-        <v>6981417</v>
+        <v>6981435</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4699,48 +4699,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128884082</v>
+        <v>128890031</v>
       </c>
       <c r="B41" t="n">
-        <v>91804</v>
+        <v>80133</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515231</v>
+        <v>515039</v>
       </c>
       <c r="R41" t="n">
-        <v>6981417</v>
+        <v>6981314</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,19 +4767,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4794,22 +4784,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128890031</v>
+        <v>128890045</v>
       </c>
       <c r="B42" t="n">
-        <v>80133</v>
+        <v>80189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4817,21 +4807,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4841,10 +4831,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515039</v>
+        <v>515170</v>
       </c>
       <c r="R42" t="n">
-        <v>6981314</v>
+        <v>6981451</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,48 +4893,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128890045</v>
+        <v>128884082</v>
       </c>
       <c r="B43" t="n">
-        <v>80189</v>
+        <v>91804</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515170</v>
+        <v>515231</v>
       </c>
       <c r="R43" t="n">
-        <v>6981451</v>
+        <v>6981417</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4971,9 +4961,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4988,12 +4988,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890024</v>
+        <v>128884114</v>
       </c>
       <c r="B45" t="n">
-        <v>91508</v>
+        <v>80229</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5108,37 +5108,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515219</v>
+        <v>515018</v>
       </c>
       <c r="R45" t="n">
-        <v>6981419</v>
+        <v>6981240</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5165,9 +5165,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5182,12 +5192,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5403,10 +5413,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890090</v>
+        <v>128890024</v>
       </c>
       <c r="B48" t="n">
-        <v>80229</v>
+        <v>91508</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5414,34 +5424,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515013</v>
+        <v>515219</v>
       </c>
       <c r="R48" t="n">
-        <v>6981245</v>
+        <v>6981419</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5476,11 +5486,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5493,60 +5498,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128884114</v>
+        <v>128890103</v>
       </c>
       <c r="B49" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515018</v>
+        <v>515126</v>
       </c>
       <c r="R49" t="n">
-        <v>6981240</v>
+        <v>6981385</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5573,19 +5578,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5600,44 +5600,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890103</v>
+        <v>128890090</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515126</v>
+        <v>515013</v>
       </c>
       <c r="R50" t="n">
-        <v>6981385</v>
+        <v>6981245</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5714,45 +5714,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890034</v>
+        <v>128890098</v>
       </c>
       <c r="B51" t="n">
-        <v>91804</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515231</v>
+        <v>515031</v>
       </c>
       <c r="R51" t="n">
-        <v>6981432</v>
+        <v>6981292</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5787,6 +5787,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5799,60 +5804,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890041</v>
+        <v>128884086</v>
       </c>
       <c r="B52" t="n">
-        <v>80229</v>
+        <v>58090</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515196</v>
+        <v>515225</v>
       </c>
       <c r="R52" t="n">
-        <v>6981428</v>
+        <v>6981406</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5879,9 +5884,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5896,12 +5911,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6015,48 +6030,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884086</v>
+        <v>128890034</v>
       </c>
       <c r="B54" t="n">
-        <v>58090</v>
+        <v>91804</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515225</v>
+        <v>515231</v>
       </c>
       <c r="R54" t="n">
-        <v>6981406</v>
+        <v>6981432</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6083,19 +6098,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6110,57 +6115,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128890098</v>
+        <v>128890041</v>
       </c>
       <c r="B55" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515031</v>
+        <v>515196</v>
       </c>
       <c r="R55" t="n">
-        <v>6981292</v>
+        <v>6981428</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6195,11 +6200,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6212,22 +6212,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128890025</v>
+        <v>128890105</v>
       </c>
       <c r="B56" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6235,34 +6235,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515214</v>
+        <v>515054</v>
       </c>
       <c r="R56" t="n">
-        <v>6981426</v>
+        <v>6981308</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6297,6 +6297,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6309,44 +6314,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884100</v>
+        <v>128884119</v>
       </c>
       <c r="B57" t="n">
-        <v>80258</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6356,10 +6361,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515158</v>
+        <v>515196</v>
       </c>
       <c r="R57" t="n">
-        <v>6981405</v>
+        <v>6981382</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6391,7 +6396,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6401,7 +6406,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6428,7 +6433,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128890105</v>
+        <v>128884090</v>
       </c>
       <c r="B58" t="n">
         <v>79124</v>
@@ -6459,17 +6464,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515054</v>
+        <v>515210</v>
       </c>
       <c r="R58" t="n">
-        <v>6981308</v>
+        <v>6981412</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6496,14 +6501,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6518,44 +6528,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884119</v>
+        <v>128884100</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>80258</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6565,10 +6575,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515196</v>
+        <v>515158</v>
       </c>
       <c r="R59" t="n">
-        <v>6981382</v>
+        <v>6981405</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6600,7 +6610,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6610,7 +6620,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6637,10 +6647,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884090</v>
+        <v>128890025</v>
       </c>
       <c r="B60" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6648,37 +6658,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515210</v>
+        <v>515214</v>
       </c>
       <c r="R60" t="n">
-        <v>6981412</v>
+        <v>6981426</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6705,19 +6715,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6732,22 +6732,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128890023</v>
+        <v>128884104</v>
       </c>
       <c r="B61" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6755,37 +6755,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515081</v>
+        <v>515104</v>
       </c>
       <c r="R61" t="n">
-        <v>6981324</v>
+        <v>6981353</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,9 +6812,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,19 +6839,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884104</v>
+        <v>128884095</v>
       </c>
       <c r="B62" t="n">
         <v>79124</v>
@@ -6876,10 +6886,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515104</v>
+        <v>515183</v>
       </c>
       <c r="R62" t="n">
-        <v>6981353</v>
+        <v>6981391</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -6911,7 +6921,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6921,7 +6931,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6948,48 +6963,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128890082</v>
+        <v>128884113</v>
       </c>
       <c r="B63" t="n">
-        <v>79210</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515014</v>
+        <v>515021</v>
       </c>
       <c r="R63" t="n">
-        <v>6981245</v>
+        <v>6981285</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7016,14 +7031,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt på lodyta</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7038,60 +7063,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884099</v>
+        <v>128890082</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>79210</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515158</v>
+        <v>515014</v>
       </c>
       <c r="R64" t="n">
-        <v>6981406</v>
+        <v>6981245</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7118,19 +7143,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7145,22 +7165,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884095</v>
+        <v>128884099</v>
       </c>
       <c r="B65" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7168,21 +7188,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7192,10 +7212,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515183</v>
+        <v>515158</v>
       </c>
       <c r="R65" t="n">
-        <v>6981391</v>
+        <v>6981406</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7227,7 +7247,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7237,12 +7257,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7269,10 +7284,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884113</v>
+        <v>128890023</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7280,37 +7295,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515021</v>
+        <v>515081</v>
       </c>
       <c r="R66" t="n">
-        <v>6981285</v>
+        <v>6981324</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7337,24 +7352,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>nr 500</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7369,12 +7369,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7483,32 +7483,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890075</v>
+        <v>128890077</v>
       </c>
       <c r="B68" t="n">
-        <v>105684</v>
+        <v>75209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515124</v>
+        <v>515057</v>
       </c>
       <c r="R68" t="n">
-        <v>6981387</v>
+        <v>6981333</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7784,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890077</v>
+        <v>128890097</v>
       </c>
       <c r="B71" t="n">
-        <v>75209</v>
+        <v>98636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515057</v>
+        <v>515060</v>
       </c>
       <c r="R71" t="n">
-        <v>6981333</v>
+        <v>6981339</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890097</v>
+        <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>98636</v>
+        <v>105684</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515060</v>
+        <v>515124</v>
       </c>
       <c r="R72" t="n">
-        <v>6981339</v>
+        <v>6981387</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,10 +7988,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884111</v>
+        <v>128890084</v>
       </c>
       <c r="B73" t="n">
-        <v>79124</v>
+        <v>91804</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7999,37 +7999,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>515033</v>
+        <v>515029</v>
       </c>
       <c r="R73" t="n">
-        <v>6981298</v>
+        <v>6981276</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8056,19 +8056,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8083,60 +8078,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128884094</v>
+        <v>128890101</v>
       </c>
       <c r="B74" t="n">
-        <v>79124</v>
+        <v>98636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515181</v>
+        <v>515108</v>
       </c>
       <c r="R74" t="n">
-        <v>6981416</v>
+        <v>6981372</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8163,19 +8158,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8190,22 +8180,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128890084</v>
+        <v>128884111</v>
       </c>
       <c r="B75" t="n">
-        <v>91804</v>
+        <v>79124</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8213,37 +8203,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>515029</v>
+        <v>515033</v>
       </c>
       <c r="R75" t="n">
-        <v>6981276</v>
+        <v>6981298</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8270,14 +8260,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8292,60 +8287,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128890101</v>
+        <v>128884094</v>
       </c>
       <c r="B76" t="n">
-        <v>98636</v>
+        <v>79124</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515108</v>
+        <v>515181</v>
       </c>
       <c r="R76" t="n">
-        <v>6981372</v>
+        <v>6981416</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8372,14 +8367,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>16 plantor på marken i gammal granskog</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,12 +8394,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8712,32 +8712,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890093</v>
+        <v>128890087</v>
       </c>
       <c r="B80" t="n">
-        <v>80096</v>
+        <v>80257</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>385</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515053</v>
+        <v>515014</v>
       </c>
       <c r="R80" t="n">
-        <v>6981314</v>
+        <v>6981245</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,10 +8814,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884081</v>
+        <v>128884091</v>
       </c>
       <c r="B81" t="n">
-        <v>91508</v>
+        <v>80229</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8825,21 +8825,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515230</v>
+        <v>515199</v>
       </c>
       <c r="R81" t="n">
-        <v>6981431</v>
+        <v>6981419</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8921,32 +8921,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128890087</v>
+        <v>128890091</v>
       </c>
       <c r="B82" t="n">
-        <v>80257</v>
+        <v>80229</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8956,10 +8956,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515014</v>
+        <v>515069</v>
       </c>
       <c r="R82" t="n">
-        <v>6981245</v>
+        <v>6981349</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På lodyta</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9023,7 +9023,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128884091</v>
+        <v>128890038</v>
       </c>
       <c r="B83" t="n">
         <v>80229</v>
@@ -9054,17 +9054,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515199</v>
+        <v>515041</v>
       </c>
       <c r="R83" t="n">
-        <v>6981419</v>
+        <v>6981296</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9091,19 +9091,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9118,22 +9108,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890091</v>
+        <v>128884081</v>
       </c>
       <c r="B84" t="n">
-        <v>80229</v>
+        <v>91508</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9141,37 +9131,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515069</v>
+        <v>515230</v>
       </c>
       <c r="R84" t="n">
-        <v>6981349</v>
+        <v>6981431</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9198,14 +9188,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9220,57 +9215,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890038</v>
+        <v>128890099</v>
       </c>
       <c r="B85" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515041</v>
+        <v>515054</v>
       </c>
       <c r="R85" t="n">
-        <v>6981296</v>
+        <v>6981308</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9305,6 +9300,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På marken 13 plantor i lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9317,44 +9317,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890096</v>
+        <v>128890093</v>
       </c>
       <c r="B86" t="n">
-        <v>80189</v>
+        <v>80096</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>385</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515014</v>
+        <v>515053</v>
       </c>
       <c r="R86" t="n">
-        <v>6981245</v>
+        <v>6981314</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9431,32 +9431,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890099</v>
+        <v>128890096</v>
       </c>
       <c r="B87" t="n">
-        <v>98636</v>
+        <v>80189</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515054</v>
+        <v>515014</v>
       </c>
       <c r="R87" t="n">
-        <v>6981308</v>
+        <v>6981245</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884109</v>
+        <v>128890092</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>80265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515053</v>
+        <v>515067</v>
       </c>
       <c r="R2" t="n">
-        <v>6981306</v>
+        <v>6981353</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:44</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884101</v>
+        <v>128884097</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515135</v>
+        <v>515184</v>
       </c>
       <c r="R3" t="n">
-        <v>6981381</v>
+        <v>6981392</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,48 +884,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128890092</v>
+        <v>128884101</v>
       </c>
       <c r="B4" t="n">
-        <v>80265</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515067</v>
+        <v>515135</v>
       </c>
       <c r="R4" t="n">
-        <v>6981353</v>
+        <v>6981381</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,14 +952,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884097</v>
+        <v>128884109</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515184</v>
+        <v>515053</v>
       </c>
       <c r="R5" t="n">
-        <v>6981392</v>
+        <v>6981306</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128890102</v>
+        <v>128890079</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>91473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515229</v>
+        <v>515071</v>
       </c>
       <c r="R7" t="n">
-        <v>6981403</v>
+        <v>6981351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>50 plantor i i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128890079</v>
+        <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>91473</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515071</v>
+        <v>515229</v>
       </c>
       <c r="R8" t="n">
-        <v>6981351</v>
+        <v>6981403</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>50 plantor i i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1720,48 +1720,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890033</v>
+        <v>128884116</v>
       </c>
       <c r="B12" t="n">
-        <v>75019</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515018</v>
+        <v>515030</v>
       </c>
       <c r="R12" t="n">
-        <v>6981215</v>
+        <v>6981199</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,9 +1788,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,60 +1815,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128884116</v>
+        <v>128890033</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>75019</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515030</v>
+        <v>515018</v>
       </c>
       <c r="R13" t="n">
-        <v>6981199</v>
+        <v>6981215</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,19 +1895,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,12 +1912,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128884079</v>
+        <v>128890028</v>
       </c>
       <c r="B17" t="n">
-        <v>78101</v>
+        <v>80095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,37 +2241,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>388</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515240</v>
+        <v>515039</v>
       </c>
       <c r="R17" t="n">
-        <v>6981445</v>
+        <v>6981285</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2298,46 +2298,37 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128890028</v>
+        <v>128890081</v>
       </c>
       <c r="B18" t="n">
         <v>80095</v>
@@ -2368,14 +2359,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515039</v>
+        <v>515203</v>
       </c>
       <c r="R18" t="n">
-        <v>6981285</v>
+        <v>6981449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,35 +2401,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128890081</v>
+        <v>128884079</v>
       </c>
       <c r="B19" t="n">
-        <v>80095</v>
+        <v>78101</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,37 +2441,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>388</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515203</v>
+        <v>515240</v>
       </c>
       <c r="R19" t="n">
-        <v>6981449</v>
+        <v>6981445</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,14 +2498,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,22 +2525,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128884084</v>
+        <v>128884110</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>80095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,21 +2548,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515227</v>
+        <v>515038</v>
       </c>
       <c r="R20" t="n">
-        <v>6981418</v>
+        <v>6981305</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2644,10 +2644,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128890095</v>
+        <v>128884084</v>
       </c>
       <c r="B21" t="n">
-        <v>92308</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2014</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515145</v>
+        <v>515227</v>
       </c>
       <c r="R21" t="n">
-        <v>6981384</v>
+        <v>6981418</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,14 +2712,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2734,22 +2739,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128890030</v>
+        <v>128890095</v>
       </c>
       <c r="B22" t="n">
-        <v>80230</v>
+        <v>92308</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2757,34 +2762,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>2014</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515032</v>
+        <v>515145</v>
       </c>
       <c r="R22" t="n">
-        <v>6981265</v>
+        <v>6981384</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,6 +2824,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2831,60 +2841,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128884089</v>
+        <v>128890030</v>
       </c>
       <c r="B23" t="n">
-        <v>80258</v>
+        <v>80230</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515218</v>
+        <v>515032</v>
       </c>
       <c r="R23" t="n">
-        <v>6981412</v>
+        <v>6981265</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2911,19 +2921,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2938,22 +2938,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884107</v>
+        <v>128890026</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,37 +2961,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515060</v>
+        <v>515052</v>
       </c>
       <c r="R24" t="n">
-        <v>6981336</v>
+        <v>6981331</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,19 +3018,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:40</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3045,44 +3040,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884110</v>
+        <v>128884089</v>
       </c>
       <c r="B25" t="n">
-        <v>80095</v>
+        <v>80258</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>388</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3092,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515038</v>
+        <v>515218</v>
       </c>
       <c r="R25" t="n">
-        <v>6981305</v>
+        <v>6981412</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3127,7 +3122,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3137,7 +3132,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3164,10 +3159,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128890026</v>
+        <v>128884107</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,37 +3170,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515052</v>
+        <v>515060</v>
       </c>
       <c r="R26" t="n">
-        <v>6981331</v>
+        <v>6981336</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3232,14 +3227,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,44 +3254,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128884103</v>
+        <v>128884108</v>
       </c>
       <c r="B27" t="n">
-        <v>80258</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515108</v>
+        <v>515059</v>
       </c>
       <c r="R27" t="n">
-        <v>6981358</v>
+        <v>6981319</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3346,7 +3346,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>nr 10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3373,32 +3378,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128890094</v>
+        <v>128890088</v>
       </c>
       <c r="B28" t="n">
-        <v>80096</v>
+        <v>79595</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>385</v>
+        <v>1797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515188</v>
+        <v>515103</v>
       </c>
       <c r="R28" t="n">
-        <v>6981440</v>
+        <v>6981364</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,7 +3453,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3475,48 +3480,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128890088</v>
+        <v>128884103</v>
       </c>
       <c r="B29" t="n">
-        <v>79595</v>
+        <v>80258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1797</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515103</v>
+        <v>515108</v>
       </c>
       <c r="R29" t="n">
-        <v>6981364</v>
+        <v>6981358</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3543,14 +3548,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3565,22 +3575,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128884108</v>
+        <v>128890094</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>80096</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3588,37 +3598,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>385</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515059</v>
+        <v>515188</v>
       </c>
       <c r="R30" t="n">
-        <v>6981319</v>
+        <v>6981440</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3645,24 +3655,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>nr 10</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,44 +3677,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128890043</v>
+        <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>80229</v>
+        <v>92210</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515166</v>
+        <v>515089</v>
       </c>
       <c r="R31" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,32 +3786,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128890029</v>
+        <v>128890043</v>
       </c>
       <c r="B32" t="n">
-        <v>92210</v>
+        <v>80229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515089</v>
+        <v>515166</v>
       </c>
       <c r="R32" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128890076</v>
+        <v>128890042</v>
       </c>
       <c r="B33" t="n">
-        <v>75209</v>
+        <v>80229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514973</v>
+        <v>515180</v>
       </c>
       <c r="R33" t="n">
-        <v>6981271</v>
+        <v>6981428</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3956,11 +3956,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3973,22 +3968,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128890042</v>
+        <v>128890076</v>
       </c>
       <c r="B34" t="n">
-        <v>80229</v>
+        <v>75209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,34 +3991,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>515180</v>
+        <v>514973</v>
       </c>
       <c r="R34" t="n">
-        <v>6981428</v>
+        <v>6981271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4058,6 +4053,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4070,12 +4070,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128890031</v>
+        <v>128890045</v>
       </c>
       <c r="B41" t="n">
-        <v>80133</v>
+        <v>80189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,21 +4710,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515039</v>
+        <v>515170</v>
       </c>
       <c r="R41" t="n">
-        <v>6981314</v>
+        <v>6981451</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4796,10 +4796,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128890045</v>
+        <v>128890031</v>
       </c>
       <c r="B42" t="n">
-        <v>80189</v>
+        <v>80133</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4807,21 +4807,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515170</v>
+        <v>515039</v>
       </c>
       <c r="R42" t="n">
-        <v>6981451</v>
+        <v>6981314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4893,10 +4893,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128884082</v>
+        <v>128890022</v>
       </c>
       <c r="B43" t="n">
-        <v>91804</v>
+        <v>96882</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4904,37 +4904,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515231</v>
+        <v>515029</v>
       </c>
       <c r="R43" t="n">
-        <v>6981417</v>
+        <v>6981199</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4961,19 +4961,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4988,22 +4978,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128890022</v>
+        <v>128884082</v>
       </c>
       <c r="B44" t="n">
-        <v>96882</v>
+        <v>91804</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5011,37 +5001,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515029</v>
+        <v>515231</v>
       </c>
       <c r="R44" t="n">
-        <v>6981199</v>
+        <v>6981417</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5068,9 +5058,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5085,60 +5085,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128884114</v>
+        <v>128890104</v>
       </c>
       <c r="B45" t="n">
-        <v>80229</v>
+        <v>75192</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515018</v>
+        <v>515070</v>
       </c>
       <c r="R45" t="n">
-        <v>6981240</v>
+        <v>6981365</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5165,19 +5165,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5192,44 +5187,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890104</v>
+        <v>128890090</v>
       </c>
       <c r="B46" t="n">
-        <v>75192</v>
+        <v>80229</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5239,10 +5234,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R46" t="n">
-        <v>6981365</v>
+        <v>6981245</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5279,7 +5274,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5306,10 +5301,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128884117</v>
+        <v>128884114</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5317,21 +5312,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5341,10 +5336,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515013</v>
+        <v>515018</v>
       </c>
       <c r="R47" t="n">
-        <v>6981204</v>
+        <v>6981240</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5376,7 +5371,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5386,7 +5381,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5413,10 +5408,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890024</v>
+        <v>128884117</v>
       </c>
       <c r="B48" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5424,37 +5419,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515219</v>
+        <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981419</v>
+        <v>6981204</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5481,9 +5476,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5498,57 +5503,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890103</v>
+        <v>128890024</v>
       </c>
       <c r="B49" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515126</v>
+        <v>515219</v>
       </c>
       <c r="R49" t="n">
-        <v>6981385</v>
+        <v>6981419</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5583,11 +5588,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5600,44 +5600,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890090</v>
+        <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515013</v>
+        <v>515126</v>
       </c>
       <c r="R50" t="n">
-        <v>6981245</v>
+        <v>6981385</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5714,45 +5714,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890098</v>
+        <v>128890041</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515031</v>
+        <v>515196</v>
       </c>
       <c r="R51" t="n">
-        <v>6981292</v>
+        <v>6981428</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5787,11 +5787,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5804,44 +5799,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884086</v>
+        <v>128884080</v>
       </c>
       <c r="B52" t="n">
-        <v>58090</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5851,10 +5846,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515225</v>
+        <v>515239</v>
       </c>
       <c r="R52" t="n">
-        <v>6981406</v>
+        <v>6981443</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -5886,7 +5881,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5896,7 +5891,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5923,10 +5918,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884080</v>
+        <v>128890034</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>91804</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5934,37 +5929,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515239</v>
+        <v>515231</v>
       </c>
       <c r="R53" t="n">
-        <v>6981443</v>
+        <v>6981432</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5991,19 +5986,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6018,60 +6003,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128890034</v>
+        <v>128884086</v>
       </c>
       <c r="B54" t="n">
-        <v>91804</v>
+        <v>58090</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515231</v>
+        <v>515225</v>
       </c>
       <c r="R54" t="n">
-        <v>6981432</v>
+        <v>6981406</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6098,9 +6083,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6115,57 +6110,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128890041</v>
+        <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515196</v>
+        <v>515031</v>
       </c>
       <c r="R55" t="n">
-        <v>6981428</v>
+        <v>6981292</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6200,6 +6195,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6212,19 +6212,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128890105</v>
+        <v>128884090</v>
       </c>
       <c r="B56" t="n">
         <v>79124</v>
@@ -6255,17 +6255,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515054</v>
+        <v>515210</v>
       </c>
       <c r="R56" t="n">
-        <v>6981308</v>
+        <v>6981412</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6292,14 +6292,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6314,12 +6319,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6433,7 +6438,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884090</v>
+        <v>128890105</v>
       </c>
       <c r="B58" t="n">
         <v>79124</v>
@@ -6464,17 +6469,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515210</v>
+        <v>515054</v>
       </c>
       <c r="R58" t="n">
-        <v>6981412</v>
+        <v>6981308</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6501,19 +6506,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:09</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6528,60 +6528,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884100</v>
+        <v>128890025</v>
       </c>
       <c r="B59" t="n">
-        <v>80258</v>
+        <v>91508</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515158</v>
+        <v>515214</v>
       </c>
       <c r="R59" t="n">
-        <v>6981405</v>
+        <v>6981426</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6608,19 +6608,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6635,60 +6625,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128890025</v>
+        <v>128884100</v>
       </c>
       <c r="B60" t="n">
-        <v>91508</v>
+        <v>80258</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515214</v>
+        <v>515158</v>
       </c>
       <c r="R60" t="n">
-        <v>6981426</v>
+        <v>6981405</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6715,9 +6705,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6732,60 +6732,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884104</v>
+        <v>128890082</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79210</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515104</v>
+        <v>515014</v>
       </c>
       <c r="R61" t="n">
-        <v>6981353</v>
+        <v>6981245</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,19 +6812,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6839,22 +6834,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884095</v>
+        <v>128884099</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6862,21 +6857,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6886,10 +6881,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515183</v>
+        <v>515158</v>
       </c>
       <c r="R62" t="n">
-        <v>6981391</v>
+        <v>6981406</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -6921,7 +6916,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6931,12 +6926,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6963,10 +6953,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884113</v>
+        <v>128890027</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6974,37 +6964,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515021</v>
+        <v>515073</v>
       </c>
       <c r="R63" t="n">
-        <v>6981285</v>
+        <v>6981343</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7031,24 +7021,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7063,60 +7043,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128890082</v>
+        <v>128884095</v>
       </c>
       <c r="B64" t="n">
-        <v>79210</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515014</v>
+        <v>515183</v>
       </c>
       <c r="R64" t="n">
-        <v>6981245</v>
+        <v>6981391</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7143,14 +7123,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rikligt på lodyta</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7165,22 +7155,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884099</v>
+        <v>128884104</v>
       </c>
       <c r="B65" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7188,21 +7178,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7212,10 +7202,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515158</v>
+        <v>515104</v>
       </c>
       <c r="R65" t="n">
-        <v>6981406</v>
+        <v>6981353</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7247,7 +7237,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7257,7 +7247,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7284,10 +7274,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128890023</v>
+        <v>128884113</v>
       </c>
       <c r="B66" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7295,37 +7285,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515081</v>
+        <v>515021</v>
       </c>
       <c r="R66" t="n">
-        <v>6981324</v>
+        <v>6981285</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7352,9 +7342,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7369,22 +7374,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128890027</v>
+        <v>128890023</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>91508</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7392,21 +7397,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7416,10 +7421,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515073</v>
+        <v>515081</v>
       </c>
       <c r="R67" t="n">
-        <v>6981343</v>
+        <v>6981324</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7452,11 +7457,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7585,32 +7585,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890080</v>
+        <v>128890097</v>
       </c>
       <c r="B69" t="n">
-        <v>80095</v>
+        <v>98636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515188</v>
+        <v>515060</v>
       </c>
       <c r="R69" t="n">
-        <v>6981440</v>
+        <v>6981339</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7687,45 +7687,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890032</v>
+        <v>128890075</v>
       </c>
       <c r="B70" t="n">
-        <v>91962</v>
+        <v>105684</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>221725</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515210</v>
+        <v>515124</v>
       </c>
       <c r="R70" t="n">
-        <v>6981426</v>
+        <v>6981387</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7760,6 +7760,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På marken i gammal gransumpskog</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7772,44 +7777,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890097</v>
+        <v>128890080</v>
       </c>
       <c r="B71" t="n">
-        <v>98636</v>
+        <v>80095</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7824,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515060</v>
+        <v>515188</v>
       </c>
       <c r="R71" t="n">
-        <v>6981339</v>
+        <v>6981440</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7864,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,45 +7891,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890075</v>
+        <v>128890032</v>
       </c>
       <c r="B72" t="n">
-        <v>105684</v>
+        <v>91962</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515124</v>
+        <v>515210</v>
       </c>
       <c r="R72" t="n">
-        <v>6981387</v>
+        <v>6981426</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7959,11 +7964,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På marken i gammal gransumpskog</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7976,12 +7976,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8090,48 +8090,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128890101</v>
+        <v>128884094</v>
       </c>
       <c r="B74" t="n">
-        <v>98636</v>
+        <v>79124</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515108</v>
+        <v>515181</v>
       </c>
       <c r="R74" t="n">
-        <v>6981372</v>
+        <v>6981416</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8158,14 +8158,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>16 plantor på marken i gammal granskog</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8180,12 +8185,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8299,48 +8304,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884094</v>
+        <v>128890101</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>98636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515181</v>
+        <v>515108</v>
       </c>
       <c r="R76" t="n">
-        <v>6981416</v>
+        <v>6981372</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8367,19 +8372,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,22 +8394,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890085</v>
+        <v>128890037</v>
       </c>
       <c r="B77" t="n">
-        <v>91804</v>
+        <v>80229</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515034</v>
+        <v>515026</v>
       </c>
       <c r="R77" t="n">
-        <v>6981293</v>
+        <v>6981261</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,11 +8479,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8496,19 +8491,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128890037</v>
+        <v>128884102</v>
       </c>
       <c r="B78" t="n">
         <v>80229</v>
@@ -8539,17 +8534,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515026</v>
+        <v>515111</v>
       </c>
       <c r="R78" t="n">
-        <v>6981261</v>
+        <v>6981360</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8576,9 +8571,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8593,22 +8598,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884102</v>
+        <v>128890085</v>
       </c>
       <c r="B79" t="n">
-        <v>80229</v>
+        <v>91804</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8616,37 +8621,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515111</v>
+        <v>515034</v>
       </c>
       <c r="R79" t="n">
-        <v>6981360</v>
+        <v>6981293</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8673,19 +8678,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,44 +8700,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890087</v>
+        <v>128890091</v>
       </c>
       <c r="B80" t="n">
-        <v>80257</v>
+        <v>80229</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515014</v>
+        <v>515069</v>
       </c>
       <c r="R80" t="n">
-        <v>6981245</v>
+        <v>6981349</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På lodyta</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,48 +8814,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884091</v>
+        <v>128890087</v>
       </c>
       <c r="B81" t="n">
-        <v>80229</v>
+        <v>80257</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515199</v>
+        <v>515014</v>
       </c>
       <c r="R81" t="n">
-        <v>6981419</v>
+        <v>6981245</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8882,19 +8882,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8909,19 +8904,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128890091</v>
+        <v>128884091</v>
       </c>
       <c r="B82" t="n">
         <v>80229</v>
@@ -8952,17 +8947,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515069</v>
+        <v>515199</v>
       </c>
       <c r="R82" t="n">
-        <v>6981349</v>
+        <v>6981419</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8989,14 +8984,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9011,12 +9011,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9120,48 +9120,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884081</v>
+        <v>128890093</v>
       </c>
       <c r="B84" t="n">
-        <v>91508</v>
+        <v>80096</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>385</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515230</v>
+        <v>515053</v>
       </c>
       <c r="R84" t="n">
-        <v>6981431</v>
+        <v>6981314</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9188,19 +9188,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9215,60 +9210,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890099</v>
+        <v>128884081</v>
       </c>
       <c r="B85" t="n">
-        <v>98636</v>
+        <v>91508</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515054</v>
+        <v>515230</v>
       </c>
       <c r="R85" t="n">
-        <v>6981308</v>
+        <v>6981431</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9295,14 +9290,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9317,22 +9317,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890093</v>
+        <v>128890099</v>
       </c>
       <c r="B86" t="n">
-        <v>80096</v>
+        <v>98636</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9340,21 +9340,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>385</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515053</v>
+        <v>515054</v>
       </c>
       <c r="R86" t="n">
-        <v>6981314</v>
+        <v>6981308</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128890092</v>
+        <v>128884115</v>
       </c>
       <c r="B2" t="n">
-        <v>80265</v>
+        <v>80094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515067</v>
+        <v>515019</v>
       </c>
       <c r="R2" t="n">
-        <v>6981353</v>
+        <v>6981238</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +743,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884097</v>
+        <v>128884109</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515184</v>
+        <v>515053</v>
       </c>
       <c r="R3" t="n">
-        <v>6981392</v>
+        <v>6981306</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +892,7 @@
         <v>128884101</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,48 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884109</v>
+        <v>128890092</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>80170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515053</v>
+        <v>515067</v>
       </c>
       <c r="R5" t="n">
-        <v>6981306</v>
+        <v>6981353</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,19 +1064,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:44</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,44 +1086,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128884115</v>
+        <v>128884097</v>
       </c>
       <c r="B6" t="n">
-        <v>80189</v>
+        <v>80134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515019</v>
+        <v>515184</v>
       </c>
       <c r="R6" t="n">
-        <v>6981238</v>
+        <v>6981392</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128890079</v>
       </c>
       <c r="B7" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>128884087</v>
       </c>
       <c r="B9" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>128890036</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128884093</v>
       </c>
       <c r="B11" t="n">
-        <v>105684</v>
+        <v>105691</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,48 +1720,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128884116</v>
+        <v>128890033</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>75022</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515030</v>
+        <v>515018</v>
       </c>
       <c r="R12" t="n">
-        <v>6981199</v>
+        <v>6981215</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,19 +1788,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,60 +1805,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890033</v>
+        <v>128884116</v>
       </c>
       <c r="B13" t="n">
-        <v>75019</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515018</v>
+        <v>515030</v>
       </c>
       <c r="R13" t="n">
-        <v>6981215</v>
+        <v>6981199</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1895,9 +1885,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,57 +1912,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128890039</v>
+        <v>128890100</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515123</v>
+        <v>515060</v>
       </c>
       <c r="R14" t="n">
-        <v>6981380</v>
+        <v>6981326</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,6 +1997,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2009,57 +2014,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128890100</v>
+        <v>128890039</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515060</v>
+        <v>515123</v>
       </c>
       <c r="R15" t="n">
-        <v>6981326</v>
+        <v>6981380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,11 +2099,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2111,22 +2111,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128884105</v>
+        <v>128890028</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>80000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515069</v>
+        <v>515039</v>
       </c>
       <c r="R16" t="n">
-        <v>6981348</v>
+        <v>6981285</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,49 +2191,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890028</v>
+        <v>128890081</v>
       </c>
       <c r="B17" t="n">
-        <v>80095</v>
+        <v>80000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,14 +2252,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515039</v>
+        <v>515203</v>
       </c>
       <c r="R17" t="n">
-        <v>6981285</v>
+        <v>6981449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2303,35 +2294,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128890081</v>
+        <v>128884105</v>
       </c>
       <c r="B18" t="n">
-        <v>80095</v>
+        <v>80134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,37 +2334,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515203</v>
+        <v>515069</v>
       </c>
       <c r="R18" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2396,14 +2391,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,12 +2418,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
         <v>128884079</v>
       </c>
       <c r="B19" t="n">
-        <v>78101</v>
+        <v>78042</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>128884110</v>
       </c>
       <c r="B20" t="n">
-        <v>80095</v>
+        <v>80000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128884084</v>
+        <v>128890095</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>92313</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515227</v>
+        <v>515145</v>
       </c>
       <c r="R21" t="n">
-        <v>6981418</v>
+        <v>6981384</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,19 +2712,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:05</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2739,22 +2734,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128890095</v>
+        <v>128890030</v>
       </c>
       <c r="B22" t="n">
-        <v>92308</v>
+        <v>80135</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,34 +2757,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2014</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515145</v>
+        <v>515032</v>
       </c>
       <c r="R22" t="n">
-        <v>6981384</v>
+        <v>6981265</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2824,11 +2819,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2841,22 +2831,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128890030</v>
+        <v>128884084</v>
       </c>
       <c r="B23" t="n">
-        <v>80230</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2864,37 +2854,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515032</v>
+        <v>515227</v>
       </c>
       <c r="R23" t="n">
-        <v>6981265</v>
+        <v>6981418</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2921,9 +2911,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2938,22 +2938,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128890026</v>
+        <v>128884107</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,37 +2961,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515052</v>
+        <v>515060</v>
       </c>
       <c r="R24" t="n">
-        <v>6981331</v>
+        <v>6981336</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,14 +3018,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3040,12 +3045,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3055,7 +3060,7 @@
         <v>128884089</v>
       </c>
       <c r="B25" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3159,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884107</v>
+        <v>128890026</v>
       </c>
       <c r="B26" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3170,37 +3175,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515060</v>
+        <v>515052</v>
       </c>
       <c r="R26" t="n">
-        <v>6981336</v>
+        <v>6981331</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3227,19 +3232,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:40</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,12 +3254,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3269,7 +3269,7 @@
         <v>128884108</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,32 +3378,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128890088</v>
+        <v>128890094</v>
       </c>
       <c r="B28" t="n">
-        <v>79595</v>
+        <v>80001</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1797</v>
+        <v>385</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515103</v>
+        <v>515188</v>
       </c>
       <c r="R28" t="n">
-        <v>6981364</v>
+        <v>6981440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3480,48 +3480,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128884103</v>
+        <v>128890088</v>
       </c>
       <c r="B29" t="n">
-        <v>80258</v>
+        <v>79500</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1797</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515108</v>
+        <v>515103</v>
       </c>
       <c r="R29" t="n">
-        <v>6981358</v>
+        <v>6981364</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3548,19 +3548,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3575,60 +3570,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128890094</v>
+        <v>128884103</v>
       </c>
       <c r="B30" t="n">
-        <v>80096</v>
+        <v>80163</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>385</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515188</v>
+        <v>515108</v>
       </c>
       <c r="R30" t="n">
-        <v>6981440</v>
+        <v>6981358</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3655,14 +3650,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,12 +3677,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
         <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>92210</v>
+        <v>92215</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>128890043</v>
       </c>
       <c r="B32" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128890042</v>
+        <v>128890076</v>
       </c>
       <c r="B33" t="n">
-        <v>80229</v>
+        <v>83005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>515180</v>
+        <v>514973</v>
       </c>
       <c r="R33" t="n">
-        <v>6981428</v>
+        <v>6981271</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3956,6 +3956,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3968,22 +3973,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128890076</v>
+        <v>128890035</v>
       </c>
       <c r="B34" t="n">
-        <v>75209</v>
+        <v>80134</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3991,34 +3996,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514973</v>
+        <v>515031</v>
       </c>
       <c r="R34" t="n">
-        <v>6981271</v>
+        <v>6981191</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,11 +4058,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4070,22 +4070,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128890035</v>
+        <v>128890042</v>
       </c>
       <c r="B35" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>515031</v>
+        <v>515180</v>
       </c>
       <c r="R35" t="n">
-        <v>6981191</v>
+        <v>6981428</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
         <v>128884083</v>
       </c>
       <c r="B36" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>128884098</v>
       </c>
       <c r="B37" t="n">
-        <v>79380</v>
+        <v>79285</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>128884092</v>
       </c>
       <c r="B38" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4500,45 +4500,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128890083</v>
+        <v>128890040</v>
       </c>
       <c r="B39" t="n">
-        <v>80133</v>
+        <v>80134</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515188</v>
+        <v>515196</v>
       </c>
       <c r="R39" t="n">
-        <v>6981452</v>
+        <v>6981392</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4573,11 +4573,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4590,57 +4585,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128890040</v>
+        <v>128890083</v>
       </c>
       <c r="B40" t="n">
-        <v>80229</v>
+        <v>80038</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515196</v>
+        <v>515188</v>
       </c>
       <c r="R40" t="n">
-        <v>6981392</v>
+        <v>6981452</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4675,6 +4670,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4687,60 +4687,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128890045</v>
+        <v>128884082</v>
       </c>
       <c r="B41" t="n">
-        <v>80189</v>
+        <v>91809</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515170</v>
+        <v>515231</v>
       </c>
       <c r="R41" t="n">
-        <v>6981451</v>
+        <v>6981417</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,9 +4767,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4784,44 +4794,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128890031</v>
+        <v>128890022</v>
       </c>
       <c r="B42" t="n">
-        <v>80133</v>
+        <v>96889</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4831,10 +4841,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515039</v>
+        <v>515029</v>
       </c>
       <c r="R42" t="n">
-        <v>6981314</v>
+        <v>6981199</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4893,32 +4903,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128890022</v>
+        <v>128890031</v>
       </c>
       <c r="B43" t="n">
-        <v>96882</v>
+        <v>80038</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4928,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515029</v>
+        <v>515039</v>
       </c>
       <c r="R43" t="n">
-        <v>6981199</v>
+        <v>6981314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4990,48 +5000,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128884082</v>
+        <v>128890045</v>
       </c>
       <c r="B44" t="n">
-        <v>91804</v>
+        <v>80094</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515231</v>
+        <v>515170</v>
       </c>
       <c r="R44" t="n">
-        <v>6981417</v>
+        <v>6981451</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5058,19 +5068,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5085,12 +5085,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5100,7 +5100,7 @@
         <v>128890104</v>
       </c>
       <c r="B45" t="n">
-        <v>75192</v>
+        <v>82988</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890090</v>
+        <v>128884117</v>
       </c>
       <c r="B46" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5210,37 +5210,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>515013</v>
       </c>
       <c r="R46" t="n">
-        <v>6981245</v>
+        <v>6981204</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5267,14 +5267,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5289,12 +5294,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5304,7 +5309,7 @@
         <v>128884114</v>
       </c>
       <c r="B47" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5408,10 +5413,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128884117</v>
+        <v>128890090</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,37 +5424,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
         <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981204</v>
+        <v>6981245</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5476,19 +5481,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5503,57 +5503,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890024</v>
+        <v>128890103</v>
       </c>
       <c r="B49" t="n">
-        <v>91508</v>
+        <v>98643</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515219</v>
+        <v>515126</v>
       </c>
       <c r="R49" t="n">
-        <v>6981419</v>
+        <v>6981385</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5588,6 +5588,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5600,57 +5605,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890103</v>
+        <v>128890024</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>91513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515126</v>
+        <v>515219</v>
       </c>
       <c r="R50" t="n">
-        <v>6981385</v>
+        <v>6981419</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5685,11 +5690,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5702,22 +5702,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890041</v>
+        <v>128890034</v>
       </c>
       <c r="B51" t="n">
-        <v>80229</v>
+        <v>91809</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515196</v>
+        <v>515231</v>
       </c>
       <c r="R51" t="n">
-        <v>6981428</v>
+        <v>6981432</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5814,7 +5814,7 @@
         <v>128884080</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890034</v>
+        <v>128890041</v>
       </c>
       <c r="B53" t="n">
-        <v>91804</v>
+        <v>80134</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515231</v>
+        <v>515196</v>
       </c>
       <c r="R53" t="n">
-        <v>6981432</v>
+        <v>6981428</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6018,7 +6018,7 @@
         <v>128884086</v>
       </c>
       <c r="B54" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884090</v>
+        <v>128890025</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6235,37 +6235,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515210</v>
+        <v>515214</v>
       </c>
       <c r="R56" t="n">
-        <v>6981412</v>
+        <v>6981426</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6292,19 +6292,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6319,44 +6309,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884119</v>
+        <v>128884100</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>80163</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6366,10 +6356,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515196</v>
+        <v>515158</v>
       </c>
       <c r="R57" t="n">
-        <v>6981382</v>
+        <v>6981405</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -6401,7 +6391,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6411,7 +6401,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6441,7 +6431,7 @@
         <v>128890105</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6540,10 +6530,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128890025</v>
+        <v>128884119</v>
       </c>
       <c r="B59" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6551,37 +6541,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515214</v>
+        <v>515196</v>
       </c>
       <c r="R59" t="n">
-        <v>6981426</v>
+        <v>6981382</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6608,9 +6598,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6625,44 +6625,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884100</v>
+        <v>128884090</v>
       </c>
       <c r="B60" t="n">
-        <v>80258</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515158</v>
+        <v>515210</v>
       </c>
       <c r="R60" t="n">
-        <v>6981405</v>
+        <v>6981412</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6744,45 +6744,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128890082</v>
+        <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>79210</v>
+        <v>91513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6450</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515014</v>
+        <v>515081</v>
       </c>
       <c r="R61" t="n">
-        <v>6981245</v>
+        <v>6981324</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6817,11 +6817,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6834,22 +6829,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884099</v>
+        <v>128884104</v>
       </c>
       <c r="B62" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6857,21 +6852,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6881,10 +6876,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515158</v>
+        <v>515104</v>
       </c>
       <c r="R62" t="n">
-        <v>6981406</v>
+        <v>6981353</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -6916,7 +6911,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6926,7 +6921,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6953,45 +6948,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128890027</v>
+        <v>128890082</v>
       </c>
       <c r="B63" t="n">
-        <v>57720</v>
+        <v>79115</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515073</v>
+        <v>515014</v>
       </c>
       <c r="R63" t="n">
-        <v>6981343</v>
+        <v>6981245</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7028,7 +7023,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7043,12 +7038,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7058,7 +7053,7 @@
         <v>128884095</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7167,10 +7162,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884104</v>
+        <v>128884113</v>
       </c>
       <c r="B65" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7202,10 +7197,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515104</v>
+        <v>515021</v>
       </c>
       <c r="R65" t="n">
-        <v>6981353</v>
+        <v>6981285</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7237,7 +7232,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7247,7 +7242,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7274,10 +7274,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884113</v>
+        <v>128884099</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7285,21 +7285,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7309,10 +7309,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515021</v>
+        <v>515158</v>
       </c>
       <c r="R66" t="n">
-        <v>6981285</v>
+        <v>6981406</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7354,12 +7354,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7386,10 +7381,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128890023</v>
+        <v>128890027</v>
       </c>
       <c r="B67" t="n">
-        <v>91508</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7397,21 +7392,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7421,10 +7416,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515081</v>
+        <v>515073</v>
       </c>
       <c r="R67" t="n">
-        <v>6981324</v>
+        <v>6981343</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7457,6 +7452,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7483,45 +7483,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890077</v>
+        <v>128890032</v>
       </c>
       <c r="B68" t="n">
-        <v>75209</v>
+        <v>91967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515057</v>
+        <v>515210</v>
       </c>
       <c r="R68" t="n">
-        <v>6981333</v>
+        <v>6981426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,11 +7556,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På gammal gran i lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7573,44 +7568,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890097</v>
+        <v>128890080</v>
       </c>
       <c r="B69" t="n">
-        <v>98636</v>
+        <v>80000</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7620,10 +7615,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515060</v>
+        <v>515188</v>
       </c>
       <c r="R69" t="n">
-        <v>6981339</v>
+        <v>6981440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7660,7 +7655,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7687,32 +7682,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890075</v>
+        <v>128890077</v>
       </c>
       <c r="B70" t="n">
-        <v>105684</v>
+        <v>83005</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7722,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515124</v>
+        <v>515057</v>
       </c>
       <c r="R70" t="n">
-        <v>6981387</v>
+        <v>6981333</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7762,7 +7757,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7789,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890080</v>
+        <v>128890097</v>
       </c>
       <c r="B71" t="n">
-        <v>80095</v>
+        <v>98643</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7824,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515188</v>
+        <v>515060</v>
       </c>
       <c r="R71" t="n">
-        <v>6981440</v>
+        <v>6981339</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7864,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7891,45 +7886,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890032</v>
+        <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>91962</v>
+        <v>105691</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515210</v>
+        <v>515124</v>
       </c>
       <c r="R72" t="n">
-        <v>6981426</v>
+        <v>6981387</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7964,6 +7959,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På marken i gammal gransumpskog</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7976,12 +7976,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7991,7 +7991,7 @@
         <v>128890084</v>
       </c>
       <c r="B73" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8090,48 +8090,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128884094</v>
+        <v>128890101</v>
       </c>
       <c r="B74" t="n">
-        <v>79124</v>
+        <v>98643</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515181</v>
+        <v>515108</v>
       </c>
       <c r="R74" t="n">
-        <v>6981416</v>
+        <v>6981372</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8158,19 +8158,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8185,12 +8180,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8200,7 +8195,7 @@
         <v>128884111</v>
       </c>
       <c r="B75" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8304,48 +8299,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128890101</v>
+        <v>128884094</v>
       </c>
       <c r="B76" t="n">
-        <v>98636</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515108</v>
+        <v>515181</v>
       </c>
       <c r="R76" t="n">
-        <v>6981372</v>
+        <v>6981416</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8372,14 +8367,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>16 plantor på marken i gammal granskog</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,22 +8394,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890037</v>
+        <v>128890085</v>
       </c>
       <c r="B77" t="n">
-        <v>80229</v>
+        <v>91809</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515026</v>
+        <v>515034</v>
       </c>
       <c r="R77" t="n">
-        <v>6981261</v>
+        <v>6981293</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,6 +8479,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8491,12 +8496,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8506,7 +8511,7 @@
         <v>128884102</v>
       </c>
       <c r="B78" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8610,10 +8615,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128890085</v>
+        <v>128890037</v>
       </c>
       <c r="B79" t="n">
-        <v>91804</v>
+        <v>80134</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8621,34 +8626,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515034</v>
+        <v>515026</v>
       </c>
       <c r="R79" t="n">
-        <v>6981293</v>
+        <v>6981261</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8683,11 +8688,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8700,44 +8700,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890091</v>
+        <v>128890093</v>
       </c>
       <c r="B80" t="n">
-        <v>80229</v>
+        <v>80001</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515069</v>
+        <v>515053</v>
       </c>
       <c r="R80" t="n">
-        <v>6981349</v>
+        <v>6981314</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,10 +8814,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128890087</v>
+        <v>128890096</v>
       </c>
       <c r="B81" t="n">
-        <v>80257</v>
+        <v>80094</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8825,21 +8825,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6461</v>
+        <v>229497</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På lodyta</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8916,10 +8916,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884091</v>
+        <v>128884081</v>
       </c>
       <c r="B82" t="n">
-        <v>80229</v>
+        <v>91513</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8927,21 +8927,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515199</v>
+        <v>515230</v>
       </c>
       <c r="R82" t="n">
-        <v>6981419</v>
+        <v>6981431</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9026,7 +9026,7 @@
         <v>128890038</v>
       </c>
       <c r="B83" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9120,32 +9120,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890093</v>
+        <v>128890087</v>
       </c>
       <c r="B84" t="n">
-        <v>80096</v>
+        <v>80162</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>385</v>
+        <v>6461</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9155,10 +9155,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515053</v>
+        <v>515014</v>
       </c>
       <c r="R84" t="n">
-        <v>6981314</v>
+        <v>6981245</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9222,10 +9222,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884081</v>
+        <v>128884091</v>
       </c>
       <c r="B85" t="n">
-        <v>91508</v>
+        <v>80134</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9233,21 +9233,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515230</v>
+        <v>515199</v>
       </c>
       <c r="R85" t="n">
-        <v>6981431</v>
+        <v>6981419</v>
       </c>
       <c r="S85" t="n">
         <v>4</v>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9329,32 +9329,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890099</v>
+        <v>128890091</v>
       </c>
       <c r="B86" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515054</v>
+        <v>515069</v>
       </c>
       <c r="R86" t="n">
-        <v>6981308</v>
+        <v>6981349</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9431,32 +9431,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890096</v>
+        <v>128890099</v>
       </c>
       <c r="B87" t="n">
-        <v>80189</v>
+        <v>98643</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515014</v>
+        <v>515054</v>
       </c>
       <c r="R87" t="n">
-        <v>6981245</v>
+        <v>6981308</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884115</v>
+        <v>128884109</v>
       </c>
       <c r="B2" t="n">
-        <v>80099</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515019</v>
+        <v>515053</v>
       </c>
       <c r="R2" t="n">
-        <v>6981238</v>
+        <v>6981306</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128890092</v>
+        <v>128884101</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515067</v>
+        <v>515135</v>
       </c>
       <c r="R3" t="n">
-        <v>6981353</v>
+        <v>6981381</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +850,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884109</v>
+        <v>128884097</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515053</v>
+        <v>515184</v>
       </c>
       <c r="R4" t="n">
-        <v>6981306</v>
+        <v>6981392</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -954,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,48 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884101</v>
+        <v>128890092</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>80175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515135</v>
+        <v>515067</v>
       </c>
       <c r="R5" t="n">
-        <v>6981381</v>
+        <v>6981353</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,19 +1064,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:29</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,44 +1086,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128884097</v>
+        <v>128884115</v>
       </c>
       <c r="B6" t="n">
-        <v>80139</v>
+        <v>80099</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515184</v>
+        <v>515019</v>
       </c>
       <c r="R6" t="n">
-        <v>6981392</v>
+        <v>6981238</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890033</v>
+        <v>128890100</v>
       </c>
       <c r="B12" t="n">
-        <v>75027</v>
+        <v>98651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515018</v>
+        <v>515060</v>
       </c>
       <c r="R12" t="n">
-        <v>6981215</v>
+        <v>6981326</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1793,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1805,60 +1810,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128884116</v>
+        <v>128890033</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>75027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515030</v>
+        <v>515018</v>
       </c>
       <c r="R13" t="n">
-        <v>6981199</v>
+        <v>6981215</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,19 +1890,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,22 +1907,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128890039</v>
+        <v>128884116</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,37 +1930,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515123</v>
+        <v>515030</v>
       </c>
       <c r="R14" t="n">
-        <v>6981380</v>
+        <v>6981199</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,9 +1987,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,57 +2014,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128890100</v>
+        <v>128890039</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515060</v>
+        <v>515123</v>
       </c>
       <c r="R15" t="n">
-        <v>6981326</v>
+        <v>6981380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,11 +2099,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2111,22 +2111,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128890028</v>
+        <v>128884079</v>
       </c>
       <c r="B16" t="n">
-        <v>80005</v>
+        <v>78047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>388</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515039</v>
+        <v>515240</v>
       </c>
       <c r="R16" t="n">
-        <v>6981285</v>
+        <v>6981445</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,37 +2191,46 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890081</v>
+        <v>128890028</v>
       </c>
       <c r="B17" t="n">
         <v>80005</v>
@@ -2252,14 +2261,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515203</v>
+        <v>515039</v>
       </c>
       <c r="R17" t="n">
-        <v>6981449</v>
+        <v>6981285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,39 +2303,35 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128884105</v>
+        <v>128890081</v>
       </c>
       <c r="B18" t="n">
-        <v>80139</v>
+        <v>80005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2334,37 +2339,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515069</v>
+        <v>515203</v>
       </c>
       <c r="R18" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2391,19 +2396,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,22 +2418,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128884079</v>
+        <v>128884105</v>
       </c>
       <c r="B19" t="n">
-        <v>78047</v>
+        <v>80139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515240</v>
+        <v>515069</v>
       </c>
       <c r="R19" t="n">
-        <v>6981445</v>
+        <v>6981348</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,48 +2537,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128884089</v>
+        <v>128890095</v>
       </c>
       <c r="B20" t="n">
-        <v>80168</v>
+        <v>92321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>2014</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515218</v>
+        <v>515145</v>
       </c>
       <c r="R20" t="n">
-        <v>6981412</v>
+        <v>6981384</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2605,19 +2605,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:09</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2632,22 +2627,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128884110</v>
+        <v>128890030</v>
       </c>
       <c r="B21" t="n">
-        <v>80005</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,37 +2650,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>388</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515038</v>
+        <v>515032</v>
       </c>
       <c r="R21" t="n">
-        <v>6981305</v>
+        <v>6981265</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,19 +2707,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2739,44 +2724,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884107</v>
+        <v>128884089</v>
       </c>
       <c r="B22" t="n">
-        <v>80139</v>
+        <v>80168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2786,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515060</v>
+        <v>515218</v>
       </c>
       <c r="R22" t="n">
-        <v>6981336</v>
+        <v>6981412</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2821,7 +2806,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2831,7 +2816,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2858,10 +2843,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128884084</v>
+        <v>128884110</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>80005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2869,21 +2854,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2893,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515227</v>
+        <v>515038</v>
       </c>
       <c r="R23" t="n">
-        <v>6981418</v>
+        <v>6981305</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -2928,7 +2913,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2938,7 +2923,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2965,10 +2950,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128890095</v>
+        <v>128884107</v>
       </c>
       <c r="B24" t="n">
-        <v>92321</v>
+        <v>80139</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2976,37 +2961,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515145</v>
+        <v>515060</v>
       </c>
       <c r="R24" t="n">
-        <v>6981384</v>
+        <v>6981336</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3033,14 +3018,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3055,22 +3045,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128890030</v>
+        <v>128884084</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>79034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,37 +3068,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515032</v>
+        <v>515227</v>
       </c>
       <c r="R25" t="n">
-        <v>6981265</v>
+        <v>6981418</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3135,9 +3125,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,12 +3152,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -5097,48 +5097,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128884117</v>
+        <v>128890103</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>98651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515013</v>
+        <v>515126</v>
       </c>
       <c r="R45" t="n">
-        <v>6981204</v>
+        <v>6981385</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5165,19 +5165,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5192,22 +5187,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890090</v>
+        <v>128890024</v>
       </c>
       <c r="B46" t="n">
-        <v>80139</v>
+        <v>91520</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5215,34 +5210,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515013</v>
+        <v>515219</v>
       </c>
       <c r="R46" t="n">
-        <v>6981245</v>
+        <v>6981419</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5277,11 +5272,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5294,60 +5284,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128884114</v>
+        <v>128890104</v>
       </c>
       <c r="B47" t="n">
-        <v>80139</v>
+        <v>82993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515018</v>
+        <v>515070</v>
       </c>
       <c r="R47" t="n">
-        <v>6981240</v>
+        <v>6981365</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5374,19 +5364,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5401,22 +5386,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890024</v>
+        <v>128884117</v>
       </c>
       <c r="B48" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5424,37 +5409,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515219</v>
+        <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981419</v>
+        <v>6981204</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5481,9 +5466,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5498,44 +5493,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890104</v>
+        <v>128890090</v>
       </c>
       <c r="B49" t="n">
-        <v>82993</v>
+        <v>80139</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5545,10 +5540,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R49" t="n">
-        <v>6981365</v>
+        <v>6981245</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5585,7 +5580,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5612,48 +5607,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890103</v>
+        <v>128884114</v>
       </c>
       <c r="B50" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515126</v>
+        <v>515018</v>
       </c>
       <c r="R50" t="n">
-        <v>6981385</v>
+        <v>6981240</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5680,14 +5675,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5702,12 +5702,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128890027</v>
+        <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>91520</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6755,21 +6755,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515073</v>
+        <v>515081</v>
       </c>
       <c r="R61" t="n">
-        <v>6981343</v>
+        <v>6981324</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6815,11 +6815,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6846,10 +6841,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128890023</v>
+        <v>128884104</v>
       </c>
       <c r="B62" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6857,37 +6852,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515081</v>
+        <v>515104</v>
       </c>
       <c r="R62" t="n">
-        <v>6981324</v>
+        <v>6981353</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6914,9 +6909,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6931,60 +6936,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884104</v>
+        <v>128890082</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515104</v>
+        <v>515014</v>
       </c>
       <c r="R63" t="n">
-        <v>6981353</v>
+        <v>6981245</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7011,19 +7016,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7038,60 +7038,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128890082</v>
+        <v>128884099</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>80139</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515014</v>
+        <v>515158</v>
       </c>
       <c r="R64" t="n">
-        <v>6981245</v>
+        <v>6981406</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7118,14 +7118,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7140,22 +7145,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884099</v>
+        <v>128884095</v>
       </c>
       <c r="B65" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7163,21 +7168,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7187,10 +7192,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515158</v>
+        <v>515183</v>
       </c>
       <c r="R65" t="n">
-        <v>6981406</v>
+        <v>6981391</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7222,7 +7227,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7232,7 +7237,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7259,7 +7269,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884095</v>
+        <v>128884113</v>
       </c>
       <c r="B66" t="n">
         <v>79034</v>
@@ -7294,10 +7304,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515183</v>
+        <v>515021</v>
       </c>
       <c r="R66" t="n">
-        <v>6981391</v>
+        <v>6981285</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7329,7 +7339,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7339,7 +7349,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7371,10 +7381,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884113</v>
+        <v>128890027</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7382,37 +7392,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515021</v>
+        <v>515073</v>
       </c>
       <c r="R67" t="n">
-        <v>6981285</v>
+        <v>6981343</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7439,24 +7449,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7471,12 +7471,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7585,32 +7585,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890077</v>
+        <v>128890097</v>
       </c>
       <c r="B69" t="n">
-        <v>83010</v>
+        <v>98651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515057</v>
+        <v>515060</v>
       </c>
       <c r="R69" t="n">
-        <v>6981333</v>
+        <v>6981339</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7687,45 +7687,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890032</v>
+        <v>128890077</v>
       </c>
       <c r="B70" t="n">
-        <v>91975</v>
+        <v>83010</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515210</v>
+        <v>515057</v>
       </c>
       <c r="R70" t="n">
-        <v>6981426</v>
+        <v>6981333</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7760,6 +7760,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På gammal gran i lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7772,22 +7777,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890097</v>
+        <v>128890032</v>
       </c>
       <c r="B71" t="n">
-        <v>98651</v>
+        <v>91975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7795,34 +7800,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515060</v>
+        <v>515210</v>
       </c>
       <c r="R71" t="n">
-        <v>6981339</v>
+        <v>6981426</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7857,11 +7862,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7874,12 +7874,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8712,32 +8712,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890087</v>
+        <v>128890099</v>
       </c>
       <c r="B80" t="n">
-        <v>80167</v>
+        <v>98651</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515014</v>
+        <v>515054</v>
       </c>
       <c r="R80" t="n">
-        <v>6981245</v>
+        <v>6981308</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På lodyta</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,48 +8814,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884091</v>
+        <v>128890087</v>
       </c>
       <c r="B81" t="n">
-        <v>80139</v>
+        <v>80167</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515199</v>
+        <v>515014</v>
       </c>
       <c r="R81" t="n">
-        <v>6981419</v>
+        <v>6981245</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8882,19 +8882,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8909,19 +8904,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128890091</v>
+        <v>128884091</v>
       </c>
       <c r="B82" t="n">
         <v>80139</v>
@@ -8952,17 +8947,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515069</v>
+        <v>515199</v>
       </c>
       <c r="R82" t="n">
-        <v>6981349</v>
+        <v>6981419</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8989,14 +8984,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9011,19 +9011,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890038</v>
+        <v>128890091</v>
       </c>
       <c r="B83" t="n">
         <v>80139</v>
@@ -9054,14 +9054,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515041</v>
+        <v>515069</v>
       </c>
       <c r="R83" t="n">
-        <v>6981296</v>
+        <v>6981349</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9096,6 +9096,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9108,57 +9113,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890099</v>
+        <v>128890038</v>
       </c>
       <c r="B84" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515054</v>
+        <v>515041</v>
       </c>
       <c r="R84" t="n">
-        <v>6981308</v>
+        <v>6981296</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9193,11 +9198,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9210,12 +9210,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884109</v>
+        <v>128884101</v>
       </c>
       <c r="B2" t="n">
         <v>79034</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515053</v>
+        <v>515135</v>
       </c>
       <c r="R2" t="n">
-        <v>6981306</v>
+        <v>6981381</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884101</v>
+        <v>128884115</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>80099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515135</v>
+        <v>515019</v>
       </c>
       <c r="R3" t="n">
-        <v>6981381</v>
+        <v>6981238</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884097</v>
+        <v>128884109</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515184</v>
+        <v>515053</v>
       </c>
       <c r="R4" t="n">
-        <v>6981392</v>
+        <v>6981306</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128884115</v>
+        <v>128884097</v>
       </c>
       <c r="B6" t="n">
-        <v>80099</v>
+        <v>80139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515019</v>
+        <v>515184</v>
       </c>
       <c r="R6" t="n">
-        <v>6981238</v>
+        <v>6981392</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128890079</v>
       </c>
       <c r="B7" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884093</v>
+        <v>128884087</v>
       </c>
       <c r="B9" t="n">
-        <v>105699</v>
+        <v>80139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515174</v>
+        <v>515217</v>
       </c>
       <c r="R9" t="n">
-        <v>6981416</v>
+        <v>6981406</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128884087</v>
+        <v>128890036</v>
       </c>
       <c r="B10" t="n">
         <v>80139</v>
@@ -1547,17 +1547,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515217</v>
+        <v>515018</v>
       </c>
       <c r="R10" t="n">
-        <v>6981406</v>
+        <v>6981217</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,19 +1584,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,60 +1601,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128890036</v>
+        <v>128884093</v>
       </c>
       <c r="B11" t="n">
-        <v>80139</v>
+        <v>105704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515018</v>
+        <v>515174</v>
       </c>
       <c r="R11" t="n">
-        <v>6981217</v>
+        <v>6981416</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,9 +1681,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,57 +1708,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890100</v>
+        <v>128890033</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>75027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515060</v>
+        <v>515018</v>
       </c>
       <c r="R12" t="n">
-        <v>6981326</v>
+        <v>6981215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,11 +1793,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1810,44 +1805,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890033</v>
+        <v>128890039</v>
       </c>
       <c r="B13" t="n">
-        <v>75027</v>
+        <v>80139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515018</v>
+        <v>515123</v>
       </c>
       <c r="R13" t="n">
-        <v>6981215</v>
+        <v>6981380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,48 +1914,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128884116</v>
+        <v>128890100</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515030</v>
+        <v>515060</v>
       </c>
       <c r="R14" t="n">
-        <v>6981199</v>
+        <v>6981326</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,19 +1982,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:07</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128890039</v>
+        <v>128884116</v>
       </c>
       <c r="B15" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,37 +2027,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515123</v>
+        <v>515030</v>
       </c>
       <c r="R15" t="n">
-        <v>6981380</v>
+        <v>6981199</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2094,9 +2084,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,22 +2111,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128884079</v>
+        <v>128890028</v>
       </c>
       <c r="B16" t="n">
-        <v>78047</v>
+        <v>80005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515240</v>
+        <v>515039</v>
       </c>
       <c r="R16" t="n">
-        <v>6981445</v>
+        <v>6981285</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,46 +2191,37 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890028</v>
+        <v>128890081</v>
       </c>
       <c r="B17" t="n">
         <v>80005</v>
@@ -2261,14 +2252,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515039</v>
+        <v>515203</v>
       </c>
       <c r="R17" t="n">
-        <v>6981285</v>
+        <v>6981449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2303,35 +2294,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128890081</v>
+        <v>128884105</v>
       </c>
       <c r="B18" t="n">
-        <v>80005</v>
+        <v>80139</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,37 +2334,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515203</v>
+        <v>515069</v>
       </c>
       <c r="R18" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2396,14 +2391,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,22 +2418,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128884105</v>
+        <v>128884079</v>
       </c>
       <c r="B19" t="n">
-        <v>80139</v>
+        <v>78047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515069</v>
+        <v>515240</v>
       </c>
       <c r="R19" t="n">
-        <v>6981348</v>
+        <v>6981445</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128890095</v>
+        <v>128884084</v>
       </c>
       <c r="B20" t="n">
-        <v>92321</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,37 +2548,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515145</v>
+        <v>515227</v>
       </c>
       <c r="R20" t="n">
-        <v>6981384</v>
+        <v>6981418</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2605,14 +2605,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,22 +2632,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128890030</v>
+        <v>128884107</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,37 +2655,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515032</v>
+        <v>515060</v>
       </c>
       <c r="R21" t="n">
-        <v>6981265</v>
+        <v>6981336</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2707,9 +2712,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,44 +2739,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884089</v>
+        <v>128884110</v>
       </c>
       <c r="B22" t="n">
-        <v>80168</v>
+        <v>80005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2786,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515218</v>
+        <v>515038</v>
       </c>
       <c r="R22" t="n">
-        <v>6981412</v>
+        <v>6981305</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2806,7 +2821,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2816,7 +2831,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2843,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128884110</v>
+        <v>128890095</v>
       </c>
       <c r="B23" t="n">
-        <v>80005</v>
+        <v>92326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,37 +2869,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>388</v>
+        <v>2014</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515038</v>
+        <v>515145</v>
       </c>
       <c r="R23" t="n">
-        <v>6981305</v>
+        <v>6981384</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2911,19 +2926,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:49</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2938,22 +2948,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884107</v>
+        <v>128890030</v>
       </c>
       <c r="B24" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,37 +2971,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515060</v>
+        <v>515032</v>
       </c>
       <c r="R24" t="n">
-        <v>6981336</v>
+        <v>6981265</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,19 +3028,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3045,22 +3045,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884084</v>
+        <v>128890026</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3068,37 +3068,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515227</v>
+        <v>515052</v>
       </c>
       <c r="R25" t="n">
-        <v>6981418</v>
+        <v>6981331</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3125,19 +3125,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:05</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,60 +3147,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128890026</v>
+        <v>128884089</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>80168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515052</v>
+        <v>515218</v>
       </c>
       <c r="R26" t="n">
-        <v>6981331</v>
+        <v>6981412</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3232,14 +3227,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,22 +3254,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128884108</v>
+        <v>128890094</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>80006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3277,37 +3277,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>385</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515059</v>
+        <v>515188</v>
       </c>
       <c r="R27" t="n">
-        <v>6981319</v>
+        <v>6981440</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3334,24 +3334,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>nr 10</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3366,12 +3356,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3587,10 +3577,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128890094</v>
+        <v>128884108</v>
       </c>
       <c r="B30" t="n">
-        <v>80006</v>
+        <v>98656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3598,37 +3588,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>385</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515188</v>
+        <v>515059</v>
       </c>
       <c r="R30" t="n">
-        <v>6981440</v>
+        <v>6981319</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3655,14 +3645,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>nr 10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,12 +3677,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
         <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>92223</v>
+        <v>92228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128884083</v>
       </c>
       <c r="B36" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>128884082</v>
       </c>
       <c r="B41" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>128890022</v>
       </c>
       <c r="B42" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5097,45 +5097,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890103</v>
+        <v>128890024</v>
       </c>
       <c r="B45" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515126</v>
+        <v>515219</v>
       </c>
       <c r="R45" t="n">
-        <v>6981385</v>
+        <v>6981419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,11 +5170,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5187,57 +5182,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890024</v>
+        <v>128890104</v>
       </c>
       <c r="B46" t="n">
-        <v>91520</v>
+        <v>82993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515219</v>
+        <v>515070</v>
       </c>
       <c r="R46" t="n">
-        <v>6981419</v>
+        <v>6981365</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5272,6 +5267,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5284,60 +5284,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128890104</v>
+        <v>128884117</v>
       </c>
       <c r="B47" t="n">
-        <v>82993</v>
+        <v>79034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R47" t="n">
-        <v>6981365</v>
+        <v>6981204</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5364,14 +5364,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5386,22 +5391,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128884117</v>
+        <v>128890090</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5409,37 +5414,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
         <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981204</v>
+        <v>6981245</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5466,19 +5471,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5493,19 +5493,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890090</v>
+        <v>128884114</v>
       </c>
       <c r="B49" t="n">
         <v>80139</v>
@@ -5536,17 +5536,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515013</v>
+        <v>515018</v>
       </c>
       <c r="R49" t="n">
-        <v>6981245</v>
+        <v>6981240</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5573,14 +5573,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5595,60 +5600,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128884114</v>
+        <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515018</v>
+        <v>515126</v>
       </c>
       <c r="R50" t="n">
-        <v>6981240</v>
+        <v>6981385</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5675,19 +5680,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5702,12 +5702,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
         <v>128890098</v>
       </c>
       <c r="B52" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5923,10 +5923,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890034</v>
+        <v>128890041</v>
       </c>
       <c r="B53" t="n">
-        <v>91805</v>
+        <v>80139</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5934,21 +5934,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515231</v>
+        <v>515196</v>
       </c>
       <c r="R53" t="n">
-        <v>6981432</v>
+        <v>6981428</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6020,10 +6020,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128890041</v>
+        <v>128884080</v>
       </c>
       <c r="B54" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6031,37 +6031,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515196</v>
+        <v>515239</v>
       </c>
       <c r="R54" t="n">
-        <v>6981428</v>
+        <v>6981443</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6088,9 +6088,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6105,22 +6115,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128884080</v>
+        <v>128890034</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>91808</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6128,37 +6138,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515239</v>
+        <v>515231</v>
       </c>
       <c r="R55" t="n">
-        <v>6981443</v>
+        <v>6981432</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6185,19 +6195,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6212,60 +6212,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884100</v>
+        <v>128890025</v>
       </c>
       <c r="B56" t="n">
-        <v>80168</v>
+        <v>91523</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515158</v>
+        <v>515214</v>
       </c>
       <c r="R56" t="n">
-        <v>6981405</v>
+        <v>6981426</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6292,19 +6292,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6319,60 +6309,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128890025</v>
+        <v>128884100</v>
       </c>
       <c r="B57" t="n">
-        <v>91520</v>
+        <v>80168</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515214</v>
+        <v>515158</v>
       </c>
       <c r="R57" t="n">
-        <v>6981426</v>
+        <v>6981405</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6399,9 +6389,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6416,12 +6416,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6747,7 +6747,7 @@
         <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884104</v>
+        <v>128890027</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515104</v>
+        <v>515073</v>
       </c>
       <c r="R62" t="n">
-        <v>6981353</v>
+        <v>6981343</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6909,19 +6909,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6936,60 +6931,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128890082</v>
+        <v>128884104</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>79034</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515014</v>
+        <v>515104</v>
       </c>
       <c r="R63" t="n">
-        <v>6981245</v>
+        <v>6981353</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7016,14 +7011,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7038,60 +7038,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884099</v>
+        <v>128890082</v>
       </c>
       <c r="B64" t="n">
-        <v>80139</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515158</v>
+        <v>515014</v>
       </c>
       <c r="R64" t="n">
-        <v>6981406</v>
+        <v>6981245</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7118,19 +7118,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7145,22 +7140,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884095</v>
+        <v>128884099</v>
       </c>
       <c r="B65" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7168,21 +7163,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7192,10 +7187,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515183</v>
+        <v>515158</v>
       </c>
       <c r="R65" t="n">
-        <v>6981391</v>
+        <v>6981406</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7227,7 +7222,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7237,12 +7232,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7269,7 +7259,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884113</v>
+        <v>128884095</v>
       </c>
       <c r="B66" t="n">
         <v>79034</v>
@@ -7304,10 +7294,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515021</v>
+        <v>515183</v>
       </c>
       <c r="R66" t="n">
-        <v>6981285</v>
+        <v>6981391</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7339,7 +7329,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7349,7 +7339,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7381,10 +7371,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128890027</v>
+        <v>128884113</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7392,37 +7382,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515073</v>
+        <v>515021</v>
       </c>
       <c r="R67" t="n">
-        <v>6981343</v>
+        <v>6981285</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7449,14 +7439,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7471,57 +7471,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890080</v>
+        <v>128890032</v>
       </c>
       <c r="B68" t="n">
-        <v>80005</v>
+        <v>91978</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515188</v>
+        <v>515210</v>
       </c>
       <c r="R68" t="n">
-        <v>6981440</v>
+        <v>6981426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,11 +7556,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7573,12 +7568,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7588,7 +7583,7 @@
         <v>128890097</v>
       </c>
       <c r="B69" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7687,32 +7682,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890077</v>
+        <v>128890075</v>
       </c>
       <c r="B70" t="n">
-        <v>83010</v>
+        <v>105704</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7722,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515057</v>
+        <v>515124</v>
       </c>
       <c r="R70" t="n">
-        <v>6981333</v>
+        <v>6981387</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7762,7 +7757,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7789,45 +7784,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890032</v>
+        <v>128890080</v>
       </c>
       <c r="B71" t="n">
-        <v>91975</v>
+        <v>80005</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515210</v>
+        <v>515188</v>
       </c>
       <c r="R71" t="n">
-        <v>6981426</v>
+        <v>6981440</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7862,6 +7857,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7874,44 +7874,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890075</v>
+        <v>128890077</v>
       </c>
       <c r="B72" t="n">
-        <v>105699</v>
+        <v>83010</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515124</v>
+        <v>515057</v>
       </c>
       <c r="R72" t="n">
-        <v>6981387</v>
+        <v>6981333</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7991,7 +7991,7 @@
         <v>128890084</v>
       </c>
       <c r="B73" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>128890101</v>
       </c>
       <c r="B76" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8406,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890037</v>
+        <v>128890085</v>
       </c>
       <c r="B77" t="n">
-        <v>80139</v>
+        <v>91808</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515026</v>
+        <v>515034</v>
       </c>
       <c r="R77" t="n">
-        <v>6981261</v>
+        <v>6981293</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,6 +8479,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8491,19 +8496,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884102</v>
+        <v>128890037</v>
       </c>
       <c r="B78" t="n">
         <v>80139</v>
@@ -8534,17 +8539,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515111</v>
+        <v>515026</v>
       </c>
       <c r="R78" t="n">
-        <v>6981360</v>
+        <v>6981261</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8571,19 +8576,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8598,22 +8593,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128890085</v>
+        <v>128884102</v>
       </c>
       <c r="B79" t="n">
-        <v>91805</v>
+        <v>80139</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8621,37 +8616,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515034</v>
+        <v>515111</v>
       </c>
       <c r="R79" t="n">
-        <v>6981293</v>
+        <v>6981360</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8678,14 +8673,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,22 +8700,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890099</v>
+        <v>128890093</v>
       </c>
       <c r="B80" t="n">
-        <v>98651</v>
+        <v>80006</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8723,21 +8723,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>385</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515054</v>
+        <v>515053</v>
       </c>
       <c r="R80" t="n">
-        <v>6981308</v>
+        <v>6981314</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,10 +8814,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128890087</v>
+        <v>128890096</v>
       </c>
       <c r="B81" t="n">
-        <v>80167</v>
+        <v>80099</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8825,21 +8825,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6461</v>
+        <v>229497</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På lodyta</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8916,10 +8916,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884091</v>
+        <v>128884081</v>
       </c>
       <c r="B82" t="n">
-        <v>80139</v>
+        <v>91523</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8927,21 +8927,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515199</v>
+        <v>515230</v>
       </c>
       <c r="R82" t="n">
-        <v>6981419</v>
+        <v>6981431</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9023,32 +9023,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890091</v>
+        <v>128890087</v>
       </c>
       <c r="B83" t="n">
-        <v>80139</v>
+        <v>80167</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9058,10 +9058,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515069</v>
+        <v>515014</v>
       </c>
       <c r="R83" t="n">
-        <v>6981349</v>
+        <v>6981245</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9125,7 +9125,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890038</v>
+        <v>128884091</v>
       </c>
       <c r="B84" t="n">
         <v>80139</v>
@@ -9156,17 +9156,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515041</v>
+        <v>515199</v>
       </c>
       <c r="R84" t="n">
-        <v>6981296</v>
+        <v>6981419</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9193,9 +9193,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9210,44 +9220,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890096</v>
+        <v>128890091</v>
       </c>
       <c r="B85" t="n">
-        <v>80099</v>
+        <v>80139</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9257,10 +9267,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515014</v>
+        <v>515069</v>
       </c>
       <c r="R85" t="n">
-        <v>6981245</v>
+        <v>6981349</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9324,10 +9334,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128884081</v>
+        <v>128890038</v>
       </c>
       <c r="B86" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9335,37 +9345,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515230</v>
+        <v>515041</v>
       </c>
       <c r="R86" t="n">
-        <v>6981431</v>
+        <v>6981296</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9392,19 +9402,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9419,22 +9419,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890093</v>
+        <v>128890099</v>
       </c>
       <c r="B87" t="n">
-        <v>80006</v>
+        <v>98656</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>385</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515053</v>
+        <v>515054</v>
       </c>
       <c r="R87" t="n">
-        <v>6981314</v>
+        <v>6981308</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884101</v>
+        <v>128884109</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515135</v>
+        <v>515053</v>
       </c>
       <c r="R2" t="n">
-        <v>6981381</v>
+        <v>6981306</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884115</v>
+        <v>128890092</v>
       </c>
       <c r="B3" t="n">
-        <v>80099</v>
+        <v>80176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515019</v>
+        <v>515067</v>
       </c>
       <c r="R3" t="n">
-        <v>6981238</v>
+        <v>6981353</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +850,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:56</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884109</v>
+        <v>128884097</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515053</v>
+        <v>515184</v>
       </c>
       <c r="R4" t="n">
-        <v>6981306</v>
+        <v>6981392</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -959,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128890092</v>
+        <v>128884115</v>
       </c>
       <c r="B5" t="n">
-        <v>80175</v>
+        <v>80100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515067</v>
+        <v>515019</v>
       </c>
       <c r="R5" t="n">
-        <v>6981353</v>
+        <v>6981238</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,14 +1059,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128884097</v>
+        <v>128884101</v>
       </c>
       <c r="B6" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515184</v>
+        <v>515135</v>
       </c>
       <c r="R6" t="n">
-        <v>6981392</v>
+        <v>6981381</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128890079</v>
       </c>
       <c r="B7" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>128884087</v>
       </c>
       <c r="B9" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>128890036</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128884093</v>
       </c>
       <c r="B11" t="n">
-        <v>105704</v>
+        <v>105707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890039</v>
+        <v>128884116</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,37 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515123</v>
+        <v>515030</v>
       </c>
       <c r="R13" t="n">
-        <v>6981380</v>
+        <v>6981199</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,9 +1885,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,12 +1912,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1917,7 +1927,7 @@
         <v>128890100</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128884116</v>
+        <v>128890039</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,37 +2037,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515030</v>
+        <v>515123</v>
       </c>
       <c r="R15" t="n">
-        <v>6981199</v>
+        <v>6981380</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2084,19 +2094,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,22 +2111,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128890028</v>
+        <v>128884079</v>
       </c>
       <c r="B16" t="n">
-        <v>80005</v>
+        <v>78048</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>388</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515039</v>
+        <v>515240</v>
       </c>
       <c r="R16" t="n">
-        <v>6981285</v>
+        <v>6981445</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,40 +2191,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890081</v>
+        <v>128890028</v>
       </c>
       <c r="B17" t="n">
-        <v>80005</v>
+        <v>80006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,14 +2261,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515203</v>
+        <v>515039</v>
       </c>
       <c r="R17" t="n">
-        <v>6981449</v>
+        <v>6981285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,39 +2303,35 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128884105</v>
+        <v>128890081</v>
       </c>
       <c r="B18" t="n">
-        <v>80139</v>
+        <v>80006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2334,37 +2339,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515069</v>
+        <v>515203</v>
       </c>
       <c r="R18" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2391,19 +2396,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,22 +2418,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128884079</v>
+        <v>128884105</v>
       </c>
       <c r="B19" t="n">
-        <v>78047</v>
+        <v>80140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515240</v>
+        <v>515069</v>
       </c>
       <c r="R19" t="n">
-        <v>6981445</v>
+        <v>6981348</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128884084</v>
+        <v>128890095</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>92329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,37 +2548,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515227</v>
+        <v>515145</v>
       </c>
       <c r="R20" t="n">
-        <v>6981418</v>
+        <v>6981384</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2605,19 +2605,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:05</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2632,22 +2627,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128884107</v>
+        <v>128890030</v>
       </c>
       <c r="B21" t="n">
-        <v>80139</v>
+        <v>80141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,37 +2650,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515060</v>
+        <v>515032</v>
       </c>
       <c r="R21" t="n">
-        <v>6981336</v>
+        <v>6981265</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,19 +2707,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2739,22 +2724,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884110</v>
+        <v>128884084</v>
       </c>
       <c r="B22" t="n">
-        <v>80005</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,21 +2747,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2786,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515038</v>
+        <v>515227</v>
       </c>
       <c r="R22" t="n">
-        <v>6981305</v>
+        <v>6981418</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2821,7 +2806,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2831,7 +2816,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2858,48 +2843,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128890095</v>
+        <v>128884089</v>
       </c>
       <c r="B23" t="n">
-        <v>92326</v>
+        <v>80169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2014</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515145</v>
+        <v>515218</v>
       </c>
       <c r="R23" t="n">
-        <v>6981384</v>
+        <v>6981412</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2926,14 +2911,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2948,19 +2938,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128890030</v>
+        <v>128884107</v>
       </c>
       <c r="B24" t="n">
         <v>80140</v>
@@ -2971,37 +2961,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515032</v>
+        <v>515060</v>
       </c>
       <c r="R24" t="n">
-        <v>6981265</v>
+        <v>6981336</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3028,9 +3018,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3045,12 +3045,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3159,32 +3159,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884089</v>
+        <v>128884110</v>
       </c>
       <c r="B26" t="n">
-        <v>80168</v>
+        <v>80006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>388</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515218</v>
+        <v>515038</v>
       </c>
       <c r="R26" t="n">
-        <v>6981412</v>
+        <v>6981305</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3269,7 +3269,7 @@
         <v>128890094</v>
       </c>
       <c r="B27" t="n">
-        <v>80006</v>
+        <v>80007</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>128890088</v>
       </c>
       <c r="B28" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>128884103</v>
       </c>
       <c r="B29" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>128884108</v>
       </c>
       <c r="B30" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3689,32 +3689,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128890029</v>
+        <v>128890043</v>
       </c>
       <c r="B31" t="n">
-        <v>92228</v>
+        <v>80140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515089</v>
+        <v>515166</v>
       </c>
       <c r="R31" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,32 +3786,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128890043</v>
+        <v>128890029</v>
       </c>
       <c r="B32" t="n">
-        <v>80139</v>
+        <v>92231</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515166</v>
+        <v>515089</v>
       </c>
       <c r="R32" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3886,7 +3886,7 @@
         <v>128890042</v>
       </c>
       <c r="B33" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>128890076</v>
       </c>
       <c r="B34" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128890035</v>
       </c>
       <c r="B35" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128884083</v>
+        <v>128884098</v>
       </c>
       <c r="B36" t="n">
-        <v>91523</v>
+        <v>79291</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>515231</v>
+        <v>515158</v>
       </c>
       <c r="R36" t="n">
-        <v>6981417</v>
+        <v>6981406</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4286,32 +4286,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128884098</v>
+        <v>128884092</v>
       </c>
       <c r="B37" t="n">
-        <v>79290</v>
+        <v>80140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>515158</v>
+        <v>515180</v>
       </c>
       <c r="R37" t="n">
-        <v>6981406</v>
+        <v>6981435</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4393,10 +4393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128884092</v>
+        <v>128884083</v>
       </c>
       <c r="B38" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>515180</v>
+        <v>515231</v>
       </c>
       <c r="R38" t="n">
-        <v>6981435</v>
+        <v>6981417</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4503,7 +4503,7 @@
         <v>128890083</v>
       </c>
       <c r="B39" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>128890040</v>
       </c>
       <c r="B40" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>128884082</v>
       </c>
       <c r="B41" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>128890022</v>
       </c>
       <c r="B42" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>128890031</v>
       </c>
       <c r="B43" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>128890045</v>
       </c>
       <c r="B44" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5097,45 +5097,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890024</v>
+        <v>128890104</v>
       </c>
       <c r="B45" t="n">
-        <v>91523</v>
+        <v>82994</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515219</v>
+        <v>515070</v>
       </c>
       <c r="R45" t="n">
-        <v>6981419</v>
+        <v>6981365</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,6 +5170,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5182,60 +5187,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890104</v>
+        <v>128884117</v>
       </c>
       <c r="B46" t="n">
-        <v>82993</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R46" t="n">
-        <v>6981365</v>
+        <v>6981204</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5262,14 +5267,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,60 +5294,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128884117</v>
+        <v>128890103</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515013</v>
+        <v>515126</v>
       </c>
       <c r="R47" t="n">
-        <v>6981204</v>
+        <v>6981385</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5364,19 +5374,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5391,22 +5396,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890090</v>
+        <v>128890024</v>
       </c>
       <c r="B48" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5414,34 +5419,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515013</v>
+        <v>515219</v>
       </c>
       <c r="R48" t="n">
-        <v>6981245</v>
+        <v>6981419</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5476,11 +5481,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5493,22 +5493,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128884114</v>
+        <v>128890090</v>
       </c>
       <c r="B49" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5536,17 +5536,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515018</v>
+        <v>515013</v>
       </c>
       <c r="R49" t="n">
-        <v>6981240</v>
+        <v>6981245</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5573,19 +5573,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5600,60 +5595,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890103</v>
+        <v>128884114</v>
       </c>
       <c r="B50" t="n">
-        <v>98656</v>
+        <v>80140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515126</v>
+        <v>515018</v>
       </c>
       <c r="R50" t="n">
-        <v>6981385</v>
+        <v>6981240</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5680,14 +5675,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5702,60 +5702,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128884086</v>
+        <v>128890098</v>
       </c>
       <c r="B51" t="n">
-        <v>58093</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515225</v>
+        <v>515031</v>
       </c>
       <c r="R51" t="n">
-        <v>6981406</v>
+        <v>6981292</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5782,19 +5782,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:07</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5809,60 +5804,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890098</v>
+        <v>128884086</v>
       </c>
       <c r="B52" t="n">
-        <v>98656</v>
+        <v>58093</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515031</v>
+        <v>515225</v>
       </c>
       <c r="R52" t="n">
-        <v>6981292</v>
+        <v>6981406</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5889,14 +5884,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5911,22 +5911,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890041</v>
+        <v>128890034</v>
       </c>
       <c r="B53" t="n">
-        <v>80139</v>
+        <v>91811</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5934,21 +5934,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515196</v>
+        <v>515231</v>
       </c>
       <c r="R53" t="n">
-        <v>6981428</v>
+        <v>6981432</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,7 +6023,7 @@
         <v>128884080</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128890034</v>
+        <v>128890041</v>
       </c>
       <c r="B55" t="n">
-        <v>91808</v>
+        <v>80140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6138,21 +6138,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515231</v>
+        <v>515196</v>
       </c>
       <c r="R55" t="n">
-        <v>6981432</v>
+        <v>6981428</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6227,7 +6227,7 @@
         <v>128890025</v>
       </c>
       <c r="B56" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6321,48 +6321,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884100</v>
+        <v>128890105</v>
       </c>
       <c r="B57" t="n">
-        <v>80168</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515158</v>
+        <v>515054</v>
       </c>
       <c r="R57" t="n">
-        <v>6981405</v>
+        <v>6981308</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6389,19 +6389,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:25</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6416,22 +6411,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128890105</v>
+        <v>128884119</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6459,17 +6454,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515054</v>
+        <v>515196</v>
       </c>
       <c r="R58" t="n">
-        <v>6981308</v>
+        <v>6981382</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6496,14 +6491,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6518,22 +6518,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884119</v>
+        <v>128884090</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515196</v>
+        <v>515210</v>
       </c>
       <c r="R59" t="n">
-        <v>6981382</v>
+        <v>6981412</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6637,32 +6637,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884090</v>
+        <v>128884100</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>80169</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515210</v>
+        <v>515158</v>
       </c>
       <c r="R60" t="n">
-        <v>6981412</v>
+        <v>6981405</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6747,7 +6747,7 @@
         <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128890027</v>
+        <v>128884104</v>
       </c>
       <c r="B62" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515073</v>
+        <v>515104</v>
       </c>
       <c r="R62" t="n">
-        <v>6981343</v>
+        <v>6981353</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6909,14 +6909,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6931,22 +6936,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884104</v>
+        <v>128884095</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6978,10 +6983,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515104</v>
+        <v>515183</v>
       </c>
       <c r="R63" t="n">
-        <v>6981353</v>
+        <v>6981391</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7013,7 +7018,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7023,7 +7028,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7050,48 +7060,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128890082</v>
+        <v>128884113</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515014</v>
+        <v>515021</v>
       </c>
       <c r="R64" t="n">
-        <v>6981245</v>
+        <v>6981285</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7118,14 +7128,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rikligt på lodyta</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7140,22 +7160,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884099</v>
+        <v>128890027</v>
       </c>
       <c r="B65" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7163,37 +7183,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515158</v>
+        <v>515073</v>
       </c>
       <c r="R65" t="n">
-        <v>6981406</v>
+        <v>6981343</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7220,19 +7240,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7247,60 +7262,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884095</v>
+        <v>128890082</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>79121</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515183</v>
+        <v>515014</v>
       </c>
       <c r="R66" t="n">
-        <v>6981391</v>
+        <v>6981245</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7327,24 +7342,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7359,22 +7364,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884113</v>
+        <v>128884099</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7382,21 +7387,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7406,10 +7411,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515021</v>
+        <v>515158</v>
       </c>
       <c r="R67" t="n">
-        <v>6981285</v>
+        <v>6981406</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -7441,7 +7446,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7451,12 +7456,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7483,45 +7483,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890032</v>
+        <v>128890080</v>
       </c>
       <c r="B68" t="n">
-        <v>91978</v>
+        <v>80006</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515210</v>
+        <v>515188</v>
       </c>
       <c r="R68" t="n">
-        <v>6981426</v>
+        <v>6981440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,6 +7556,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7568,22 +7573,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890097</v>
+        <v>128890032</v>
       </c>
       <c r="B69" t="n">
-        <v>98656</v>
+        <v>91981</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7591,34 +7596,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515060</v>
+        <v>515210</v>
       </c>
       <c r="R69" t="n">
-        <v>6981339</v>
+        <v>6981426</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7653,11 +7658,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7670,44 +7670,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890075</v>
+        <v>128890077</v>
       </c>
       <c r="B70" t="n">
-        <v>105704</v>
+        <v>83011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515124</v>
+        <v>515057</v>
       </c>
       <c r="R70" t="n">
-        <v>6981387</v>
+        <v>6981333</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7784,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890080</v>
+        <v>128890097</v>
       </c>
       <c r="B71" t="n">
-        <v>80005</v>
+        <v>98659</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515188</v>
+        <v>515060</v>
       </c>
       <c r="R71" t="n">
-        <v>6981440</v>
+        <v>6981339</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890077</v>
+        <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>83010</v>
+        <v>105707</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515057</v>
+        <v>515124</v>
       </c>
       <c r="R72" t="n">
-        <v>6981333</v>
+        <v>6981387</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7991,7 +7991,7 @@
         <v>128890084</v>
       </c>
       <c r="B73" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>128884111</v>
       </c>
       <c r="B74" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>128884094</v>
       </c>
       <c r="B75" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>128890101</v>
       </c>
       <c r="B76" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8406,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890085</v>
+        <v>128890037</v>
       </c>
       <c r="B77" t="n">
-        <v>91808</v>
+        <v>80140</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515034</v>
+        <v>515026</v>
       </c>
       <c r="R77" t="n">
-        <v>6981293</v>
+        <v>6981261</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,11 +8479,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8496,22 +8491,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128890037</v>
+        <v>128884102</v>
       </c>
       <c r="B78" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8539,17 +8534,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515026</v>
+        <v>515111</v>
       </c>
       <c r="R78" t="n">
-        <v>6981261</v>
+        <v>6981360</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8576,9 +8571,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8593,22 +8598,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884102</v>
+        <v>128890085</v>
       </c>
       <c r="B79" t="n">
-        <v>80139</v>
+        <v>91811</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8616,37 +8621,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515111</v>
+        <v>515034</v>
       </c>
       <c r="R79" t="n">
-        <v>6981360</v>
+        <v>6981293</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8673,19 +8678,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,44 +8700,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890093</v>
+        <v>128890087</v>
       </c>
       <c r="B80" t="n">
-        <v>80006</v>
+        <v>80168</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>385</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515053</v>
+        <v>515014</v>
       </c>
       <c r="R80" t="n">
-        <v>6981314</v>
+        <v>6981245</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,48 +8814,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128890096</v>
+        <v>128884091</v>
       </c>
       <c r="B81" t="n">
-        <v>80099</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515014</v>
+        <v>515199</v>
       </c>
       <c r="R81" t="n">
-        <v>6981245</v>
+        <v>6981419</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8882,14 +8882,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8904,22 +8909,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884081</v>
+        <v>128890091</v>
       </c>
       <c r="B82" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8927,37 +8932,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515230</v>
+        <v>515069</v>
       </c>
       <c r="R82" t="n">
-        <v>6981431</v>
+        <v>6981349</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8984,19 +8989,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9011,57 +9011,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890087</v>
+        <v>128890038</v>
       </c>
       <c r="B83" t="n">
-        <v>80167</v>
+        <v>80140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515014</v>
+        <v>515041</v>
       </c>
       <c r="R83" t="n">
-        <v>6981245</v>
+        <v>6981296</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9096,11 +9096,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På lodyta</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9113,60 +9108,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884091</v>
+        <v>128890099</v>
       </c>
       <c r="B84" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515199</v>
+        <v>515054</v>
       </c>
       <c r="R84" t="n">
-        <v>6981419</v>
+        <v>6981308</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9193,19 +9188,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9220,22 +9210,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890091</v>
+        <v>128884081</v>
       </c>
       <c r="B85" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9243,37 +9233,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515069</v>
+        <v>515230</v>
       </c>
       <c r="R85" t="n">
-        <v>6981349</v>
+        <v>6981431</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9300,14 +9290,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9322,57 +9317,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890038</v>
+        <v>128890093</v>
       </c>
       <c r="B86" t="n">
-        <v>80139</v>
+        <v>80007</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515041</v>
+        <v>515053</v>
       </c>
       <c r="R86" t="n">
-        <v>6981296</v>
+        <v>6981314</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9407,6 +9402,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9419,44 +9419,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890099</v>
+        <v>128890096</v>
       </c>
       <c r="B87" t="n">
-        <v>98656</v>
+        <v>80100</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515054</v>
+        <v>515014</v>
       </c>
       <c r="R87" t="n">
-        <v>6981308</v>
+        <v>6981245</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128890092</v>
+        <v>128884101</v>
       </c>
       <c r="B3" t="n">
-        <v>80176</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515067</v>
+        <v>515135</v>
       </c>
       <c r="R3" t="n">
-        <v>6981353</v>
+        <v>6981381</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +850,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,60 +877,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884097</v>
+        <v>128890092</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515184</v>
+        <v>515067</v>
       </c>
       <c r="R4" t="n">
-        <v>6981392</v>
+        <v>6981353</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,19 +957,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:19</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884115</v>
+        <v>128884097</v>
       </c>
       <c r="B5" t="n">
-        <v>80100</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515019</v>
+        <v>515184</v>
       </c>
       <c r="R5" t="n">
-        <v>6981238</v>
+        <v>6981392</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128884101</v>
+        <v>128884115</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>80100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515135</v>
+        <v>515019</v>
       </c>
       <c r="R6" t="n">
-        <v>6981381</v>
+        <v>6981238</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1720,32 +1720,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890033</v>
+        <v>128890039</v>
       </c>
       <c r="B12" t="n">
-        <v>75027</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515018</v>
+        <v>515123</v>
       </c>
       <c r="R12" t="n">
-        <v>6981215</v>
+        <v>6981380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,48 +1817,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128884116</v>
+        <v>128890033</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>75027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515030</v>
+        <v>515018</v>
       </c>
       <c r="R13" t="n">
-        <v>6981199</v>
+        <v>6981215</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,19 +1885,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,60 +1902,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128890100</v>
+        <v>128884116</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515060</v>
+        <v>515030</v>
       </c>
       <c r="R14" t="n">
-        <v>6981326</v>
+        <v>6981199</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,14 +1982,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,57 +2009,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128890039</v>
+        <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515123</v>
+        <v>515060</v>
       </c>
       <c r="R15" t="n">
-        <v>6981380</v>
+        <v>6981326</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,6 +2094,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2111,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2843,48 +2843,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128884089</v>
+        <v>128890026</v>
       </c>
       <c r="B23" t="n">
-        <v>80169</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515218</v>
+        <v>515052</v>
       </c>
       <c r="R23" t="n">
-        <v>6981412</v>
+        <v>6981331</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2911,19 +2911,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:09</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2938,22 +2933,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884107</v>
+        <v>128884110</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>80006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,21 +2956,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2985,10 +2980,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515060</v>
+        <v>515038</v>
       </c>
       <c r="R24" t="n">
-        <v>6981336</v>
+        <v>6981305</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3020,7 +3015,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3030,7 +3025,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3057,48 +3052,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128890026</v>
+        <v>128884089</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>80169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515052</v>
+        <v>515218</v>
       </c>
       <c r="R25" t="n">
-        <v>6981331</v>
+        <v>6981412</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3125,14 +3120,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3147,22 +3147,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884110</v>
+        <v>128884107</v>
       </c>
       <c r="B26" t="n">
-        <v>80006</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515038</v>
+        <v>515060</v>
       </c>
       <c r="R26" t="n">
-        <v>6981305</v>
+        <v>6981336</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3266,32 +3266,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128890094</v>
+        <v>128890088</v>
       </c>
       <c r="B27" t="n">
-        <v>80007</v>
+        <v>79506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>385</v>
+        <v>1797</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515188</v>
+        <v>515103</v>
       </c>
       <c r="R27" t="n">
-        <v>6981440</v>
+        <v>6981364</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3368,32 +3368,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128890088</v>
+        <v>128890094</v>
       </c>
       <c r="B28" t="n">
-        <v>79506</v>
+        <v>80007</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1797</v>
+        <v>385</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515103</v>
+        <v>515188</v>
       </c>
       <c r="R28" t="n">
-        <v>6981364</v>
+        <v>6981440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3689,32 +3689,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128890043</v>
+        <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>80140</v>
+        <v>92231</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515166</v>
+        <v>515089</v>
       </c>
       <c r="R31" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,32 +3786,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128890029</v>
+        <v>128890043</v>
       </c>
       <c r="B32" t="n">
-        <v>92231</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515089</v>
+        <v>515166</v>
       </c>
       <c r="R32" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128890042</v>
+        <v>128890076</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>83011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>515180</v>
+        <v>514973</v>
       </c>
       <c r="R33" t="n">
-        <v>6981428</v>
+        <v>6981271</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3956,6 +3956,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3968,22 +3973,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128890076</v>
+        <v>128890042</v>
       </c>
       <c r="B34" t="n">
-        <v>83011</v>
+        <v>80140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3991,34 +3996,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514973</v>
+        <v>515180</v>
       </c>
       <c r="R34" t="n">
-        <v>6981271</v>
+        <v>6981428</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,11 +4058,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4070,12 +4070,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128884082</v>
+        <v>128890022</v>
       </c>
       <c r="B41" t="n">
-        <v>91811</v>
+        <v>96905</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515231</v>
+        <v>515029</v>
       </c>
       <c r="R41" t="n">
-        <v>6981417</v>
+        <v>6981199</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,19 +4767,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4794,22 +4784,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128890022</v>
+        <v>128884082</v>
       </c>
       <c r="B42" t="n">
-        <v>96905</v>
+        <v>91811</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4817,37 +4807,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515029</v>
+        <v>515231</v>
       </c>
       <c r="R42" t="n">
-        <v>6981199</v>
+        <v>6981417</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4874,9 +4864,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,12 +4891,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5097,32 +5097,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890104</v>
+        <v>128890103</v>
       </c>
       <c r="B45" t="n">
-        <v>82994</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515070</v>
+        <v>515126</v>
       </c>
       <c r="R45" t="n">
-        <v>6981365</v>
+        <v>6981385</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5199,10 +5199,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128884117</v>
+        <v>128890024</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5210,37 +5210,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515013</v>
+        <v>515219</v>
       </c>
       <c r="R46" t="n">
-        <v>6981204</v>
+        <v>6981419</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5267,19 +5267,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5294,44 +5284,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128890103</v>
+        <v>128890104</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>82994</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5341,10 +5331,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515126</v>
+        <v>515070</v>
       </c>
       <c r="R47" t="n">
-        <v>6981385</v>
+        <v>6981365</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5381,7 +5371,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5408,10 +5398,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890024</v>
+        <v>128884117</v>
       </c>
       <c r="B48" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,37 +5409,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515219</v>
+        <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981419</v>
+        <v>6981204</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5476,9 +5466,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5493,12 +5493,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5714,45 +5714,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890098</v>
+        <v>128890034</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515031</v>
+        <v>515231</v>
       </c>
       <c r="R51" t="n">
-        <v>6981292</v>
+        <v>6981432</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5787,11 +5787,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5804,60 +5799,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884086</v>
+        <v>128890041</v>
       </c>
       <c r="B52" t="n">
-        <v>58093</v>
+        <v>80140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515225</v>
+        <v>515196</v>
       </c>
       <c r="R52" t="n">
-        <v>6981406</v>
+        <v>6981428</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5884,19 +5879,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5911,60 +5896,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890034</v>
+        <v>128884086</v>
       </c>
       <c r="B53" t="n">
-        <v>91811</v>
+        <v>58093</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515231</v>
+        <v>515225</v>
       </c>
       <c r="R53" t="n">
-        <v>6981432</v>
+        <v>6981406</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5991,9 +5976,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6008,60 +6003,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884080</v>
+        <v>128890098</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515239</v>
+        <v>515031</v>
       </c>
       <c r="R54" t="n">
-        <v>6981443</v>
+        <v>6981292</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6088,19 +6083,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6115,22 +6105,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128890041</v>
+        <v>128884080</v>
       </c>
       <c r="B55" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6138,37 +6128,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515196</v>
+        <v>515239</v>
       </c>
       <c r="R55" t="n">
-        <v>6981428</v>
+        <v>6981443</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6195,9 +6185,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6212,60 +6212,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128890025</v>
+        <v>128884100</v>
       </c>
       <c r="B56" t="n">
-        <v>91526</v>
+        <v>80169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515214</v>
+        <v>515158</v>
       </c>
       <c r="R56" t="n">
-        <v>6981426</v>
+        <v>6981405</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6292,9 +6292,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6309,22 +6319,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128890105</v>
+        <v>128890025</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6332,34 +6342,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515054</v>
+        <v>515214</v>
       </c>
       <c r="R57" t="n">
-        <v>6981308</v>
+        <v>6981426</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6394,11 +6404,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6411,19 +6416,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884119</v>
+        <v>128890105</v>
       </c>
       <c r="B58" t="n">
         <v>79035</v>
@@ -6454,17 +6459,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515196</v>
+        <v>515054</v>
       </c>
       <c r="R58" t="n">
-        <v>6981382</v>
+        <v>6981308</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6491,19 +6496,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>16:26</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6518,19 +6518,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884090</v>
+        <v>128884119</v>
       </c>
       <c r="B59" t="n">
         <v>79035</v>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515210</v>
+        <v>515196</v>
       </c>
       <c r="R59" t="n">
-        <v>6981412</v>
+        <v>6981382</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6637,32 +6637,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884100</v>
+        <v>128884090</v>
       </c>
       <c r="B60" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515158</v>
+        <v>515210</v>
       </c>
       <c r="R60" t="n">
-        <v>6981405</v>
+        <v>6981412</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6744,10 +6744,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128890023</v>
+        <v>128884099</v>
       </c>
       <c r="B61" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6755,37 +6755,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515081</v>
+        <v>515158</v>
       </c>
       <c r="R61" t="n">
-        <v>6981324</v>
+        <v>6981406</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,9 +6812,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,22 +6839,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884104</v>
+        <v>128890027</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6852,37 +6862,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515104</v>
+        <v>515073</v>
       </c>
       <c r="R62" t="n">
-        <v>6981353</v>
+        <v>6981343</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6909,19 +6919,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6936,22 +6941,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884095</v>
+        <v>128890023</v>
       </c>
       <c r="B63" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6959,37 +6964,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515183</v>
+        <v>515081</v>
       </c>
       <c r="R63" t="n">
-        <v>6981391</v>
+        <v>6981324</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7016,24 +7021,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>nr 500</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7048,19 +7038,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884113</v>
+        <v>128884104</v>
       </c>
       <c r="B64" t="n">
         <v>79035</v>
@@ -7095,10 +7085,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515021</v>
+        <v>515104</v>
       </c>
       <c r="R64" t="n">
-        <v>6981285</v>
+        <v>6981353</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7130,7 +7120,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7140,12 +7130,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7172,45 +7157,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128890027</v>
+        <v>128890082</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>79121</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515073</v>
+        <v>515014</v>
       </c>
       <c r="R65" t="n">
-        <v>6981343</v>
+        <v>6981245</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7247,7 +7232,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7262,60 +7247,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128890082</v>
+        <v>128884095</v>
       </c>
       <c r="B66" t="n">
-        <v>79121</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515014</v>
+        <v>515183</v>
       </c>
       <c r="R66" t="n">
-        <v>6981245</v>
+        <v>6981391</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7342,14 +7327,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt på lodyta</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7364,22 +7359,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884099</v>
+        <v>128884113</v>
       </c>
       <c r="B67" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7387,21 +7382,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7411,10 +7406,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515158</v>
+        <v>515021</v>
       </c>
       <c r="R67" t="n">
-        <v>6981406</v>
+        <v>6981285</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -7446,7 +7441,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7456,7 +7451,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7483,32 +7483,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890080</v>
+        <v>128890097</v>
       </c>
       <c r="B68" t="n">
-        <v>80006</v>
+        <v>98659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515188</v>
+        <v>515060</v>
       </c>
       <c r="R68" t="n">
-        <v>6981440</v>
+        <v>6981339</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7585,45 +7585,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890032</v>
+        <v>128890080</v>
       </c>
       <c r="B69" t="n">
-        <v>91981</v>
+        <v>80006</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515210</v>
+        <v>515188</v>
       </c>
       <c r="R69" t="n">
-        <v>6981426</v>
+        <v>6981440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7658,6 +7658,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7670,57 +7675,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890077</v>
+        <v>128890032</v>
       </c>
       <c r="B70" t="n">
-        <v>83011</v>
+        <v>91981</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515057</v>
+        <v>515210</v>
       </c>
       <c r="R70" t="n">
-        <v>6981333</v>
+        <v>6981426</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7755,11 +7760,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På gammal gran i lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7772,44 +7772,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890097</v>
+        <v>128890077</v>
       </c>
       <c r="B71" t="n">
-        <v>98659</v>
+        <v>83011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515060</v>
+        <v>515057</v>
       </c>
       <c r="R71" t="n">
-        <v>6981339</v>
+        <v>6981333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7988,32 +7988,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128890084</v>
+        <v>128890101</v>
       </c>
       <c r="B73" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>515029</v>
+        <v>515108</v>
       </c>
       <c r="R73" t="n">
-        <v>6981276</v>
+        <v>6981372</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8090,10 +8090,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128884111</v>
+        <v>128890084</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8101,37 +8101,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515033</v>
+        <v>515029</v>
       </c>
       <c r="R74" t="n">
-        <v>6981298</v>
+        <v>6981276</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8158,19 +8158,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8185,19 +8180,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884094</v>
+        <v>128884111</v>
       </c>
       <c r="B75" t="n">
         <v>79035</v>
@@ -8232,10 +8227,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>515181</v>
+        <v>515033</v>
       </c>
       <c r="R75" t="n">
-        <v>6981416</v>
+        <v>6981298</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -8267,7 +8262,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8277,7 +8272,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8304,48 +8299,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128890101</v>
+        <v>128884094</v>
       </c>
       <c r="B76" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515108</v>
+        <v>515181</v>
       </c>
       <c r="R76" t="n">
-        <v>6981372</v>
+        <v>6981416</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8372,14 +8367,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>16 plantor på marken i gammal granskog</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,22 +8394,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890037</v>
+        <v>128890085</v>
       </c>
       <c r="B77" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515026</v>
+        <v>515034</v>
       </c>
       <c r="R77" t="n">
-        <v>6981261</v>
+        <v>6981293</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,6 +8479,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8491,12 +8496,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8610,10 +8615,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128890085</v>
+        <v>128890037</v>
       </c>
       <c r="B79" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8621,34 +8626,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515034</v>
+        <v>515026</v>
       </c>
       <c r="R79" t="n">
-        <v>6981293</v>
+        <v>6981261</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8683,11 +8688,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8700,22 +8700,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890087</v>
+        <v>128890096</v>
       </c>
       <c r="B80" t="n">
-        <v>80168</v>
+        <v>80100</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8723,21 +8723,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>229497</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På lodyta</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,48 +8814,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884091</v>
+        <v>128890093</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>80007</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515199</v>
+        <v>515053</v>
       </c>
       <c r="R81" t="n">
-        <v>6981419</v>
+        <v>6981314</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8882,19 +8882,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8909,22 +8904,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128890091</v>
+        <v>128884081</v>
       </c>
       <c r="B82" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8932,37 +8927,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515069</v>
+        <v>515230</v>
       </c>
       <c r="R82" t="n">
-        <v>6981349</v>
+        <v>6981431</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8989,14 +8984,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9011,57 +9011,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890038</v>
+        <v>128890087</v>
       </c>
       <c r="B83" t="n">
-        <v>80140</v>
+        <v>80168</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515041</v>
+        <v>515014</v>
       </c>
       <c r="R83" t="n">
-        <v>6981296</v>
+        <v>6981245</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9096,6 +9096,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På lodyta</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9108,60 +9113,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890099</v>
+        <v>128884091</v>
       </c>
       <c r="B84" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515054</v>
+        <v>515199</v>
       </c>
       <c r="R84" t="n">
-        <v>6981308</v>
+        <v>6981419</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9188,14 +9193,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9210,22 +9220,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884081</v>
+        <v>128890091</v>
       </c>
       <c r="B85" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9233,37 +9243,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515230</v>
+        <v>515069</v>
       </c>
       <c r="R85" t="n">
-        <v>6981431</v>
+        <v>6981349</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9290,19 +9300,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9317,57 +9322,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890093</v>
+        <v>128890038</v>
       </c>
       <c r="B86" t="n">
-        <v>80007</v>
+        <v>80140</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515053</v>
+        <v>515041</v>
       </c>
       <c r="R86" t="n">
-        <v>6981314</v>
+        <v>6981296</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9402,11 +9407,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9419,44 +9419,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890096</v>
+        <v>128890099</v>
       </c>
       <c r="B87" t="n">
-        <v>80100</v>
+        <v>98659</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515014</v>
+        <v>515054</v>
       </c>
       <c r="R87" t="n">
-        <v>6981245</v>
+        <v>6981308</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128890079</v>
+        <v>128890102</v>
       </c>
       <c r="B7" t="n">
-        <v>91491</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515071</v>
+        <v>515229</v>
       </c>
       <c r="R7" t="n">
-        <v>6981351</v>
+        <v>6981403</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>50 plantor i i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128890102</v>
+        <v>128890079</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>91491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515229</v>
+        <v>515071</v>
       </c>
       <c r="R8" t="n">
-        <v>6981403</v>
+        <v>6981351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>50 plantor i i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890039</v>
+        <v>128890100</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515123</v>
+        <v>515060</v>
       </c>
       <c r="R12" t="n">
-        <v>6981380</v>
+        <v>6981326</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1793,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1805,44 +1810,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890033</v>
+        <v>128890039</v>
       </c>
       <c r="B13" t="n">
-        <v>75027</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515018</v>
+        <v>515123</v>
       </c>
       <c r="R13" t="n">
-        <v>6981215</v>
+        <v>6981380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,48 +1919,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128884116</v>
+        <v>128890033</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>75027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515030</v>
+        <v>515018</v>
       </c>
       <c r="R14" t="n">
-        <v>6981199</v>
+        <v>6981215</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,19 +1987,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,60 +2004,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128890100</v>
+        <v>128884116</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515060</v>
+        <v>515030</v>
       </c>
       <c r="R15" t="n">
-        <v>6981326</v>
+        <v>6981199</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2089,14 +2084,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,22 +2111,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128884079</v>
+        <v>128890028</v>
       </c>
       <c r="B16" t="n">
-        <v>78048</v>
+        <v>80006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515240</v>
+        <v>515039</v>
       </c>
       <c r="R16" t="n">
-        <v>6981445</v>
+        <v>6981285</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,46 +2191,37 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890028</v>
+        <v>128890081</v>
       </c>
       <c r="B17" t="n">
         <v>80006</v>
@@ -2261,14 +2252,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515039</v>
+        <v>515203</v>
       </c>
       <c r="R17" t="n">
-        <v>6981285</v>
+        <v>6981449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2303,35 +2294,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128890081</v>
+        <v>128884105</v>
       </c>
       <c r="B18" t="n">
-        <v>80006</v>
+        <v>80140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,37 +2334,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515203</v>
+        <v>515069</v>
       </c>
       <c r="R18" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2396,14 +2391,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,22 +2418,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128884105</v>
+        <v>128884079</v>
       </c>
       <c r="B19" t="n">
-        <v>80140</v>
+        <v>78048</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515069</v>
+        <v>515240</v>
       </c>
       <c r="R19" t="n">
-        <v>6981348</v>
+        <v>6981445</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2843,48 +2843,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128890026</v>
+        <v>128884089</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>80169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515052</v>
+        <v>515218</v>
       </c>
       <c r="R23" t="n">
-        <v>6981331</v>
+        <v>6981412</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2911,14 +2911,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2933,22 +2938,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884110</v>
+        <v>128884107</v>
       </c>
       <c r="B24" t="n">
-        <v>80006</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,21 +2961,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2980,10 +2985,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515038</v>
+        <v>515060</v>
       </c>
       <c r="R24" t="n">
-        <v>6981305</v>
+        <v>6981336</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3015,7 +3020,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3025,7 +3030,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3052,48 +3057,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884089</v>
+        <v>128890026</v>
       </c>
       <c r="B25" t="n">
-        <v>80169</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515218</v>
+        <v>515052</v>
       </c>
       <c r="R25" t="n">
-        <v>6981412</v>
+        <v>6981331</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3120,19 +3125,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:09</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3147,22 +3147,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884107</v>
+        <v>128884110</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>80006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515060</v>
+        <v>515038</v>
       </c>
       <c r="R26" t="n">
-        <v>6981336</v>
+        <v>6981305</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4699,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128890022</v>
+        <v>128884082</v>
       </c>
       <c r="B41" t="n">
-        <v>96905</v>
+        <v>91811</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515029</v>
+        <v>515231</v>
       </c>
       <c r="R41" t="n">
-        <v>6981199</v>
+        <v>6981417</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,9 +4767,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4784,60 +4794,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128884082</v>
+        <v>128890031</v>
       </c>
       <c r="B42" t="n">
-        <v>91811</v>
+        <v>80044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515231</v>
+        <v>515039</v>
       </c>
       <c r="R42" t="n">
-        <v>6981417</v>
+        <v>6981314</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4864,19 +4874,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,44 +4891,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128890031</v>
+        <v>128890022</v>
       </c>
       <c r="B43" t="n">
-        <v>80044</v>
+        <v>96905</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515039</v>
+        <v>515029</v>
       </c>
       <c r="R43" t="n">
-        <v>6981314</v>
+        <v>6981199</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -7483,32 +7483,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890097</v>
+        <v>128890080</v>
       </c>
       <c r="B68" t="n">
-        <v>98659</v>
+        <v>80006</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515060</v>
+        <v>515188</v>
       </c>
       <c r="R68" t="n">
-        <v>6981339</v>
+        <v>6981440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7585,45 +7585,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890080</v>
+        <v>128890032</v>
       </c>
       <c r="B69" t="n">
-        <v>80006</v>
+        <v>91981</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515188</v>
+        <v>515210</v>
       </c>
       <c r="R69" t="n">
-        <v>6981440</v>
+        <v>6981426</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7658,11 +7658,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7675,57 +7670,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890032</v>
+        <v>128890077</v>
       </c>
       <c r="B70" t="n">
-        <v>91981</v>
+        <v>83011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515210</v>
+        <v>515057</v>
       </c>
       <c r="R70" t="n">
-        <v>6981426</v>
+        <v>6981333</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7760,6 +7755,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På gammal gran i lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7772,44 +7772,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890077</v>
+        <v>128890075</v>
       </c>
       <c r="B71" t="n">
-        <v>83011</v>
+        <v>105707</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515057</v>
+        <v>515124</v>
       </c>
       <c r="R71" t="n">
-        <v>6981333</v>
+        <v>6981387</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890075</v>
+        <v>128890097</v>
       </c>
       <c r="B72" t="n">
-        <v>105707</v>
+        <v>98659</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515124</v>
+        <v>515060</v>
       </c>
       <c r="R72" t="n">
-        <v>6981387</v>
+        <v>6981339</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8508,7 +8508,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884102</v>
+        <v>128890037</v>
       </c>
       <c r="B78" t="n">
         <v>80140</v>
@@ -8539,17 +8539,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515111</v>
+        <v>515026</v>
       </c>
       <c r="R78" t="n">
-        <v>6981360</v>
+        <v>6981261</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8576,19 +8576,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8603,19 +8593,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128890037</v>
+        <v>128884102</v>
       </c>
       <c r="B79" t="n">
         <v>80140</v>
@@ -8646,17 +8636,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515026</v>
+        <v>515111</v>
       </c>
       <c r="R79" t="n">
-        <v>6981261</v>
+        <v>6981360</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8683,9 +8673,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,44 +8700,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890096</v>
+        <v>128890099</v>
       </c>
       <c r="B80" t="n">
-        <v>80100</v>
+        <v>98659</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515014</v>
+        <v>515054</v>
       </c>
       <c r="R80" t="n">
-        <v>6981245</v>
+        <v>6981308</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9431,32 +9431,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890099</v>
+        <v>128890096</v>
       </c>
       <c r="B87" t="n">
-        <v>98659</v>
+        <v>80100</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515054</v>
+        <v>515014</v>
       </c>
       <c r="R87" t="n">
-        <v>6981308</v>
+        <v>6981245</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884109</v>
+        <v>128890092</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>80176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515053</v>
+        <v>515067</v>
       </c>
       <c r="R2" t="n">
-        <v>6981306</v>
+        <v>6981353</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:44</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884101</v>
+        <v>128884097</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515135</v>
+        <v>515184</v>
       </c>
       <c r="R3" t="n">
-        <v>6981381</v>
+        <v>6981392</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,48 +884,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128890092</v>
+        <v>128884109</v>
       </c>
       <c r="B4" t="n">
-        <v>80176</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515067</v>
+        <v>515053</v>
       </c>
       <c r="R4" t="n">
-        <v>6981353</v>
+        <v>6981306</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,14 +952,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884097</v>
+        <v>128884101</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515184</v>
+        <v>515135</v>
       </c>
       <c r="R5" t="n">
-        <v>6981392</v>
+        <v>6981381</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128890102</v>
+        <v>128890079</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>91491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515229</v>
+        <v>515071</v>
       </c>
       <c r="R7" t="n">
-        <v>6981403</v>
+        <v>6981351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>50 plantor i i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128890079</v>
+        <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>91491</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515071</v>
+        <v>515229</v>
       </c>
       <c r="R8" t="n">
-        <v>6981351</v>
+        <v>6981403</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>50 plantor i i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884087</v>
+        <v>128884093</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>105707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515217</v>
+        <v>515174</v>
       </c>
       <c r="R9" t="n">
-        <v>6981406</v>
+        <v>6981416</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128890036</v>
+        <v>128884087</v>
       </c>
       <c r="B10" t="n">
         <v>80140</v>
@@ -1547,17 +1547,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515018</v>
+        <v>515217</v>
       </c>
       <c r="R10" t="n">
-        <v>6981217</v>
+        <v>6981406</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,9 +1584,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,60 +1611,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128884093</v>
+        <v>128890036</v>
       </c>
       <c r="B11" t="n">
-        <v>105707</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515174</v>
+        <v>515018</v>
       </c>
       <c r="R11" t="n">
-        <v>6981416</v>
+        <v>6981217</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1681,19 +1691,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,57 +1708,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890100</v>
+        <v>128890033</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>75027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515060</v>
+        <v>515018</v>
       </c>
       <c r="R12" t="n">
-        <v>6981326</v>
+        <v>6981215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,11 +1793,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1810,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890039</v>
+        <v>128884116</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,37 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515123</v>
+        <v>515030</v>
       </c>
       <c r="R13" t="n">
-        <v>6981380</v>
+        <v>6981199</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1890,9 +1885,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,44 +1912,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128890033</v>
+        <v>128890039</v>
       </c>
       <c r="B14" t="n">
-        <v>75027</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515018</v>
+        <v>515123</v>
       </c>
       <c r="R14" t="n">
-        <v>6981215</v>
+        <v>6981380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,48 +2021,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128884116</v>
+        <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515030</v>
+        <v>515060</v>
       </c>
       <c r="R15" t="n">
-        <v>6981199</v>
+        <v>6981326</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2084,19 +2089,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:07</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,22 +2111,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128890028</v>
+        <v>128884105</v>
       </c>
       <c r="B16" t="n">
-        <v>80006</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515039</v>
+        <v>515069</v>
       </c>
       <c r="R16" t="n">
-        <v>6981285</v>
+        <v>6981348</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,40 +2191,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890081</v>
+        <v>128884079</v>
       </c>
       <c r="B17" t="n">
-        <v>80006</v>
+        <v>78048</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,37 +2241,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>388</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515203</v>
+        <v>515240</v>
       </c>
       <c r="R17" t="n">
-        <v>6981449</v>
+        <v>6981445</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2289,14 +2298,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2311,22 +2325,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128884105</v>
+        <v>128890028</v>
       </c>
       <c r="B18" t="n">
-        <v>80140</v>
+        <v>80006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2334,37 +2348,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515069</v>
+        <v>515039</v>
       </c>
       <c r="R18" t="n">
-        <v>6981348</v>
+        <v>6981285</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2391,49 +2405,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128884079</v>
+        <v>128890081</v>
       </c>
       <c r="B19" t="n">
-        <v>78048</v>
+        <v>80006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,37 +2446,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515240</v>
+        <v>515203</v>
       </c>
       <c r="R19" t="n">
-        <v>6981445</v>
+        <v>6981449</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2498,19 +2503,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,22 +2525,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128890095</v>
+        <v>128890026</v>
       </c>
       <c r="B20" t="n">
-        <v>92329</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,34 +2548,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515145</v>
+        <v>515052</v>
       </c>
       <c r="R20" t="n">
-        <v>6981384</v>
+        <v>6981331</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gråalslåga i gransumpskog</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,22 +2627,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128890030</v>
+        <v>128884110</v>
       </c>
       <c r="B21" t="n">
-        <v>80141</v>
+        <v>80006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,37 +2650,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>388</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515032</v>
+        <v>515038</v>
       </c>
       <c r="R21" t="n">
-        <v>6981265</v>
+        <v>6981305</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2707,9 +2707,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,22 +2734,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884084</v>
+        <v>128890095</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>92329</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2747,37 +2757,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515227</v>
+        <v>515145</v>
       </c>
       <c r="R22" t="n">
-        <v>6981418</v>
+        <v>6981384</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2804,19 +2814,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:05</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2831,60 +2836,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128884089</v>
+        <v>128890030</v>
       </c>
       <c r="B23" t="n">
-        <v>80169</v>
+        <v>80141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515218</v>
+        <v>515032</v>
       </c>
       <c r="R23" t="n">
-        <v>6981412</v>
+        <v>6981265</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2911,19 +2916,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2938,22 +2933,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884107</v>
+        <v>128884084</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,21 +2956,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2985,10 +2980,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515060</v>
+        <v>515227</v>
       </c>
       <c r="R24" t="n">
-        <v>6981336</v>
+        <v>6981418</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3020,7 +3015,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3030,7 +3025,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3057,48 +3052,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128890026</v>
+        <v>128884089</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>80169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515052</v>
+        <v>515218</v>
       </c>
       <c r="R25" t="n">
-        <v>6981331</v>
+        <v>6981412</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3125,14 +3120,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3147,22 +3147,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884110</v>
+        <v>128884107</v>
       </c>
       <c r="B26" t="n">
-        <v>80006</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515038</v>
+        <v>515060</v>
       </c>
       <c r="R26" t="n">
-        <v>6981305</v>
+        <v>6981336</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,48 +3368,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128890094</v>
+        <v>128884103</v>
       </c>
       <c r="B28" t="n">
-        <v>80007</v>
+        <v>80169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>385</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515188</v>
+        <v>515108</v>
       </c>
       <c r="R28" t="n">
-        <v>6981440</v>
+        <v>6981358</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3436,14 +3436,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3458,60 +3463,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128884103</v>
+        <v>128890094</v>
       </c>
       <c r="B29" t="n">
-        <v>80169</v>
+        <v>80007</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>385</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515108</v>
+        <v>515188</v>
       </c>
       <c r="R29" t="n">
-        <v>6981358</v>
+        <v>6981440</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3538,19 +3543,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3565,12 +3565,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128890076</v>
+        <v>128890042</v>
       </c>
       <c r="B33" t="n">
-        <v>83011</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514973</v>
+        <v>515180</v>
       </c>
       <c r="R33" t="n">
-        <v>6981271</v>
+        <v>6981428</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3956,11 +3956,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3973,19 +3968,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128890042</v>
+        <v>128890035</v>
       </c>
       <c r="B34" t="n">
         <v>80140</v>
@@ -4020,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>515180</v>
+        <v>515031</v>
       </c>
       <c r="R34" t="n">
-        <v>6981428</v>
+        <v>6981191</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4082,10 +4077,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128890035</v>
+        <v>128890076</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>83011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,34 +4088,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>515031</v>
+        <v>514973</v>
       </c>
       <c r="R35" t="n">
-        <v>6981191</v>
+        <v>6981271</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4167,44 +4167,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128884098</v>
+        <v>128884083</v>
       </c>
       <c r="B36" t="n">
-        <v>79291</v>
+        <v>91526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6459</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>515158</v>
+        <v>515231</v>
       </c>
       <c r="R36" t="n">
-        <v>6981406</v>
+        <v>6981417</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4286,32 +4286,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128884092</v>
+        <v>128884098</v>
       </c>
       <c r="B37" t="n">
-        <v>80140</v>
+        <v>79291</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>515180</v>
+        <v>515158</v>
       </c>
       <c r="R37" t="n">
-        <v>6981435</v>
+        <v>6981406</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4393,10 +4393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128884083</v>
+        <v>128884092</v>
       </c>
       <c r="B38" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4404,21 +4404,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>515231</v>
+        <v>515180</v>
       </c>
       <c r="R38" t="n">
-        <v>6981417</v>
+        <v>6981435</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4699,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128884082</v>
+        <v>128890022</v>
       </c>
       <c r="B41" t="n">
-        <v>91811</v>
+        <v>96905</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515231</v>
+        <v>515029</v>
       </c>
       <c r="R41" t="n">
-        <v>6981417</v>
+        <v>6981199</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,19 +4767,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4794,60 +4784,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128890031</v>
+        <v>128884082</v>
       </c>
       <c r="B42" t="n">
-        <v>80044</v>
+        <v>91811</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515039</v>
+        <v>515231</v>
       </c>
       <c r="R42" t="n">
-        <v>6981314</v>
+        <v>6981417</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4874,9 +4864,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,44 +4891,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128890022</v>
+        <v>128890031</v>
       </c>
       <c r="B43" t="n">
-        <v>96905</v>
+        <v>80044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515029</v>
+        <v>515039</v>
       </c>
       <c r="R43" t="n">
-        <v>6981199</v>
+        <v>6981314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5097,45 +5097,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890103</v>
+        <v>128890024</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515126</v>
+        <v>515219</v>
       </c>
       <c r="R45" t="n">
-        <v>6981385</v>
+        <v>6981419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,11 +5170,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5187,22 +5182,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890024</v>
+        <v>128884114</v>
       </c>
       <c r="B46" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5210,37 +5205,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515219</v>
+        <v>515018</v>
       </c>
       <c r="R46" t="n">
-        <v>6981419</v>
+        <v>6981240</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5267,9 +5262,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,60 +5289,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128890104</v>
+        <v>128884117</v>
       </c>
       <c r="B47" t="n">
-        <v>82994</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R47" t="n">
-        <v>6981365</v>
+        <v>6981204</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5364,14 +5369,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5386,60 +5396,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128884117</v>
+        <v>128890104</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>82994</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515013</v>
+        <v>515070</v>
       </c>
       <c r="R48" t="n">
-        <v>6981204</v>
+        <v>6981365</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5466,19 +5476,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5493,12 +5498,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5607,48 +5612,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128884114</v>
+        <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515018</v>
+        <v>515126</v>
       </c>
       <c r="R50" t="n">
-        <v>6981240</v>
+        <v>6981385</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5675,19 +5680,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5702,12 +5702,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890041</v>
+        <v>128884080</v>
       </c>
       <c r="B52" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5822,37 +5822,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515196</v>
+        <v>515239</v>
       </c>
       <c r="R52" t="n">
-        <v>6981428</v>
+        <v>6981443</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5879,9 +5879,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5896,60 +5906,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884086</v>
+        <v>128890041</v>
       </c>
       <c r="B53" t="n">
-        <v>58093</v>
+        <v>80140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515225</v>
+        <v>515196</v>
       </c>
       <c r="R53" t="n">
-        <v>6981406</v>
+        <v>6981428</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5976,19 +5986,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6003,60 +6003,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128890098</v>
+        <v>128884086</v>
       </c>
       <c r="B54" t="n">
-        <v>98659</v>
+        <v>58093</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515031</v>
+        <v>515225</v>
       </c>
       <c r="R54" t="n">
-        <v>6981292</v>
+        <v>6981406</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6083,14 +6083,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6105,60 +6110,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128884080</v>
+        <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515239</v>
+        <v>515031</v>
       </c>
       <c r="R55" t="n">
-        <v>6981443</v>
+        <v>6981292</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6185,19 +6190,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6212,60 +6212,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884100</v>
+        <v>128890105</v>
       </c>
       <c r="B56" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515158</v>
+        <v>515054</v>
       </c>
       <c r="R56" t="n">
-        <v>6981405</v>
+        <v>6981308</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6292,19 +6292,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:25</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6319,22 +6314,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128890025</v>
+        <v>128884119</v>
       </c>
       <c r="B57" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6342,37 +6337,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515214</v>
+        <v>515196</v>
       </c>
       <c r="R57" t="n">
-        <v>6981426</v>
+        <v>6981382</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6399,9 +6394,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6416,19 +6421,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128890105</v>
+        <v>128884090</v>
       </c>
       <c r="B58" t="n">
         <v>79035</v>
@@ -6459,17 +6464,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515054</v>
+        <v>515210</v>
       </c>
       <c r="R58" t="n">
-        <v>6981308</v>
+        <v>6981412</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6496,14 +6501,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6518,44 +6528,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884119</v>
+        <v>128884100</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6565,10 +6575,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515196</v>
+        <v>515158</v>
       </c>
       <c r="R59" t="n">
-        <v>6981382</v>
+        <v>6981405</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6600,7 +6610,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6610,7 +6620,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6637,10 +6647,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884090</v>
+        <v>128890025</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6648,37 +6658,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515210</v>
+        <v>515214</v>
       </c>
       <c r="R60" t="n">
-        <v>6981412</v>
+        <v>6981426</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6705,19 +6715,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6732,60 +6732,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884099</v>
+        <v>128890082</v>
       </c>
       <c r="B61" t="n">
-        <v>80140</v>
+        <v>79121</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515158</v>
+        <v>515014</v>
       </c>
       <c r="R61" t="n">
-        <v>6981406</v>
+        <v>6981245</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,19 +6812,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6839,22 +6834,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128890027</v>
+        <v>128884099</v>
       </c>
       <c r="B62" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6862,37 +6857,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515073</v>
+        <v>515158</v>
       </c>
       <c r="R62" t="n">
-        <v>6981343</v>
+        <v>6981406</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6919,14 +6914,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,22 +6941,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128890023</v>
+        <v>128890027</v>
       </c>
       <c r="B63" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6964,21 +6964,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515081</v>
+        <v>515073</v>
       </c>
       <c r="R63" t="n">
-        <v>6981324</v>
+        <v>6981343</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7024,6 +7024,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7050,10 +7055,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884104</v>
+        <v>128890023</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7061,37 +7066,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515104</v>
+        <v>515081</v>
       </c>
       <c r="R64" t="n">
-        <v>6981353</v>
+        <v>6981324</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7118,19 +7123,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7145,60 +7140,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128890082</v>
+        <v>128884104</v>
       </c>
       <c r="B65" t="n">
-        <v>79121</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515014</v>
+        <v>515104</v>
       </c>
       <c r="R65" t="n">
-        <v>6981245</v>
+        <v>6981353</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7225,14 +7220,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7247,12 +7247,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7483,45 +7483,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890080</v>
+        <v>128890032</v>
       </c>
       <c r="B68" t="n">
-        <v>80006</v>
+        <v>91981</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515188</v>
+        <v>515210</v>
       </c>
       <c r="R68" t="n">
-        <v>6981440</v>
+        <v>6981426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,11 +7556,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7573,57 +7568,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890032</v>
+        <v>128890077</v>
       </c>
       <c r="B69" t="n">
-        <v>91981</v>
+        <v>83011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515210</v>
+        <v>515057</v>
       </c>
       <c r="R69" t="n">
-        <v>6981426</v>
+        <v>6981333</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7658,6 +7653,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På gammal gran i lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7670,22 +7670,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890077</v>
+        <v>128890080</v>
       </c>
       <c r="B70" t="n">
-        <v>83011</v>
+        <v>80006</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7693,21 +7693,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>388</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515057</v>
+        <v>515188</v>
       </c>
       <c r="R70" t="n">
-        <v>6981333</v>
+        <v>6981440</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7784,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890075</v>
+        <v>128890097</v>
       </c>
       <c r="B71" t="n">
-        <v>105707</v>
+        <v>98659</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515124</v>
+        <v>515060</v>
       </c>
       <c r="R71" t="n">
-        <v>6981387</v>
+        <v>6981339</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890097</v>
+        <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>98659</v>
+        <v>105707</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515060</v>
+        <v>515124</v>
       </c>
       <c r="R72" t="n">
-        <v>6981339</v>
+        <v>6981387</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,48 +7988,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128890101</v>
+        <v>128884111</v>
       </c>
       <c r="B73" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>515108</v>
+        <v>515033</v>
       </c>
       <c r="R73" t="n">
-        <v>6981372</v>
+        <v>6981298</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8056,14 +8056,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>16 plantor på marken i gammal granskog</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8078,22 +8083,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128890084</v>
+        <v>128884094</v>
       </c>
       <c r="B74" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8101,37 +8106,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515029</v>
+        <v>515181</v>
       </c>
       <c r="R74" t="n">
-        <v>6981276</v>
+        <v>6981416</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8158,14 +8163,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8180,22 +8190,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884111</v>
+        <v>128890084</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8203,37 +8213,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>515033</v>
+        <v>515029</v>
       </c>
       <c r="R75" t="n">
-        <v>6981298</v>
+        <v>6981276</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8260,19 +8270,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8287,60 +8292,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884094</v>
+        <v>128890101</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515181</v>
+        <v>515108</v>
       </c>
       <c r="R76" t="n">
-        <v>6981416</v>
+        <v>6981372</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8367,19 +8372,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,22 +8394,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890085</v>
+        <v>128890037</v>
       </c>
       <c r="B77" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515034</v>
+        <v>515026</v>
       </c>
       <c r="R77" t="n">
-        <v>6981293</v>
+        <v>6981261</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,11 +8479,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8496,22 +8491,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128890037</v>
+        <v>128890085</v>
       </c>
       <c r="B78" t="n">
-        <v>80140</v>
+        <v>91811</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8519,34 +8514,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515026</v>
+        <v>515034</v>
       </c>
       <c r="R78" t="n">
-        <v>6981261</v>
+        <v>6981293</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8581,6 +8576,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8593,12 +8593,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8712,10 +8712,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890099</v>
+        <v>128890093</v>
       </c>
       <c r="B80" t="n">
-        <v>98659</v>
+        <v>80007</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8723,21 +8723,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>385</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515054</v>
+        <v>515053</v>
       </c>
       <c r="R80" t="n">
-        <v>6981308</v>
+        <v>6981314</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,48 +8814,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128890093</v>
+        <v>128884081</v>
       </c>
       <c r="B81" t="n">
-        <v>80007</v>
+        <v>91526</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>385</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515053</v>
+        <v>515230</v>
       </c>
       <c r="R81" t="n">
-        <v>6981314</v>
+        <v>6981431</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8882,14 +8882,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8904,22 +8909,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884081</v>
+        <v>128884091</v>
       </c>
       <c r="B82" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8927,21 +8932,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8951,10 +8956,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515230</v>
+        <v>515199</v>
       </c>
       <c r="R82" t="n">
-        <v>6981431</v>
+        <v>6981419</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -8986,7 +8991,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8996,7 +9001,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9023,32 +9028,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890087</v>
+        <v>128890091</v>
       </c>
       <c r="B83" t="n">
-        <v>80168</v>
+        <v>80140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9058,10 +9063,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515014</v>
+        <v>515069</v>
       </c>
       <c r="R83" t="n">
-        <v>6981245</v>
+        <v>6981349</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9098,7 +9103,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På lodyta</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9125,7 +9130,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884091</v>
+        <v>128890038</v>
       </c>
       <c r="B84" t="n">
         <v>80140</v>
@@ -9156,17 +9161,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515199</v>
+        <v>515041</v>
       </c>
       <c r="R84" t="n">
-        <v>6981419</v>
+        <v>6981296</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9193,19 +9198,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9220,44 +9215,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890091</v>
+        <v>128890087</v>
       </c>
       <c r="B85" t="n">
-        <v>80140</v>
+        <v>80168</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9267,10 +9262,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515069</v>
+        <v>515014</v>
       </c>
       <c r="R85" t="n">
-        <v>6981349</v>
+        <v>6981245</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9307,7 +9302,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9334,45 +9329,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890038</v>
+        <v>128890099</v>
       </c>
       <c r="B86" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515041</v>
+        <v>515054</v>
       </c>
       <c r="R86" t="n">
-        <v>6981296</v>
+        <v>6981308</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9407,6 +9402,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På marken 13 plantor i lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9419,12 +9419,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128890092</v>
+        <v>128884109</v>
       </c>
       <c r="B2" t="n">
-        <v>80176</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515067</v>
+        <v>515053</v>
       </c>
       <c r="R2" t="n">
-        <v>6981353</v>
+        <v>6981306</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +743,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884097</v>
+        <v>128884101</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515184</v>
+        <v>515135</v>
       </c>
       <c r="R3" t="n">
-        <v>6981392</v>
+        <v>6981381</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884109</v>
+        <v>128884097</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515053</v>
+        <v>515184</v>
       </c>
       <c r="R4" t="n">
-        <v>6981306</v>
+        <v>6981392</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -954,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,48 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884101</v>
+        <v>128890092</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>80180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515135</v>
+        <v>515067</v>
       </c>
       <c r="R5" t="n">
-        <v>6981381</v>
+        <v>6981353</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,19 +1064,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:29</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,12 +1086,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
         <v>128884115</v>
       </c>
       <c r="B6" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128890079</v>
       </c>
       <c r="B7" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>128884093</v>
       </c>
       <c r="B9" t="n">
-        <v>105707</v>
+        <v>105717</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>128884087</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>128890036</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128890033</v>
       </c>
       <c r="B12" t="n">
-        <v>75027</v>
+        <v>75029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128884116</v>
+        <v>128890039</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,37 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515030</v>
+        <v>515123</v>
       </c>
       <c r="R13" t="n">
-        <v>6981199</v>
+        <v>6981380</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,19 +1885,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,57 +1902,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128890039</v>
+        <v>128890100</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515123</v>
+        <v>515060</v>
       </c>
       <c r="R14" t="n">
-        <v>6981380</v>
+        <v>6981326</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,6 +1987,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2009,60 +2004,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128890100</v>
+        <v>128884116</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515060</v>
+        <v>515030</v>
       </c>
       <c r="R15" t="n">
-        <v>6981326</v>
+        <v>6981199</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2089,14 +2084,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,22 +2111,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128884105</v>
+        <v>128890028</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80010</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515069</v>
+        <v>515039</v>
       </c>
       <c r="R16" t="n">
-        <v>6981348</v>
+        <v>6981285</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,49 +2191,40 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128884079</v>
+        <v>128890081</v>
       </c>
       <c r="B17" t="n">
-        <v>78048</v>
+        <v>80010</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,37 +2232,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>388</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515240</v>
+        <v>515203</v>
       </c>
       <c r="R17" t="n">
-        <v>6981445</v>
+        <v>6981449</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2298,19 +2289,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,22 +2311,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128890028</v>
+        <v>128884079</v>
       </c>
       <c r="B18" t="n">
-        <v>80006</v>
+        <v>78052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,37 +2334,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>388</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515039</v>
+        <v>515240</v>
       </c>
       <c r="R18" t="n">
-        <v>6981285</v>
+        <v>6981445</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2405,40 +2391,49 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128890081</v>
+        <v>128884105</v>
       </c>
       <c r="B19" t="n">
-        <v>80006</v>
+        <v>80144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,37 +2441,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515203</v>
+        <v>515069</v>
       </c>
       <c r="R19" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,14 +2498,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,22 +2525,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128890026</v>
+        <v>128890095</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>92336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,34 +2548,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2014</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515052</v>
+        <v>515145</v>
       </c>
       <c r="R20" t="n">
-        <v>6981331</v>
+        <v>6981384</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,22 +2627,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128884110</v>
+        <v>128890030</v>
       </c>
       <c r="B21" t="n">
-        <v>80006</v>
+        <v>80145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,37 +2650,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>388</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515038</v>
+        <v>515032</v>
       </c>
       <c r="R21" t="n">
-        <v>6981305</v>
+        <v>6981265</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2707,19 +2707,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2734,22 +2724,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128890095</v>
+        <v>128884110</v>
       </c>
       <c r="B22" t="n">
-        <v>92329</v>
+        <v>80010</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2757,37 +2747,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2014</v>
+        <v>388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515145</v>
+        <v>515038</v>
       </c>
       <c r="R22" t="n">
-        <v>6981384</v>
+        <v>6981305</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,14 +2804,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2836,22 +2831,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128890030</v>
+        <v>128890026</v>
       </c>
       <c r="B23" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,21 +2854,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2883,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515032</v>
+        <v>515052</v>
       </c>
       <c r="R23" t="n">
-        <v>6981265</v>
+        <v>6981331</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,6 +2914,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2945,32 +2945,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884084</v>
+        <v>128884089</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>80173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515227</v>
+        <v>515218</v>
       </c>
       <c r="R24" t="n">
-        <v>6981418</v>
+        <v>6981412</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3052,32 +3052,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884089</v>
+        <v>128884084</v>
       </c>
       <c r="B25" t="n">
-        <v>80169</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515218</v>
+        <v>515227</v>
       </c>
       <c r="R25" t="n">
-        <v>6981412</v>
+        <v>6981418</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3162,7 +3162,7 @@
         <v>128884107</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>128890088</v>
       </c>
       <c r="B27" t="n">
-        <v>79506</v>
+        <v>79510</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>128884103</v>
       </c>
       <c r="B28" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>128890094</v>
       </c>
       <c r="B29" t="n">
-        <v>80007</v>
+        <v>80011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>128884108</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>128890043</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>128890042</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128890035</v>
+        <v>128890076</v>
       </c>
       <c r="B34" t="n">
-        <v>80140</v>
+        <v>83015</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3991,34 +3991,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>515031</v>
+        <v>514973</v>
       </c>
       <c r="R34" t="n">
-        <v>6981191</v>
+        <v>6981271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,6 +4053,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4065,22 +4070,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128890076</v>
+        <v>128890035</v>
       </c>
       <c r="B35" t="n">
-        <v>83011</v>
+        <v>80144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4088,34 +4093,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514973</v>
+        <v>515031</v>
       </c>
       <c r="R35" t="n">
-        <v>6981271</v>
+        <v>6981191</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4167,12 +4167,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4182,7 +4182,7 @@
         <v>128884083</v>
       </c>
       <c r="B36" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>128884098</v>
       </c>
       <c r="B37" t="n">
-        <v>79291</v>
+        <v>79295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>128884092</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4500,45 +4500,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128890083</v>
+        <v>128890040</v>
       </c>
       <c r="B39" t="n">
-        <v>80044</v>
+        <v>80144</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515188</v>
+        <v>515196</v>
       </c>
       <c r="R39" t="n">
-        <v>6981452</v>
+        <v>6981392</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4573,11 +4573,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4590,57 +4585,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128890040</v>
+        <v>128890083</v>
       </c>
       <c r="B40" t="n">
-        <v>80140</v>
+        <v>80048</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515196</v>
+        <v>515188</v>
       </c>
       <c r="R40" t="n">
-        <v>6981392</v>
+        <v>6981452</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4675,6 +4670,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4687,22 +4687,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128890022</v>
+        <v>128884082</v>
       </c>
       <c r="B41" t="n">
-        <v>96905</v>
+        <v>91818</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515029</v>
+        <v>515231</v>
       </c>
       <c r="R41" t="n">
-        <v>6981199</v>
+        <v>6981417</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,9 +4767,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4784,22 +4794,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128884082</v>
+        <v>128890022</v>
       </c>
       <c r="B42" t="n">
-        <v>91811</v>
+        <v>96915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4807,37 +4817,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515231</v>
+        <v>515029</v>
       </c>
       <c r="R42" t="n">
-        <v>6981417</v>
+        <v>6981199</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4864,19 +4874,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,12 +4891,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4906,7 +4906,7 @@
         <v>128890031</v>
       </c>
       <c r="B43" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>128890045</v>
       </c>
       <c r="B44" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>128890024</v>
       </c>
       <c r="B45" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5194,48 +5194,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128884114</v>
+        <v>128890104</v>
       </c>
       <c r="B46" t="n">
-        <v>80140</v>
+        <v>82998</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515018</v>
+        <v>515070</v>
       </c>
       <c r="R46" t="n">
-        <v>6981240</v>
+        <v>6981365</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5262,19 +5262,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5289,12 +5284,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5304,7 +5299,7 @@
         <v>128884117</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5408,32 +5403,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890104</v>
+        <v>128890090</v>
       </c>
       <c r="B48" t="n">
-        <v>82994</v>
+        <v>80144</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5438,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981365</v>
+        <v>6981245</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5483,7 +5478,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5510,10 +5505,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890090</v>
+        <v>128884114</v>
       </c>
       <c r="B49" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5541,17 +5536,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515013</v>
+        <v>515018</v>
       </c>
       <c r="R49" t="n">
-        <v>6981245</v>
+        <v>6981240</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5578,14 +5573,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5600,12 +5600,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
         <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>128890034</v>
       </c>
       <c r="B51" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884080</v>
+        <v>128890041</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5822,37 +5822,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515239</v>
+        <v>515196</v>
       </c>
       <c r="R52" t="n">
-        <v>6981443</v>
+        <v>6981428</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5879,19 +5879,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5906,60 +5896,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890041</v>
+        <v>128884086</v>
       </c>
       <c r="B53" t="n">
-        <v>80140</v>
+        <v>58095</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515196</v>
+        <v>515225</v>
       </c>
       <c r="R53" t="n">
-        <v>6981428</v>
+        <v>6981406</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5986,9 +5976,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6003,44 +6003,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884086</v>
+        <v>128884080</v>
       </c>
       <c r="B54" t="n">
-        <v>58093</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515225</v>
+        <v>515239</v>
       </c>
       <c r="R54" t="n">
-        <v>6981406</v>
+        <v>6981443</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6125,7 +6125,7 @@
         <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128890105</v>
+        <v>128890025</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6235,34 +6235,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515054</v>
+        <v>515214</v>
       </c>
       <c r="R56" t="n">
-        <v>6981308</v>
+        <v>6981426</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6297,11 +6297,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6314,22 +6309,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128884119</v>
+        <v>128890105</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6357,17 +6352,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515196</v>
+        <v>515054</v>
       </c>
       <c r="R57" t="n">
-        <v>6981382</v>
+        <v>6981308</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6394,19 +6389,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>16:26</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6421,22 +6411,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884090</v>
+        <v>128884119</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6468,10 +6458,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515210</v>
+        <v>515196</v>
       </c>
       <c r="R58" t="n">
-        <v>6981412</v>
+        <v>6981382</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -6503,7 +6493,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6513,7 +6503,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6540,32 +6530,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884100</v>
+        <v>128884090</v>
       </c>
       <c r="B59" t="n">
-        <v>80169</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6575,10 +6565,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515158</v>
+        <v>515210</v>
       </c>
       <c r="R59" t="n">
-        <v>6981405</v>
+        <v>6981412</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6610,7 +6600,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6620,7 +6610,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6647,48 +6637,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128890025</v>
+        <v>128884100</v>
       </c>
       <c r="B60" t="n">
-        <v>91526</v>
+        <v>80173</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515214</v>
+        <v>515158</v>
       </c>
       <c r="R60" t="n">
-        <v>6981426</v>
+        <v>6981405</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6715,9 +6705,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6732,60 +6732,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128890082</v>
+        <v>128884104</v>
       </c>
       <c r="B61" t="n">
-        <v>79121</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515014</v>
+        <v>515104</v>
       </c>
       <c r="R61" t="n">
-        <v>6981245</v>
+        <v>6981353</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,14 +6812,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6834,22 +6839,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884099</v>
+        <v>128884095</v>
       </c>
       <c r="B62" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6857,21 +6862,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6881,10 +6886,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515158</v>
+        <v>515183</v>
       </c>
       <c r="R62" t="n">
-        <v>6981406</v>
+        <v>6981391</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -6916,7 +6921,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6926,7 +6931,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6953,10 +6963,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128890027</v>
+        <v>128884113</v>
       </c>
       <c r="B63" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6964,37 +6974,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515073</v>
+        <v>515021</v>
       </c>
       <c r="R63" t="n">
-        <v>6981343</v>
+        <v>6981285</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7021,14 +7031,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7043,22 +7063,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128890023</v>
+        <v>128890027</v>
       </c>
       <c r="B64" t="n">
-        <v>91526</v>
+        <v>57725</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7066,21 +7086,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7090,10 +7110,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515081</v>
+        <v>515073</v>
       </c>
       <c r="R64" t="n">
-        <v>6981324</v>
+        <v>6981343</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7126,6 +7146,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7152,10 +7177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884104</v>
+        <v>128884099</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7163,21 +7188,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7187,10 +7212,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515104</v>
+        <v>515158</v>
       </c>
       <c r="R65" t="n">
-        <v>6981353</v>
+        <v>6981406</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7222,7 +7247,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7232,7 +7257,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7259,10 +7284,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884095</v>
+        <v>128890023</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7270,37 +7295,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515183</v>
+        <v>515081</v>
       </c>
       <c r="R66" t="n">
-        <v>6981391</v>
+        <v>6981324</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7327,24 +7352,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>nr 500</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7359,60 +7369,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884113</v>
+        <v>128890082</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>79125</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515021</v>
+        <v>515014</v>
       </c>
       <c r="R67" t="n">
-        <v>6981285</v>
+        <v>6981245</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7439,24 +7449,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7471,12 +7471,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
         <v>128890032</v>
       </c>
       <c r="B68" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7580,10 +7580,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890077</v>
+        <v>128890080</v>
       </c>
       <c r="B69" t="n">
-        <v>83011</v>
+        <v>80010</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7591,21 +7591,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>388</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515057</v>
+        <v>515188</v>
       </c>
       <c r="R69" t="n">
-        <v>6981333</v>
+        <v>6981440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7655,7 +7655,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7682,10 +7682,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890080</v>
+        <v>128890077</v>
       </c>
       <c r="B70" t="n">
-        <v>80006</v>
+        <v>83015</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7693,21 +7693,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>388</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515188</v>
+        <v>515057</v>
       </c>
       <c r="R70" t="n">
-        <v>6981440</v>
+        <v>6981333</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7787,7 +7787,7 @@
         <v>128890097</v>
       </c>
       <c r="B71" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>105707</v>
+        <v>105717</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>128884111</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8095,48 +8095,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128884094</v>
+        <v>128890101</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515181</v>
+        <v>515108</v>
       </c>
       <c r="R74" t="n">
-        <v>6981416</v>
+        <v>6981372</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8163,19 +8163,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8190,12 +8185,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8205,7 +8200,7 @@
         <v>128890084</v>
       </c>
       <c r="B75" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8304,48 +8299,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128890101</v>
+        <v>128884094</v>
       </c>
       <c r="B76" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515108</v>
+        <v>515181</v>
       </c>
       <c r="R76" t="n">
-        <v>6981372</v>
+        <v>6981416</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8372,14 +8367,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>16 plantor på marken i gammal granskog</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,12 +8394,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8409,7 +8409,7 @@
         <v>128890037</v>
       </c>
       <c r="B77" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8503,10 +8503,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128890085</v>
+        <v>128884102</v>
       </c>
       <c r="B78" t="n">
-        <v>91811</v>
+        <v>80144</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8514,37 +8514,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515034</v>
+        <v>515111</v>
       </c>
       <c r="R78" t="n">
-        <v>6981293</v>
+        <v>6981360</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8571,14 +8571,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8593,22 +8598,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884102</v>
+        <v>128890085</v>
       </c>
       <c r="B79" t="n">
-        <v>80140</v>
+        <v>91818</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8616,37 +8621,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515111</v>
+        <v>515034</v>
       </c>
       <c r="R79" t="n">
-        <v>6981360</v>
+        <v>6981293</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8673,19 +8678,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,44 +8700,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890093</v>
+        <v>128890087</v>
       </c>
       <c r="B80" t="n">
-        <v>80007</v>
+        <v>80172</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>385</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515053</v>
+        <v>515014</v>
       </c>
       <c r="R80" t="n">
-        <v>6981314</v>
+        <v>6981245</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,10 +8814,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884081</v>
+        <v>128884091</v>
       </c>
       <c r="B81" t="n">
-        <v>91526</v>
+        <v>80144</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8825,21 +8825,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515230</v>
+        <v>515199</v>
       </c>
       <c r="R81" t="n">
-        <v>6981431</v>
+        <v>6981419</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8921,10 +8921,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884091</v>
+        <v>128890091</v>
       </c>
       <c r="B82" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8952,17 +8952,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515199</v>
+        <v>515069</v>
       </c>
       <c r="R82" t="n">
-        <v>6981419</v>
+        <v>6981349</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8989,19 +8989,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9016,22 +9011,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890091</v>
+        <v>128890038</v>
       </c>
       <c r="B83" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9059,14 +9054,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515069</v>
+        <v>515041</v>
       </c>
       <c r="R83" t="n">
-        <v>6981349</v>
+        <v>6981296</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9101,11 +9096,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9118,22 +9108,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890038</v>
+        <v>128884081</v>
       </c>
       <c r="B84" t="n">
-        <v>80140</v>
+        <v>91533</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9141,37 +9131,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515041</v>
+        <v>515230</v>
       </c>
       <c r="R84" t="n">
-        <v>6981296</v>
+        <v>6981431</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9198,9 +9188,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9215,44 +9215,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890087</v>
+        <v>128890093</v>
       </c>
       <c r="B85" t="n">
-        <v>80168</v>
+        <v>80011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6461</v>
+        <v>385</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9262,10 +9262,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515014</v>
+        <v>515053</v>
       </c>
       <c r="R85" t="n">
-        <v>6981245</v>
+        <v>6981314</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På lodyta</t>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9332,7 +9332,7 @@
         <v>128890099</v>
       </c>
       <c r="B86" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>128890096</v>
       </c>
       <c r="B87" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -1720,48 +1720,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890033</v>
+        <v>128884116</v>
       </c>
       <c r="B12" t="n">
-        <v>75029</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515018</v>
+        <v>515030</v>
       </c>
       <c r="R12" t="n">
-        <v>6981215</v>
+        <v>6981199</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,9 +1788,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,44 +1815,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890039</v>
+        <v>128890033</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>75029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515123</v>
+        <v>515018</v>
       </c>
       <c r="R13" t="n">
-        <v>6981380</v>
+        <v>6981215</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,45 +1924,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128890100</v>
+        <v>128890039</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515060</v>
+        <v>515123</v>
       </c>
       <c r="R14" t="n">
-        <v>6981326</v>
+        <v>6981380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,11 +1997,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2004,60 +2009,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128884116</v>
+        <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515030</v>
+        <v>515060</v>
       </c>
       <c r="R15" t="n">
-        <v>6981199</v>
+        <v>6981326</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2084,19 +2089,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:07</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128884079</v>
+        <v>128884105</v>
       </c>
       <c r="B18" t="n">
-        <v>78052</v>
+        <v>80144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2334,21 +2334,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515240</v>
+        <v>515069</v>
       </c>
       <c r="R18" t="n">
-        <v>6981445</v>
+        <v>6981348</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2430,10 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128884105</v>
+        <v>128884079</v>
       </c>
       <c r="B19" t="n">
-        <v>80144</v>
+        <v>78052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515069</v>
+        <v>515240</v>
       </c>
       <c r="R19" t="n">
-        <v>6981348</v>
+        <v>6981445</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128890095</v>
+        <v>128890026</v>
       </c>
       <c r="B20" t="n">
-        <v>92336</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,34 +2548,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515145</v>
+        <v>515052</v>
       </c>
       <c r="R20" t="n">
-        <v>6981384</v>
+        <v>6981331</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gråalslåga i gransumpskog</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,22 +2627,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128890030</v>
+        <v>128884110</v>
       </c>
       <c r="B21" t="n">
-        <v>80145</v>
+        <v>80010</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,37 +2650,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>388</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515032</v>
+        <v>515038</v>
       </c>
       <c r="R21" t="n">
-        <v>6981265</v>
+        <v>6981305</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2707,9 +2707,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,44 +2734,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884110</v>
+        <v>128884089</v>
       </c>
       <c r="B22" t="n">
-        <v>80010</v>
+        <v>80173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>388</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2781,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515038</v>
+        <v>515218</v>
       </c>
       <c r="R22" t="n">
-        <v>6981305</v>
+        <v>6981412</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2806,7 +2816,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2816,7 +2826,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2843,10 +2853,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128890026</v>
+        <v>128890095</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>92336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,34 +2864,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2014</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515052</v>
+        <v>515145</v>
       </c>
       <c r="R23" t="n">
-        <v>6981331</v>
+        <v>6981384</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,7 +2928,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2933,60 +2943,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884089</v>
+        <v>128890030</v>
       </c>
       <c r="B24" t="n">
-        <v>80173</v>
+        <v>80145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515218</v>
+        <v>515032</v>
       </c>
       <c r="R24" t="n">
-        <v>6981412</v>
+        <v>6981265</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3013,19 +3023,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3040,22 +3040,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884084</v>
+        <v>128884107</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515227</v>
+        <v>515060</v>
       </c>
       <c r="R25" t="n">
-        <v>6981418</v>
+        <v>6981336</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3159,10 +3159,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884107</v>
+        <v>128884084</v>
       </c>
       <c r="B26" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515060</v>
+        <v>515227</v>
       </c>
       <c r="R26" t="n">
-        <v>6981336</v>
+        <v>6981418</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4500,45 +4500,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128890040</v>
+        <v>128890083</v>
       </c>
       <c r="B39" t="n">
-        <v>80144</v>
+        <v>80048</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515196</v>
+        <v>515188</v>
       </c>
       <c r="R39" t="n">
-        <v>6981392</v>
+        <v>6981452</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4573,6 +4573,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4585,57 +4590,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128890083</v>
+        <v>128890040</v>
       </c>
       <c r="B40" t="n">
-        <v>80048</v>
+        <v>80144</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515188</v>
+        <v>515196</v>
       </c>
       <c r="R40" t="n">
-        <v>6981452</v>
+        <v>6981392</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4670,11 +4675,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4687,12 +4687,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5714,10 +5714,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890034</v>
+        <v>128890041</v>
       </c>
       <c r="B51" t="n">
-        <v>91818</v>
+        <v>80144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5749,10 +5749,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515231</v>
+        <v>515196</v>
       </c>
       <c r="R51" t="n">
-        <v>6981432</v>
+        <v>6981428</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890041</v>
+        <v>128890034</v>
       </c>
       <c r="B52" t="n">
-        <v>80144</v>
+        <v>91818</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515196</v>
+        <v>515231</v>
       </c>
       <c r="R52" t="n">
-        <v>6981428</v>
+        <v>6981432</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5908,32 +5908,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884086</v>
+        <v>128884080</v>
       </c>
       <c r="B53" t="n">
-        <v>58095</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5943,10 +5943,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515225</v>
+        <v>515239</v>
       </c>
       <c r="R53" t="n">
-        <v>6981406</v>
+        <v>6981443</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6015,32 +6015,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884080</v>
+        <v>128884086</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>58095</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515239</v>
+        <v>515225</v>
       </c>
       <c r="R54" t="n">
-        <v>6981443</v>
+        <v>6981406</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6744,48 +6744,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884104</v>
+        <v>128890082</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79125</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515104</v>
+        <v>515014</v>
       </c>
       <c r="R61" t="n">
-        <v>6981353</v>
+        <v>6981245</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,19 +6812,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6839,19 +6834,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884095</v>
+        <v>128884104</v>
       </c>
       <c r="B62" t="n">
         <v>79039</v>
@@ -6886,10 +6881,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515183</v>
+        <v>515104</v>
       </c>
       <c r="R62" t="n">
-        <v>6981391</v>
+        <v>6981353</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -6921,7 +6916,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6931,12 +6926,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6963,7 +6953,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884113</v>
+        <v>128884095</v>
       </c>
       <c r="B63" t="n">
         <v>79039</v>
@@ -6998,10 +6988,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515021</v>
+        <v>515183</v>
       </c>
       <c r="R63" t="n">
-        <v>6981285</v>
+        <v>6981391</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7033,7 +7023,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7043,7 +7033,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7075,10 +7065,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128890027</v>
+        <v>128884113</v>
       </c>
       <c r="B64" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7086,37 +7076,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515073</v>
+        <v>515021</v>
       </c>
       <c r="R64" t="n">
-        <v>6981343</v>
+        <v>6981285</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7143,14 +7133,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7165,22 +7165,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884099</v>
+        <v>128890027</v>
       </c>
       <c r="B65" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7188,37 +7188,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515158</v>
+        <v>515073</v>
       </c>
       <c r="R65" t="n">
-        <v>6981406</v>
+        <v>6981343</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7245,19 +7245,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7272,12 +7267,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7381,48 +7376,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128890082</v>
+        <v>128884099</v>
       </c>
       <c r="B67" t="n">
-        <v>79125</v>
+        <v>80144</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515014</v>
+        <v>515158</v>
       </c>
       <c r="R67" t="n">
-        <v>6981245</v>
+        <v>6981406</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7449,14 +7444,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7471,22 +7471,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890032</v>
+        <v>128890097</v>
       </c>
       <c r="B68" t="n">
-        <v>91988</v>
+        <v>98669</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7494,34 +7494,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515210</v>
+        <v>515060</v>
       </c>
       <c r="R68" t="n">
-        <v>6981426</v>
+        <v>6981339</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,6 +7556,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7568,44 +7573,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890080</v>
+        <v>128890075</v>
       </c>
       <c r="B69" t="n">
-        <v>80010</v>
+        <v>105717</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>388</v>
+        <v>221725</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7615,10 +7620,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515188</v>
+        <v>515124</v>
       </c>
       <c r="R69" t="n">
-        <v>6981440</v>
+        <v>6981387</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7655,7 +7660,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7682,45 +7687,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890077</v>
+        <v>128890032</v>
       </c>
       <c r="B70" t="n">
-        <v>83015</v>
+        <v>91988</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515057</v>
+        <v>515210</v>
       </c>
       <c r="R70" t="n">
-        <v>6981333</v>
+        <v>6981426</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7755,11 +7760,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På gammal gran i lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7772,44 +7772,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890097</v>
+        <v>128890080</v>
       </c>
       <c r="B71" t="n">
-        <v>98669</v>
+        <v>80010</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515060</v>
+        <v>515188</v>
       </c>
       <c r="R71" t="n">
-        <v>6981339</v>
+        <v>6981440</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890075</v>
+        <v>128890077</v>
       </c>
       <c r="B72" t="n">
-        <v>105717</v>
+        <v>83015</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515124</v>
+        <v>515057</v>
       </c>
       <c r="R72" t="n">
-        <v>6981387</v>
+        <v>6981333</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884109</v>
+        <v>128890092</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>80180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515053</v>
+        <v>515067</v>
       </c>
       <c r="R2" t="n">
-        <v>6981306</v>
+        <v>6981353</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:44</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884101</v>
+        <v>128884109</v>
       </c>
       <c r="B3" t="n">
         <v>79039</v>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515135</v>
+        <v>515053</v>
       </c>
       <c r="R3" t="n">
-        <v>6981381</v>
+        <v>6981306</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884097</v>
+        <v>128884101</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515184</v>
+        <v>515135</v>
       </c>
       <c r="R4" t="n">
-        <v>6981392</v>
+        <v>6981381</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -959,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,48 +991,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128890092</v>
+        <v>128884097</v>
       </c>
       <c r="B5" t="n">
-        <v>80180</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515067</v>
+        <v>515184</v>
       </c>
       <c r="R5" t="n">
-        <v>6981353</v>
+        <v>6981392</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,14 +1059,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,12 +1086,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128890079</v>
+        <v>128890102</v>
       </c>
       <c r="B7" t="n">
-        <v>91497</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515071</v>
+        <v>515229</v>
       </c>
       <c r="R7" t="n">
-        <v>6981351</v>
+        <v>6981403</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>50 plantor i i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128890102</v>
+        <v>128890079</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515229</v>
+        <v>515071</v>
       </c>
       <c r="R8" t="n">
-        <v>6981403</v>
+        <v>6981351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>50 plantor i i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884093</v>
+        <v>128884087</v>
       </c>
       <c r="B9" t="n">
-        <v>105717</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515174</v>
+        <v>515217</v>
       </c>
       <c r="R9" t="n">
-        <v>6981416</v>
+        <v>6981406</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128884087</v>
+        <v>128890036</v>
       </c>
       <c r="B10" t="n">
         <v>80144</v>
@@ -1547,17 +1547,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515217</v>
+        <v>515018</v>
       </c>
       <c r="R10" t="n">
-        <v>6981406</v>
+        <v>6981217</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,19 +1584,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,60 +1601,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128890036</v>
+        <v>128884093</v>
       </c>
       <c r="B11" t="n">
-        <v>80144</v>
+        <v>105724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515018</v>
+        <v>515174</v>
       </c>
       <c r="R11" t="n">
-        <v>6981217</v>
+        <v>6981416</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,9 +1681,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,60 +1708,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128884116</v>
+        <v>128890033</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>75029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515030</v>
+        <v>515018</v>
       </c>
       <c r="R12" t="n">
-        <v>6981199</v>
+        <v>6981215</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,19 +1788,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,60 +1805,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890033</v>
+        <v>128884116</v>
       </c>
       <c r="B13" t="n">
-        <v>75029</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515018</v>
+        <v>515030</v>
       </c>
       <c r="R13" t="n">
-        <v>6981215</v>
+        <v>6981199</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1895,9 +1885,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,12 +1912,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
         <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2537,48 +2537,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128890026</v>
+        <v>128884089</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>80173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515052</v>
+        <v>515218</v>
       </c>
       <c r="R20" t="n">
-        <v>6981331</v>
+        <v>6981412</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2605,14 +2605,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,22 +2632,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128884110</v>
+        <v>128884107</v>
       </c>
       <c r="B21" t="n">
-        <v>80010</v>
+        <v>80144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,21 +2655,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2674,10 +2679,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515038</v>
+        <v>515060</v>
       </c>
       <c r="R21" t="n">
-        <v>6981305</v>
+        <v>6981336</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2709,7 +2714,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2719,7 +2724,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2746,32 +2751,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884089</v>
+        <v>128884110</v>
       </c>
       <c r="B22" t="n">
-        <v>80173</v>
+        <v>80010</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2781,10 +2786,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515218</v>
+        <v>515038</v>
       </c>
       <c r="R22" t="n">
-        <v>6981412</v>
+        <v>6981305</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2816,7 +2821,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2826,7 +2831,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2853,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128890095</v>
+        <v>128890026</v>
       </c>
       <c r="B23" t="n">
-        <v>92336</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2864,34 +2869,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2014</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515145</v>
+        <v>515052</v>
       </c>
       <c r="R23" t="n">
-        <v>6981384</v>
+        <v>6981331</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,7 +2933,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gråalslåga i gransumpskog</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2943,22 +2948,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128890030</v>
+        <v>128884084</v>
       </c>
       <c r="B24" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2966,37 +2971,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515032</v>
+        <v>515227</v>
       </c>
       <c r="R24" t="n">
-        <v>6981265</v>
+        <v>6981418</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3023,9 +3028,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3040,22 +3055,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884107</v>
+        <v>128890095</v>
       </c>
       <c r="B25" t="n">
-        <v>80144</v>
+        <v>92343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,37 +3078,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2014</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515060</v>
+        <v>515145</v>
       </c>
       <c r="R25" t="n">
-        <v>6981336</v>
+        <v>6981384</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3120,19 +3135,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:40</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3147,22 +3157,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884084</v>
+        <v>128890030</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3170,37 +3180,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515227</v>
+        <v>515032</v>
       </c>
       <c r="R26" t="n">
-        <v>6981418</v>
+        <v>6981265</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3227,19 +3237,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,44 +3254,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128890088</v>
+        <v>128890094</v>
       </c>
       <c r="B27" t="n">
-        <v>79510</v>
+        <v>80011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1797</v>
+        <v>385</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515103</v>
+        <v>515188</v>
       </c>
       <c r="R27" t="n">
-        <v>6981364</v>
+        <v>6981440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3368,32 +3368,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128884103</v>
+        <v>128884108</v>
       </c>
       <c r="B28" t="n">
-        <v>80173</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515108</v>
+        <v>515059</v>
       </c>
       <c r="R28" t="n">
-        <v>6981358</v>
+        <v>6981319</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3448,7 +3448,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>nr 10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3475,48 +3480,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128890094</v>
+        <v>128884103</v>
       </c>
       <c r="B29" t="n">
-        <v>80011</v>
+        <v>80173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>385</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515188</v>
+        <v>515108</v>
       </c>
       <c r="R29" t="n">
-        <v>6981440</v>
+        <v>6981358</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3543,14 +3548,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3565,60 +3575,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128884108</v>
+        <v>128890088</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>79510</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515059</v>
+        <v>515103</v>
       </c>
       <c r="R30" t="n">
-        <v>6981319</v>
+        <v>6981364</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3645,24 +3655,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>nr 10</t>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,12 +3677,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
         <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>92238</v>
+        <v>92245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>128890076</v>
       </c>
       <c r="B34" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128884083</v>
       </c>
       <c r="B36" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>128884082</v>
       </c>
       <c r="B41" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>128890022</v>
       </c>
       <c r="B42" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>128890024</v>
       </c>
       <c r="B45" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>128890104</v>
       </c>
       <c r="B46" t="n">
-        <v>82998</v>
+        <v>82988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890034</v>
+        <v>128884080</v>
       </c>
       <c r="B52" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5822,37 +5822,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515231</v>
+        <v>515239</v>
       </c>
       <c r="R52" t="n">
-        <v>6981432</v>
+        <v>6981443</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5879,9 +5879,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5896,22 +5906,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884080</v>
+        <v>128890034</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>91825</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5919,37 +5929,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515239</v>
+        <v>515231</v>
       </c>
       <c r="R53" t="n">
-        <v>6981443</v>
+        <v>6981432</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5976,19 +5986,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6003,12 +6003,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6125,7 +6125,7 @@
         <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6224,48 +6224,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128890025</v>
+        <v>128884100</v>
       </c>
       <c r="B56" t="n">
-        <v>91533</v>
+        <v>80173</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515214</v>
+        <v>515158</v>
       </c>
       <c r="R56" t="n">
-        <v>6981426</v>
+        <v>6981405</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6292,9 +6292,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6309,12 +6319,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6637,48 +6647,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884100</v>
+        <v>128890025</v>
       </c>
       <c r="B60" t="n">
-        <v>80173</v>
+        <v>91540</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515158</v>
+        <v>515214</v>
       </c>
       <c r="R60" t="n">
-        <v>6981405</v>
+        <v>6981426</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6705,19 +6715,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6732,57 +6732,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128890082</v>
+        <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>79125</v>
+        <v>91540</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6450</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515014</v>
+        <v>515081</v>
       </c>
       <c r="R61" t="n">
-        <v>6981245</v>
+        <v>6981324</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6817,11 +6817,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6834,22 +6829,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884104</v>
+        <v>128890027</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6857,37 +6852,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515104</v>
+        <v>515073</v>
       </c>
       <c r="R62" t="n">
-        <v>6981353</v>
+        <v>6981343</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6914,19 +6909,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,19 +6931,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884095</v>
+        <v>128884104</v>
       </c>
       <c r="B63" t="n">
         <v>79039</v>
@@ -6988,10 +6978,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515183</v>
+        <v>515104</v>
       </c>
       <c r="R63" t="n">
-        <v>6981391</v>
+        <v>6981353</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7023,7 +7013,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7033,12 +7023,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7065,48 +7050,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884113</v>
+        <v>128890082</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>79125</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515021</v>
+        <v>515014</v>
       </c>
       <c r="R64" t="n">
-        <v>6981285</v>
+        <v>6981245</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7133,24 +7118,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7165,22 +7140,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128890027</v>
+        <v>128884099</v>
       </c>
       <c r="B65" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7188,37 +7163,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515073</v>
+        <v>515158</v>
       </c>
       <c r="R65" t="n">
-        <v>6981343</v>
+        <v>6981406</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7245,14 +7220,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7267,22 +7247,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128890023</v>
+        <v>128884095</v>
       </c>
       <c r="B66" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7290,37 +7270,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515081</v>
+        <v>515183</v>
       </c>
       <c r="R66" t="n">
-        <v>6981324</v>
+        <v>6981391</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7347,9 +7327,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7364,22 +7359,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884099</v>
+        <v>128884113</v>
       </c>
       <c r="B67" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7387,21 +7382,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7411,10 +7406,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515158</v>
+        <v>515021</v>
       </c>
       <c r="R67" t="n">
-        <v>6981406</v>
+        <v>6981285</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -7446,7 +7441,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7456,7 +7451,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7483,32 +7483,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890097</v>
+        <v>128890077</v>
       </c>
       <c r="B68" t="n">
-        <v>98669</v>
+        <v>83005</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515060</v>
+        <v>515057</v>
       </c>
       <c r="R68" t="n">
-        <v>6981339</v>
+        <v>6981333</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7585,45 +7585,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890075</v>
+        <v>128890032</v>
       </c>
       <c r="B69" t="n">
-        <v>105717</v>
+        <v>91995</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221725</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515124</v>
+        <v>515210</v>
       </c>
       <c r="R69" t="n">
-        <v>6981387</v>
+        <v>6981426</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7658,11 +7658,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På marken i gammal gransumpskog</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7675,22 +7670,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890032</v>
+        <v>128890097</v>
       </c>
       <c r="B70" t="n">
-        <v>91988</v>
+        <v>98676</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7698,34 +7693,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515210</v>
+        <v>515060</v>
       </c>
       <c r="R70" t="n">
-        <v>6981426</v>
+        <v>6981339</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7760,6 +7755,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7772,12 +7772,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890077</v>
+        <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>83015</v>
+        <v>105724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515057</v>
+        <v>515124</v>
       </c>
       <c r="R72" t="n">
-        <v>6981333</v>
+        <v>6981387</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8095,48 +8095,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128890101</v>
+        <v>128884094</v>
       </c>
       <c r="B74" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515108</v>
+        <v>515181</v>
       </c>
       <c r="R74" t="n">
-        <v>6981372</v>
+        <v>6981416</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8163,14 +8163,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>16 plantor på marken i gammal granskog</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8185,12 +8190,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8200,7 +8205,7 @@
         <v>128890084</v>
       </c>
       <c r="B75" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8299,48 +8304,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884094</v>
+        <v>128890101</v>
       </c>
       <c r="B76" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515181</v>
+        <v>515108</v>
       </c>
       <c r="R76" t="n">
-        <v>6981416</v>
+        <v>6981372</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8367,19 +8372,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,12 +8394,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8613,7 +8613,7 @@
         <v>128890085</v>
       </c>
       <c r="B79" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8712,48 +8712,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890087</v>
+        <v>128884081</v>
       </c>
       <c r="B80" t="n">
-        <v>80172</v>
+        <v>91540</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515014</v>
+        <v>515230</v>
       </c>
       <c r="R80" t="n">
-        <v>6981245</v>
+        <v>6981431</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8780,14 +8780,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På lodyta</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8802,60 +8807,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128884091</v>
+        <v>128890093</v>
       </c>
       <c r="B81" t="n">
-        <v>80144</v>
+        <v>80011</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515199</v>
+        <v>515053</v>
       </c>
       <c r="R81" t="n">
-        <v>6981419</v>
+        <v>6981314</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8882,19 +8887,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8909,44 +8909,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128890091</v>
+        <v>128890096</v>
       </c>
       <c r="B82" t="n">
-        <v>80144</v>
+        <v>80104</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8956,10 +8956,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515069</v>
+        <v>515014</v>
       </c>
       <c r="R82" t="n">
-        <v>6981349</v>
+        <v>6981245</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9023,45 +9023,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890038</v>
+        <v>128890099</v>
       </c>
       <c r="B83" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515041</v>
+        <v>515054</v>
       </c>
       <c r="R83" t="n">
-        <v>6981296</v>
+        <v>6981308</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9096,6 +9096,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På marken 13 plantor i lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9108,60 +9113,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884081</v>
+        <v>128890087</v>
       </c>
       <c r="B84" t="n">
-        <v>91533</v>
+        <v>80172</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515230</v>
+        <v>515014</v>
       </c>
       <c r="R84" t="n">
-        <v>6981431</v>
+        <v>6981245</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9188,19 +9193,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9215,60 +9215,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890093</v>
+        <v>128884091</v>
       </c>
       <c r="B85" t="n">
-        <v>80011</v>
+        <v>80144</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515053</v>
+        <v>515199</v>
       </c>
       <c r="R85" t="n">
-        <v>6981314</v>
+        <v>6981419</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9295,14 +9295,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9317,44 +9322,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890099</v>
+        <v>128890091</v>
       </c>
       <c r="B86" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9364,10 +9369,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515054</v>
+        <v>515069</v>
       </c>
       <c r="R86" t="n">
-        <v>6981308</v>
+        <v>6981349</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9404,7 +9409,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9431,45 +9436,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890096</v>
+        <v>128890038</v>
       </c>
       <c r="B87" t="n">
-        <v>80104</v>
+        <v>80144</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515014</v>
+        <v>515041</v>
       </c>
       <c r="R87" t="n">
-        <v>6981245</v>
+        <v>6981296</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9504,11 +9509,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -9521,12 +9521,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128890092</v>
       </c>
       <c r="B2" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884109</v>
+        <v>128884097</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515053</v>
+        <v>515184</v>
       </c>
       <c r="R3" t="n">
-        <v>6981306</v>
+        <v>6981392</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
         <v>128884101</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884097</v>
+        <v>128884109</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515184</v>
+        <v>515053</v>
       </c>
       <c r="R5" t="n">
-        <v>6981392</v>
+        <v>6981306</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,7 +1101,7 @@
         <v>128884115</v>
       </c>
       <c r="B6" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128890102</v>
+        <v>128890079</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>91506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515229</v>
+        <v>515071</v>
       </c>
       <c r="R7" t="n">
-        <v>6981403</v>
+        <v>6981351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>50 plantor i i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128890079</v>
+        <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515071</v>
+        <v>515229</v>
       </c>
       <c r="R8" t="n">
-        <v>6981351</v>
+        <v>6981403</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>50 plantor i i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,7 +1412,7 @@
         <v>128884087</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>128890036</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128884093</v>
       </c>
       <c r="B11" t="n">
-        <v>105724</v>
+        <v>105726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128890033</v>
       </c>
       <c r="B12" t="n">
-        <v>75029</v>
+        <v>75031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128884116</v>
+        <v>128890039</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,37 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515030</v>
+        <v>515123</v>
       </c>
       <c r="R13" t="n">
-        <v>6981199</v>
+        <v>6981380</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,19 +1885,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,22 +1902,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128890039</v>
+        <v>128884116</v>
       </c>
       <c r="B14" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,37 +1925,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515123</v>
+        <v>515030</v>
       </c>
       <c r="R14" t="n">
-        <v>6981380</v>
+        <v>6981199</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,9 +1982,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,12 +2009,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
         <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>128890028</v>
       </c>
       <c r="B16" t="n">
-        <v>80010</v>
+        <v>80012</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>128890081</v>
       </c>
       <c r="B17" t="n">
-        <v>80010</v>
+        <v>80012</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128884105</v>
       </c>
       <c r="B18" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128884079</v>
       </c>
       <c r="B19" t="n">
-        <v>78052</v>
+        <v>78054</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,48 +2537,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128884089</v>
+        <v>128890095</v>
       </c>
       <c r="B20" t="n">
-        <v>80173</v>
+        <v>92345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>2014</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515218</v>
+        <v>515145</v>
       </c>
       <c r="R20" t="n">
-        <v>6981412</v>
+        <v>6981384</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2605,19 +2605,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:09</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2632,22 +2627,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128884107</v>
+        <v>128890030</v>
       </c>
       <c r="B21" t="n">
-        <v>80144</v>
+        <v>80147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,37 +2650,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515060</v>
+        <v>515032</v>
       </c>
       <c r="R21" t="n">
-        <v>6981336</v>
+        <v>6981265</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,19 +2707,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2739,44 +2724,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884110</v>
+        <v>128884089</v>
       </c>
       <c r="B22" t="n">
-        <v>80010</v>
+        <v>80175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>388</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2786,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515038</v>
+        <v>515218</v>
       </c>
       <c r="R22" t="n">
-        <v>6981305</v>
+        <v>6981412</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2821,7 +2806,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2831,7 +2816,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2858,10 +2843,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128890026</v>
+        <v>128884107</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2869,37 +2854,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515052</v>
+        <v>515060</v>
       </c>
       <c r="R23" t="n">
-        <v>6981331</v>
+        <v>6981336</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2926,14 +2911,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2948,12 +2938,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2963,7 +2953,7 @@
         <v>128884084</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3067,10 +3057,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128890095</v>
+        <v>128884110</v>
       </c>
       <c r="B25" t="n">
-        <v>92343</v>
+        <v>80012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,37 +3068,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2014</v>
+        <v>388</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515145</v>
+        <v>515038</v>
       </c>
       <c r="R25" t="n">
-        <v>6981384</v>
+        <v>6981305</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3135,14 +3125,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3157,22 +3152,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128890030</v>
+        <v>128890026</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3180,21 +3175,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3204,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515032</v>
+        <v>515052</v>
       </c>
       <c r="R26" t="n">
-        <v>6981265</v>
+        <v>6981331</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,6 +3235,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3266,10 +3266,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128890094</v>
+        <v>128884108</v>
       </c>
       <c r="B27" t="n">
-        <v>80011</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3277,37 +3277,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>385</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515188</v>
+        <v>515059</v>
       </c>
       <c r="R27" t="n">
-        <v>6981440</v>
+        <v>6981319</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3334,14 +3334,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>nr 10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,60 +3366,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128884108</v>
+        <v>128890088</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>79512</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515059</v>
+        <v>515103</v>
       </c>
       <c r="R28" t="n">
-        <v>6981319</v>
+        <v>6981364</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3436,24 +3446,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>nr 10</t>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3468,12 +3468,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
         <v>128884103</v>
       </c>
       <c r="B29" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,32 +3587,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128890088</v>
+        <v>128890094</v>
       </c>
       <c r="B30" t="n">
-        <v>79510</v>
+        <v>80013</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1797</v>
+        <v>385</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515103</v>
+        <v>515188</v>
       </c>
       <c r="R30" t="n">
-        <v>6981364</v>
+        <v>6981440</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3692,7 +3692,7 @@
         <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>92245</v>
+        <v>92247</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>128890043</v>
       </c>
       <c r="B32" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>128890042</v>
       </c>
       <c r="B33" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>128890076</v>
       </c>
       <c r="B34" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128890035</v>
       </c>
       <c r="B35" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128884083</v>
       </c>
       <c r="B36" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>128884098</v>
       </c>
       <c r="B37" t="n">
-        <v>79295</v>
+        <v>79297</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>128884092</v>
       </c>
       <c r="B38" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>128890083</v>
       </c>
       <c r="B39" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>128890040</v>
       </c>
       <c r="B40" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>128884082</v>
       </c>
       <c r="B41" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4806,32 +4806,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128890022</v>
+        <v>128890031</v>
       </c>
       <c r="B42" t="n">
-        <v>96922</v>
+        <v>80050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4841,10 +4841,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515029</v>
+        <v>515039</v>
       </c>
       <c r="R42" t="n">
-        <v>6981199</v>
+        <v>6981314</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128890031</v>
+        <v>128890045</v>
       </c>
       <c r="B43" t="n">
-        <v>80048</v>
+        <v>80106</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4914,21 +4914,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515039</v>
+        <v>515170</v>
       </c>
       <c r="R43" t="n">
-        <v>6981314</v>
+        <v>6981451</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5000,32 +5000,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128890045</v>
+        <v>128890022</v>
       </c>
       <c r="B44" t="n">
-        <v>80104</v>
+        <v>96924</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515170</v>
+        <v>515029</v>
       </c>
       <c r="R44" t="n">
-        <v>6981451</v>
+        <v>6981199</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5097,45 +5097,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890024</v>
+        <v>128890104</v>
       </c>
       <c r="B45" t="n">
-        <v>91540</v>
+        <v>82990</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515219</v>
+        <v>515070</v>
       </c>
       <c r="R45" t="n">
-        <v>6981419</v>
+        <v>6981365</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,6 +5170,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5182,60 +5187,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890104</v>
+        <v>128884117</v>
       </c>
       <c r="B46" t="n">
-        <v>82988</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R46" t="n">
-        <v>6981365</v>
+        <v>6981204</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5262,14 +5267,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,22 +5294,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128884117</v>
+        <v>128890090</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5307,37 +5317,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
         <v>515013</v>
       </c>
       <c r="R47" t="n">
-        <v>6981204</v>
+        <v>6981245</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5364,19 +5374,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5391,22 +5396,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890090</v>
+        <v>128884114</v>
       </c>
       <c r="B48" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5434,17 +5439,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515013</v>
+        <v>515018</v>
       </c>
       <c r="R48" t="n">
-        <v>6981245</v>
+        <v>6981240</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5471,14 +5476,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5493,22 +5503,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128884114</v>
+        <v>128890024</v>
       </c>
       <c r="B49" t="n">
-        <v>80144</v>
+        <v>91542</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5516,37 +5526,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515018</v>
+        <v>515219</v>
       </c>
       <c r="R49" t="n">
-        <v>6981240</v>
+        <v>6981419</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5573,19 +5583,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5600,12 +5600,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
         <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5714,45 +5714,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890041</v>
+        <v>128890098</v>
       </c>
       <c r="B51" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515196</v>
+        <v>515031</v>
       </c>
       <c r="R51" t="n">
-        <v>6981428</v>
+        <v>6981292</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5787,6 +5787,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5799,22 +5804,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884080</v>
+        <v>128890034</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>91827</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5822,37 +5827,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515239</v>
+        <v>515231</v>
       </c>
       <c r="R52" t="n">
-        <v>6981443</v>
+        <v>6981432</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5879,19 +5884,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5906,22 +5901,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890034</v>
+        <v>128890041</v>
       </c>
       <c r="B53" t="n">
-        <v>91825</v>
+        <v>80146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5929,21 +5924,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5953,10 +5948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515231</v>
+        <v>515196</v>
       </c>
       <c r="R53" t="n">
-        <v>6981432</v>
+        <v>6981428</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6015,32 +6010,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884086</v>
+        <v>128884080</v>
       </c>
       <c r="B54" t="n">
-        <v>58095</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6050,10 +6045,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515225</v>
+        <v>515239</v>
       </c>
       <c r="R54" t="n">
-        <v>6981406</v>
+        <v>6981443</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6085,7 +6080,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6095,7 +6090,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6122,48 +6117,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128890098</v>
+        <v>128884086</v>
       </c>
       <c r="B55" t="n">
-        <v>98676</v>
+        <v>58097</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515031</v>
+        <v>515225</v>
       </c>
       <c r="R55" t="n">
-        <v>6981292</v>
+        <v>6981406</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6190,14 +6185,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6212,60 +6212,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128884100</v>
+        <v>128890025</v>
       </c>
       <c r="B56" t="n">
-        <v>80173</v>
+        <v>91542</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515158</v>
+        <v>515214</v>
       </c>
       <c r="R56" t="n">
-        <v>6981405</v>
+        <v>6981426</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6292,19 +6292,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6319,60 +6309,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128890105</v>
+        <v>128884100</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>80175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515054</v>
+        <v>515158</v>
       </c>
       <c r="R57" t="n">
-        <v>6981308</v>
+        <v>6981405</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6399,14 +6389,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6421,22 +6416,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128884119</v>
+        <v>128890105</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6464,17 +6459,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515196</v>
+        <v>515054</v>
       </c>
       <c r="R58" t="n">
-        <v>6981382</v>
+        <v>6981308</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6501,19 +6496,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>16:26</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>150 bålar på gammal levande gran i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6528,12 +6518,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6543,7 +6533,7 @@
         <v>128884090</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6647,10 +6637,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128890025</v>
+        <v>128884119</v>
       </c>
       <c r="B60" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6658,37 +6648,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515214</v>
+        <v>515196</v>
       </c>
       <c r="R60" t="n">
-        <v>6981426</v>
+        <v>6981382</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6715,9 +6705,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6732,12 +6732,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6747,7 +6747,7 @@
         <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128890027</v>
+        <v>128884104</v>
       </c>
       <c r="B62" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515073</v>
+        <v>515104</v>
       </c>
       <c r="R62" t="n">
-        <v>6981343</v>
+        <v>6981353</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6909,14 +6909,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6931,60 +6936,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884104</v>
+        <v>128890082</v>
       </c>
       <c r="B63" t="n">
-        <v>79039</v>
+        <v>79127</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515104</v>
+        <v>515014</v>
       </c>
       <c r="R63" t="n">
-        <v>6981353</v>
+        <v>6981245</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7011,19 +7016,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7038,60 +7038,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128890082</v>
+        <v>128884099</v>
       </c>
       <c r="B64" t="n">
-        <v>79125</v>
+        <v>80146</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515014</v>
+        <v>515158</v>
       </c>
       <c r="R64" t="n">
-        <v>6981245</v>
+        <v>6981406</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7118,14 +7118,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7140,22 +7145,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884099</v>
+        <v>128884095</v>
       </c>
       <c r="B65" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7163,21 +7168,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7187,10 +7192,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515158</v>
+        <v>515183</v>
       </c>
       <c r="R65" t="n">
-        <v>6981406</v>
+        <v>6981391</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7222,7 +7227,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7232,7 +7237,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7259,10 +7269,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884095</v>
+        <v>128884113</v>
       </c>
       <c r="B66" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7294,10 +7304,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515183</v>
+        <v>515021</v>
       </c>
       <c r="R66" t="n">
-        <v>6981391</v>
+        <v>6981285</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7329,7 +7339,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7339,7 +7349,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7371,10 +7381,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884113</v>
+        <v>128890027</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7382,37 +7392,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515021</v>
+        <v>515073</v>
       </c>
       <c r="R67" t="n">
-        <v>6981285</v>
+        <v>6981343</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7439,24 +7449,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7471,57 +7471,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890077</v>
+        <v>128890032</v>
       </c>
       <c r="B68" t="n">
-        <v>83005</v>
+        <v>91997</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515057</v>
+        <v>515210</v>
       </c>
       <c r="R68" t="n">
-        <v>6981333</v>
+        <v>6981426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,11 +7556,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På gammal gran i lövrik granskog</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7573,57 +7568,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890032</v>
+        <v>128890080</v>
       </c>
       <c r="B69" t="n">
-        <v>91995</v>
+        <v>80012</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515210</v>
+        <v>515188</v>
       </c>
       <c r="R69" t="n">
-        <v>6981426</v>
+        <v>6981440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7658,6 +7653,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7670,44 +7670,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890097</v>
+        <v>128890077</v>
       </c>
       <c r="B70" t="n">
-        <v>98676</v>
+        <v>83007</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515060</v>
+        <v>515057</v>
       </c>
       <c r="R70" t="n">
-        <v>6981339</v>
+        <v>6981333</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7784,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890080</v>
+        <v>128890097</v>
       </c>
       <c r="B71" t="n">
-        <v>80010</v>
+        <v>98678</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515188</v>
+        <v>515060</v>
       </c>
       <c r="R71" t="n">
-        <v>6981440</v>
+        <v>6981339</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7889,7 +7889,7 @@
         <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>105724</v>
+        <v>105726</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884111</v>
+        <v>128890084</v>
       </c>
       <c r="B73" t="n">
-        <v>79039</v>
+        <v>91827</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7999,37 +7999,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>515033</v>
+        <v>515029</v>
       </c>
       <c r="R73" t="n">
-        <v>6981298</v>
+        <v>6981276</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8056,19 +8056,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8083,22 +8078,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128884094</v>
+        <v>128884111</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8130,10 +8125,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515181</v>
+        <v>515033</v>
       </c>
       <c r="R74" t="n">
-        <v>6981416</v>
+        <v>6981298</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -8165,7 +8160,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8175,7 +8170,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8202,10 +8197,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128890084</v>
+        <v>128884094</v>
       </c>
       <c r="B75" t="n">
-        <v>91825</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8213,37 +8208,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>515029</v>
+        <v>515181</v>
       </c>
       <c r="R75" t="n">
-        <v>6981276</v>
+        <v>6981416</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8270,14 +8265,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8292,12 +8292,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8307,7 +8307,7 @@
         <v>128890101</v>
       </c>
       <c r="B76" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>128890037</v>
       </c>
       <c r="B77" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>128884102</v>
       </c>
       <c r="B78" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>128890085</v>
       </c>
       <c r="B79" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8712,48 +8712,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128884081</v>
+        <v>128890093</v>
       </c>
       <c r="B80" t="n">
-        <v>91540</v>
+        <v>80013</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>385</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515230</v>
+        <v>515053</v>
       </c>
       <c r="R80" t="n">
-        <v>6981431</v>
+        <v>6981314</v>
       </c>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8780,19 +8780,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8807,44 +8802,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128890093</v>
+        <v>128890087</v>
       </c>
       <c r="B81" t="n">
-        <v>80011</v>
+        <v>80174</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>385</v>
+        <v>6461</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8854,10 +8849,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515053</v>
+        <v>515014</v>
       </c>
       <c r="R81" t="n">
-        <v>6981314</v>
+        <v>6981245</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8894,7 +8889,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8921,48 +8916,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128890096</v>
+        <v>128884091</v>
       </c>
       <c r="B82" t="n">
-        <v>80104</v>
+        <v>80146</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515014</v>
+        <v>515199</v>
       </c>
       <c r="R82" t="n">
-        <v>6981245</v>
+        <v>6981419</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8989,14 +8984,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9011,44 +9011,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890099</v>
+        <v>128890091</v>
       </c>
       <c r="B83" t="n">
-        <v>98676</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9058,10 +9058,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515054</v>
+        <v>515069</v>
       </c>
       <c r="R83" t="n">
-        <v>6981308</v>
+        <v>6981349</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9125,45 +9125,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890087</v>
+        <v>128890038</v>
       </c>
       <c r="B84" t="n">
-        <v>80172</v>
+        <v>80146</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515014</v>
+        <v>515041</v>
       </c>
       <c r="R84" t="n">
-        <v>6981245</v>
+        <v>6981296</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9198,11 +9198,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På lodyta</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9215,60 +9210,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884091</v>
+        <v>128890099</v>
       </c>
       <c r="B85" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515199</v>
+        <v>515054</v>
       </c>
       <c r="R85" t="n">
-        <v>6981419</v>
+        <v>6981308</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9295,19 +9290,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9322,44 +9312,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890091</v>
+        <v>128890096</v>
       </c>
       <c r="B86" t="n">
-        <v>80144</v>
+        <v>80106</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9369,10 +9359,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515069</v>
+        <v>515014</v>
       </c>
       <c r="R86" t="n">
-        <v>6981349</v>
+        <v>6981245</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9436,10 +9426,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890038</v>
+        <v>128884081</v>
       </c>
       <c r="B87" t="n">
-        <v>80144</v>
+        <v>91542</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9447,37 +9437,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515041</v>
+        <v>515230</v>
       </c>
       <c r="R87" t="n">
-        <v>6981296</v>
+        <v>6981431</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9504,9 +9494,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9521,12 +9521,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884097</v>
+        <v>128884101</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515184</v>
+        <v>515135</v>
       </c>
       <c r="R3" t="n">
-        <v>6981392</v>
+        <v>6981381</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884101</v>
+        <v>128884097</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515135</v>
+        <v>515184</v>
       </c>
       <c r="R4" t="n">
-        <v>6981381</v>
+        <v>6981392</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890033</v>
+        <v>128890100</v>
       </c>
       <c r="B12" t="n">
-        <v>75031</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515018</v>
+        <v>515060</v>
       </c>
       <c r="R12" t="n">
-        <v>6981215</v>
+        <v>6981326</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1793,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1805,44 +1810,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890039</v>
+        <v>128890033</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>75031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515123</v>
+        <v>515018</v>
       </c>
       <c r="R13" t="n">
-        <v>6981380</v>
+        <v>6981215</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,45 +2026,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128890100</v>
+        <v>128890039</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515060</v>
+        <v>515123</v>
       </c>
       <c r="R15" t="n">
-        <v>6981326</v>
+        <v>6981380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,11 +2099,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2111,19 +2111,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128890028</v>
+        <v>128890081</v>
       </c>
       <c r="B16" t="n">
         <v>80012</v>
@@ -2154,14 +2154,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515039</v>
+        <v>515203</v>
       </c>
       <c r="R16" t="n">
-        <v>6981285</v>
+        <v>6981449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,32 +2196,36 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890081</v>
+        <v>128890028</v>
       </c>
       <c r="B17" t="n">
         <v>80012</v>
@@ -2252,14 +2256,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515203</v>
+        <v>515039</v>
       </c>
       <c r="R17" t="n">
-        <v>6981449</v>
+        <v>6981285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,29 +2298,25 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2736,32 +2736,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884089</v>
+        <v>128884107</v>
       </c>
       <c r="B22" t="n">
-        <v>80175</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515218</v>
+        <v>515060</v>
       </c>
       <c r="R22" t="n">
-        <v>6981412</v>
+        <v>6981336</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128884107</v>
+        <v>128884084</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515060</v>
+        <v>515227</v>
       </c>
       <c r="R23" t="n">
-        <v>6981336</v>
+        <v>6981418</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2950,10 +2950,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884084</v>
+        <v>128890026</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,37 +2961,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515227</v>
+        <v>515052</v>
       </c>
       <c r="R24" t="n">
-        <v>6981418</v>
+        <v>6981331</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,19 +3018,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:05</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3045,12 +3040,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3164,48 +3159,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128890026</v>
+        <v>128884089</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515052</v>
+        <v>515218</v>
       </c>
       <c r="R26" t="n">
-        <v>6981331</v>
+        <v>6981412</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3232,14 +3227,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,12 +3254,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3378,32 +3378,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128890088</v>
+        <v>128890094</v>
       </c>
       <c r="B28" t="n">
-        <v>79512</v>
+        <v>80013</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1797</v>
+        <v>385</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515103</v>
+        <v>515188</v>
       </c>
       <c r="R28" t="n">
-        <v>6981364</v>
+        <v>6981440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3480,48 +3480,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128884103</v>
+        <v>128890088</v>
       </c>
       <c r="B29" t="n">
-        <v>80175</v>
+        <v>79512</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1797</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515108</v>
+        <v>515103</v>
       </c>
       <c r="R29" t="n">
-        <v>6981358</v>
+        <v>6981364</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3548,19 +3548,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3575,60 +3570,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128890094</v>
+        <v>128884103</v>
       </c>
       <c r="B30" t="n">
-        <v>80013</v>
+        <v>80175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>385</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515188</v>
+        <v>515108</v>
       </c>
       <c r="R30" t="n">
-        <v>6981440</v>
+        <v>6981358</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3655,14 +3650,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,44 +3677,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128890029</v>
+        <v>128890043</v>
       </c>
       <c r="B31" t="n">
-        <v>92247</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515089</v>
+        <v>515166</v>
       </c>
       <c r="R31" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,32 +3786,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128890043</v>
+        <v>128890029</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>92247</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515166</v>
+        <v>515089</v>
       </c>
       <c r="R32" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4699,48 +4699,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128884082</v>
+        <v>128890045</v>
       </c>
       <c r="B41" t="n">
-        <v>91827</v>
+        <v>80106</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515231</v>
+        <v>515170</v>
       </c>
       <c r="R41" t="n">
-        <v>6981417</v>
+        <v>6981451</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,19 +4767,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4794,60 +4784,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128890031</v>
+        <v>128884082</v>
       </c>
       <c r="B42" t="n">
-        <v>80050</v>
+        <v>91827</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515039</v>
+        <v>515231</v>
       </c>
       <c r="R42" t="n">
-        <v>6981314</v>
+        <v>6981417</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4874,9 +4864,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,44 +4891,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128890045</v>
+        <v>128890022</v>
       </c>
       <c r="B43" t="n">
-        <v>80106</v>
+        <v>96924</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515170</v>
+        <v>515029</v>
       </c>
       <c r="R43" t="n">
-        <v>6981451</v>
+        <v>6981199</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5000,32 +5000,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128890022</v>
+        <v>128890031</v>
       </c>
       <c r="B44" t="n">
-        <v>96924</v>
+        <v>80050</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515029</v>
+        <v>515039</v>
       </c>
       <c r="R44" t="n">
-        <v>6981199</v>
+        <v>6981314</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5097,45 +5097,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890104</v>
+        <v>128890024</v>
       </c>
       <c r="B45" t="n">
-        <v>82990</v>
+        <v>91542</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515070</v>
+        <v>515219</v>
       </c>
       <c r="R45" t="n">
-        <v>6981365</v>
+        <v>6981419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,11 +5170,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5187,60 +5182,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128884117</v>
+        <v>128890104</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>82990</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515013</v>
+        <v>515070</v>
       </c>
       <c r="R46" t="n">
-        <v>6981204</v>
+        <v>6981365</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5267,19 +5262,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5294,22 +5284,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128890090</v>
+        <v>128884117</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5317,37 +5307,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
         <v>515013</v>
       </c>
       <c r="R47" t="n">
-        <v>6981245</v>
+        <v>6981204</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5374,14 +5364,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,19 +5391,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128884114</v>
+        <v>128890090</v>
       </c>
       <c r="B48" t="n">
         <v>80146</v>
@@ -5439,17 +5434,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515018</v>
+        <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981240</v>
+        <v>6981245</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5476,19 +5471,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5503,22 +5493,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890024</v>
+        <v>128884114</v>
       </c>
       <c r="B49" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5526,37 +5516,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515219</v>
+        <v>515018</v>
       </c>
       <c r="R49" t="n">
-        <v>6981419</v>
+        <v>6981240</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5583,9 +5573,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5600,12 +5600,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5714,48 +5714,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890098</v>
+        <v>128884080</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515031</v>
+        <v>515239</v>
       </c>
       <c r="R51" t="n">
-        <v>6981292</v>
+        <v>6981443</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5782,14 +5782,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5804,60 +5809,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890034</v>
+        <v>128884086</v>
       </c>
       <c r="B52" t="n">
-        <v>91827</v>
+        <v>58097</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515231</v>
+        <v>515225</v>
       </c>
       <c r="R52" t="n">
-        <v>6981432</v>
+        <v>6981406</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5884,9 +5889,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5901,57 +5916,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890041</v>
+        <v>128890098</v>
       </c>
       <c r="B53" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515196</v>
+        <v>515031</v>
       </c>
       <c r="R53" t="n">
-        <v>6981428</v>
+        <v>6981292</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5986,6 +6001,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5998,22 +6018,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884080</v>
+        <v>128890034</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6021,37 +6041,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515239</v>
+        <v>515231</v>
       </c>
       <c r="R54" t="n">
-        <v>6981443</v>
+        <v>6981432</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6078,19 +6098,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6105,60 +6115,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128884086</v>
+        <v>128890041</v>
       </c>
       <c r="B55" t="n">
-        <v>58097</v>
+        <v>80146</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515225</v>
+        <v>515196</v>
       </c>
       <c r="R55" t="n">
-        <v>6981406</v>
+        <v>6981428</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6185,19 +6195,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6212,12 +6212,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128884090</v>
+        <v>128884119</v>
       </c>
       <c r="B59" t="n">
         <v>79041</v>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515210</v>
+        <v>515196</v>
       </c>
       <c r="R59" t="n">
-        <v>6981412</v>
+        <v>6981382</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6637,7 +6637,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128884119</v>
+        <v>128884090</v>
       </c>
       <c r="B60" t="n">
         <v>79041</v>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515196</v>
+        <v>515210</v>
       </c>
       <c r="R60" t="n">
-        <v>6981382</v>
+        <v>6981412</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6744,10 +6744,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128890023</v>
+        <v>128884104</v>
       </c>
       <c r="B61" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6755,37 +6755,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515081</v>
+        <v>515104</v>
       </c>
       <c r="R61" t="n">
-        <v>6981324</v>
+        <v>6981353</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,9 +6812,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,60 +6839,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884104</v>
+        <v>128890082</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79127</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515104</v>
+        <v>515014</v>
       </c>
       <c r="R62" t="n">
-        <v>6981353</v>
+        <v>6981245</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6909,19 +6919,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6936,60 +6941,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128890082</v>
+        <v>128884099</v>
       </c>
       <c r="B63" t="n">
-        <v>79127</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515014</v>
+        <v>515158</v>
       </c>
       <c r="R63" t="n">
-        <v>6981245</v>
+        <v>6981406</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7016,14 +7021,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7038,22 +7048,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884099</v>
+        <v>128884095</v>
       </c>
       <c r="B64" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7061,21 +7071,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7085,10 +7095,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515158</v>
+        <v>515183</v>
       </c>
       <c r="R64" t="n">
-        <v>6981406</v>
+        <v>6981391</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7120,7 +7130,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7130,7 +7140,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7157,7 +7172,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884095</v>
+        <v>128884113</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7192,10 +7207,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515183</v>
+        <v>515021</v>
       </c>
       <c r="R65" t="n">
-        <v>6981391</v>
+        <v>6981285</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7227,7 +7242,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7237,7 +7252,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7269,10 +7284,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884113</v>
+        <v>128890023</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7280,37 +7295,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515021</v>
+        <v>515081</v>
       </c>
       <c r="R66" t="n">
-        <v>6981285</v>
+        <v>6981324</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7337,24 +7352,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>nr 500</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7369,12 +7369,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7483,45 +7483,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890032</v>
+        <v>128890080</v>
       </c>
       <c r="B68" t="n">
-        <v>91997</v>
+        <v>80012</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515210</v>
+        <v>515188</v>
       </c>
       <c r="R68" t="n">
-        <v>6981426</v>
+        <v>6981440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,6 +7556,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7568,57 +7573,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890080</v>
+        <v>128890032</v>
       </c>
       <c r="B69" t="n">
-        <v>80012</v>
+        <v>91997</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515188</v>
+        <v>515210</v>
       </c>
       <c r="R69" t="n">
-        <v>6981440</v>
+        <v>6981426</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7653,11 +7658,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7670,12 +7670,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7784,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890097</v>
+        <v>128890075</v>
       </c>
       <c r="B71" t="n">
-        <v>98678</v>
+        <v>105726</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515060</v>
+        <v>515124</v>
       </c>
       <c r="R71" t="n">
-        <v>6981339</v>
+        <v>6981387</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890075</v>
+        <v>128890097</v>
       </c>
       <c r="B72" t="n">
-        <v>105726</v>
+        <v>98678</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515124</v>
+        <v>515060</v>
       </c>
       <c r="R72" t="n">
-        <v>6981387</v>
+        <v>6981339</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8197,48 +8197,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884094</v>
+        <v>128890101</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>515181</v>
+        <v>515108</v>
       </c>
       <c r="R75" t="n">
-        <v>6981416</v>
+        <v>6981372</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8265,19 +8265,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8292,60 +8287,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128890101</v>
+        <v>128884094</v>
       </c>
       <c r="B76" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515108</v>
+        <v>515181</v>
       </c>
       <c r="R76" t="n">
-        <v>6981372</v>
+        <v>6981416</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8372,14 +8367,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>16 plantor på marken i gammal granskog</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,22 +8394,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890037</v>
+        <v>128890085</v>
       </c>
       <c r="B77" t="n">
-        <v>80146</v>
+        <v>91827</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515026</v>
+        <v>515034</v>
       </c>
       <c r="R77" t="n">
-        <v>6981261</v>
+        <v>6981293</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,6 +8479,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8491,19 +8496,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884102</v>
+        <v>128890037</v>
       </c>
       <c r="B78" t="n">
         <v>80146</v>
@@ -8534,17 +8539,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515111</v>
+        <v>515026</v>
       </c>
       <c r="R78" t="n">
-        <v>6981360</v>
+        <v>6981261</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8571,19 +8576,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8598,22 +8593,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128890085</v>
+        <v>128884102</v>
       </c>
       <c r="B79" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8621,37 +8616,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515034</v>
+        <v>515111</v>
       </c>
       <c r="R79" t="n">
-        <v>6981293</v>
+        <v>6981360</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8678,14 +8673,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,44 +8700,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890093</v>
+        <v>128890096</v>
       </c>
       <c r="B80" t="n">
-        <v>80013</v>
+        <v>80106</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>385</v>
+        <v>229497</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515053</v>
+        <v>515014</v>
       </c>
       <c r="R80" t="n">
-        <v>6981314</v>
+        <v>6981245</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8814,32 +8814,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128890087</v>
+        <v>128890099</v>
       </c>
       <c r="B81" t="n">
-        <v>80174</v>
+        <v>98678</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515014</v>
+        <v>515054</v>
       </c>
       <c r="R81" t="n">
-        <v>6981245</v>
+        <v>6981308</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På lodyta</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8916,48 +8916,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128884091</v>
+        <v>128890093</v>
       </c>
       <c r="B82" t="n">
-        <v>80146</v>
+        <v>80013</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515199</v>
+        <v>515053</v>
       </c>
       <c r="R82" t="n">
-        <v>6981419</v>
+        <v>6981314</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8984,19 +8984,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9011,44 +9006,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890091</v>
+        <v>128890087</v>
       </c>
       <c r="B83" t="n">
-        <v>80146</v>
+        <v>80174</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9058,10 +9053,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515069</v>
+        <v>515014</v>
       </c>
       <c r="R83" t="n">
-        <v>6981349</v>
+        <v>6981245</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9098,7 +9093,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9125,10 +9120,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128890038</v>
+        <v>128884081</v>
       </c>
       <c r="B84" t="n">
-        <v>80146</v>
+        <v>91542</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9136,37 +9131,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515041</v>
+        <v>515230</v>
       </c>
       <c r="R84" t="n">
-        <v>6981296</v>
+        <v>6981431</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9193,9 +9188,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9210,60 +9215,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890099</v>
+        <v>128884091</v>
       </c>
       <c r="B85" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515054</v>
+        <v>515199</v>
       </c>
       <c r="R85" t="n">
-        <v>6981308</v>
+        <v>6981419</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9290,14 +9295,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9312,44 +9322,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890096</v>
+        <v>128890091</v>
       </c>
       <c r="B86" t="n">
-        <v>80106</v>
+        <v>80146</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9359,10 +9369,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515014</v>
+        <v>515069</v>
       </c>
       <c r="R86" t="n">
-        <v>6981245</v>
+        <v>6981349</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9426,10 +9436,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128884081</v>
+        <v>128890038</v>
       </c>
       <c r="B87" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9437,37 +9447,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515230</v>
+        <v>515041</v>
       </c>
       <c r="R87" t="n">
-        <v>6981431</v>
+        <v>6981296</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9494,19 +9504,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9521,12 +9521,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128890092</v>
+        <v>128884109</v>
       </c>
       <c r="B2" t="n">
-        <v>80182</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515067</v>
+        <v>515053</v>
       </c>
       <c r="R2" t="n">
-        <v>6981353</v>
+        <v>6981306</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +743,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,60 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884101</v>
+        <v>128890092</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>80182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515135</v>
+        <v>515067</v>
       </c>
       <c r="R3" t="n">
-        <v>6981381</v>
+        <v>6981353</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,19 +850,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:29</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884097</v>
+        <v>128884101</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515184</v>
+        <v>515135</v>
       </c>
       <c r="R4" t="n">
-        <v>6981392</v>
+        <v>6981381</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884109</v>
+        <v>128884097</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515053</v>
+        <v>515184</v>
       </c>
       <c r="R5" t="n">
-        <v>6981306</v>
+        <v>6981392</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890100</v>
+        <v>128890033</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>75031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515060</v>
+        <v>515018</v>
       </c>
       <c r="R12" t="n">
-        <v>6981326</v>
+        <v>6981215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,11 +1793,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>11 plantor i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1810,60 +1805,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128890033</v>
+        <v>128884116</v>
       </c>
       <c r="B13" t="n">
-        <v>75031</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515018</v>
+        <v>515030</v>
       </c>
       <c r="R13" t="n">
-        <v>6981215</v>
+        <v>6981199</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1890,9 +1885,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128884116</v>
+        <v>128890039</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,37 +1935,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515030</v>
+        <v>515123</v>
       </c>
       <c r="R14" t="n">
-        <v>6981199</v>
+        <v>6981380</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1987,19 +1992,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,57 +2009,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128890039</v>
+        <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515123</v>
+        <v>515060</v>
       </c>
       <c r="R15" t="n">
-        <v>6981380</v>
+        <v>6981326</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,6 +2094,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2111,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3378,48 +3378,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128890094</v>
+        <v>128884103</v>
       </c>
       <c r="B28" t="n">
-        <v>80013</v>
+        <v>80175</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>385</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515188</v>
+        <v>515108</v>
       </c>
       <c r="R28" t="n">
-        <v>6981440</v>
+        <v>6981358</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3446,14 +3446,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3468,44 +3473,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128890088</v>
+        <v>128890094</v>
       </c>
       <c r="B29" t="n">
-        <v>79512</v>
+        <v>80013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1797</v>
+        <v>385</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3515,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515103</v>
+        <v>515188</v>
       </c>
       <c r="R29" t="n">
-        <v>6981364</v>
+        <v>6981440</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3555,7 +3560,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,48 +3587,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128884103</v>
+        <v>128890088</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>79512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>1797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515108</v>
+        <v>515103</v>
       </c>
       <c r="R30" t="n">
-        <v>6981358</v>
+        <v>6981364</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3650,19 +3655,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,44 +3677,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128890043</v>
+        <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>92247</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515166</v>
+        <v>515089</v>
       </c>
       <c r="R31" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,32 +3786,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128890029</v>
+        <v>128890043</v>
       </c>
       <c r="B32" t="n">
-        <v>92247</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515089</v>
+        <v>515166</v>
       </c>
       <c r="R32" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5194,48 +5194,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128890104</v>
+        <v>128884117</v>
       </c>
       <c r="B46" t="n">
-        <v>82990</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515070</v>
+        <v>515013</v>
       </c>
       <c r="R46" t="n">
-        <v>6981365</v>
+        <v>6981204</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5262,14 +5262,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,22 +5289,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128884117</v>
+        <v>128890090</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5307,37 +5312,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
         <v>515013</v>
       </c>
       <c r="R47" t="n">
-        <v>6981204</v>
+        <v>6981245</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5364,19 +5369,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5391,19 +5391,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128890090</v>
+        <v>128884114</v>
       </c>
       <c r="B48" t="n">
         <v>80146</v>
@@ -5434,17 +5434,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515013</v>
+        <v>515018</v>
       </c>
       <c r="R48" t="n">
-        <v>6981245</v>
+        <v>6981240</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5471,14 +5471,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5493,60 +5498,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128884114</v>
+        <v>128890104</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>82990</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515018</v>
+        <v>515070</v>
       </c>
       <c r="R49" t="n">
-        <v>6981240</v>
+        <v>6981365</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5573,19 +5578,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5600,12 +5600,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5714,10 +5714,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128884080</v>
+        <v>128890034</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5725,37 +5725,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515239</v>
+        <v>515231</v>
       </c>
       <c r="R51" t="n">
-        <v>6981443</v>
+        <v>6981432</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5782,19 +5782,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5809,60 +5799,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884086</v>
+        <v>128890041</v>
       </c>
       <c r="B52" t="n">
-        <v>58097</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515225</v>
+        <v>515196</v>
       </c>
       <c r="R52" t="n">
-        <v>6981406</v>
+        <v>6981428</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5889,19 +5879,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5916,60 +5896,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890098</v>
+        <v>128884080</v>
       </c>
       <c r="B53" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515031</v>
+        <v>515239</v>
       </c>
       <c r="R53" t="n">
-        <v>6981292</v>
+        <v>6981443</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5996,14 +5976,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6018,60 +6003,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128890034</v>
+        <v>128884086</v>
       </c>
       <c r="B54" t="n">
-        <v>91827</v>
+        <v>58097</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515231</v>
+        <v>515225</v>
       </c>
       <c r="R54" t="n">
-        <v>6981432</v>
+        <v>6981406</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6098,9 +6083,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6115,57 +6110,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128890041</v>
+        <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515196</v>
+        <v>515031</v>
       </c>
       <c r="R55" t="n">
-        <v>6981428</v>
+        <v>6981292</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6200,6 +6195,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6212,12 +6212,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884104</v>
+        <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6755,37 +6755,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515104</v>
+        <v>515081</v>
       </c>
       <c r="R61" t="n">
-        <v>6981353</v>
+        <v>6981324</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,19 +6812,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6839,60 +6829,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128890082</v>
+        <v>128884104</v>
       </c>
       <c r="B62" t="n">
-        <v>79127</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515014</v>
+        <v>515104</v>
       </c>
       <c r="R62" t="n">
-        <v>6981245</v>
+        <v>6981353</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6919,14 +6909,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,60 +6936,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884099</v>
+        <v>128890082</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>79127</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515158</v>
+        <v>515014</v>
       </c>
       <c r="R63" t="n">
-        <v>6981406</v>
+        <v>6981245</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7021,19 +7016,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7048,22 +7038,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884095</v>
+        <v>128884099</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7071,21 +7061,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7095,10 +7085,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515183</v>
+        <v>515158</v>
       </c>
       <c r="R64" t="n">
-        <v>6981391</v>
+        <v>6981406</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -7130,7 +7120,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7140,12 +7130,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7172,7 +7157,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884113</v>
+        <v>128884095</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7207,10 +7192,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515021</v>
+        <v>515183</v>
       </c>
       <c r="R65" t="n">
-        <v>6981285</v>
+        <v>6981391</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7242,7 +7227,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7252,7 +7237,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7284,10 +7269,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128890023</v>
+        <v>128884113</v>
       </c>
       <c r="B66" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7295,37 +7280,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515081</v>
+        <v>515021</v>
       </c>
       <c r="R66" t="n">
-        <v>6981324</v>
+        <v>6981285</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7352,9 +7337,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7369,12 +7369,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8197,48 +8197,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128890101</v>
+        <v>128884094</v>
       </c>
       <c r="B75" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>515108</v>
+        <v>515181</v>
       </c>
       <c r="R75" t="n">
-        <v>6981372</v>
+        <v>6981416</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8265,14 +8265,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>16 plantor på marken i gammal granskog</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8287,60 +8292,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128884094</v>
+        <v>128890101</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515181</v>
+        <v>515108</v>
       </c>
       <c r="R76" t="n">
-        <v>6981416</v>
+        <v>6981372</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8367,19 +8372,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8394,22 +8394,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890085</v>
+        <v>128890037</v>
       </c>
       <c r="B77" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515034</v>
+        <v>515026</v>
       </c>
       <c r="R77" t="n">
-        <v>6981293</v>
+        <v>6981261</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,11 +8479,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8496,19 +8491,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128890037</v>
+        <v>128884102</v>
       </c>
       <c r="B78" t="n">
         <v>80146</v>
@@ -8539,17 +8534,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515026</v>
+        <v>515111</v>
       </c>
       <c r="R78" t="n">
-        <v>6981261</v>
+        <v>6981360</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8576,9 +8571,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8593,22 +8598,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128884102</v>
+        <v>128890085</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>91827</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8616,37 +8621,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515111</v>
+        <v>515034</v>
       </c>
       <c r="R79" t="n">
-        <v>6981360</v>
+        <v>6981293</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8673,19 +8678,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:30</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,12 +8700,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884109</v>
+        <v>128884115</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>80106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515053</v>
+        <v>515019</v>
       </c>
       <c r="R2" t="n">
-        <v>6981306</v>
+        <v>6981238</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128890092</v>
+        <v>128884109</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515067</v>
+        <v>515053</v>
       </c>
       <c r="R3" t="n">
-        <v>6981353</v>
+        <v>6981306</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +850,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -991,48 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128884097</v>
+        <v>128890092</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515184</v>
+        <v>515067</v>
       </c>
       <c r="R5" t="n">
-        <v>6981392</v>
+        <v>6981353</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,19 +1064,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:19</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,44 +1086,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128884115</v>
+        <v>128884097</v>
       </c>
       <c r="B6" t="n">
-        <v>80106</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515019</v>
+        <v>515184</v>
       </c>
       <c r="R6" t="n">
-        <v>6981238</v>
+        <v>6981392</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
         <v>128890079</v>
       </c>
       <c r="B7" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884087</v>
+        <v>128884093</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>105752</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515217</v>
+        <v>515174</v>
       </c>
       <c r="R9" t="n">
-        <v>6981406</v>
+        <v>6981416</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128890036</v>
+        <v>128884087</v>
       </c>
       <c r="B10" t="n">
         <v>80146</v>
@@ -1547,17 +1547,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515018</v>
+        <v>515217</v>
       </c>
       <c r="R10" t="n">
-        <v>6981217</v>
+        <v>6981406</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,9 +1584,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,60 +1611,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128884093</v>
+        <v>128890036</v>
       </c>
       <c r="B11" t="n">
-        <v>105726</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515174</v>
+        <v>515018</v>
       </c>
       <c r="R11" t="n">
-        <v>6981416</v>
+        <v>6981217</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1681,19 +1691,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,12 +1708,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
         <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128890081</v>
+        <v>128890028</v>
       </c>
       <c r="B16" t="n">
         <v>80012</v>
@@ -2154,14 +2154,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515203</v>
+        <v>515039</v>
       </c>
       <c r="R16" t="n">
-        <v>6981449</v>
+        <v>6981285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,36 +2196,32 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890028</v>
+        <v>128890081</v>
       </c>
       <c r="B17" t="n">
         <v>80012</v>
@@ -2256,14 +2252,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515039</v>
+        <v>515203</v>
       </c>
       <c r="R17" t="n">
-        <v>6981285</v>
+        <v>6981449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,25 +2294,29 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128890095</v>
+        <v>128884110</v>
       </c>
       <c r="B20" t="n">
-        <v>92345</v>
+        <v>80012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2548,37 +2548,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515145</v>
+        <v>515038</v>
       </c>
       <c r="R20" t="n">
-        <v>6981384</v>
+        <v>6981305</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2605,14 +2605,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,60 +2632,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128890030</v>
+        <v>128884089</v>
       </c>
       <c r="B21" t="n">
-        <v>80147</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515032</v>
+        <v>515218</v>
       </c>
       <c r="R21" t="n">
-        <v>6981265</v>
+        <v>6981412</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2707,9 +2712,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,12 +2739,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2950,10 +2965,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128890026</v>
+        <v>128890095</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>92359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,34 +2976,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515052</v>
+        <v>515145</v>
       </c>
       <c r="R24" t="n">
-        <v>6981331</v>
+        <v>6981384</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,7 +3040,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3040,22 +3055,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884110</v>
+        <v>128890030</v>
       </c>
       <c r="B25" t="n">
-        <v>80012</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,37 +3078,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>388</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515038</v>
+        <v>515032</v>
       </c>
       <c r="R25" t="n">
-        <v>6981305</v>
+        <v>6981265</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3120,19 +3135,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3147,60 +3152,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128884089</v>
+        <v>128890026</v>
       </c>
       <c r="B26" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515218</v>
+        <v>515052</v>
       </c>
       <c r="R26" t="n">
-        <v>6981412</v>
+        <v>6981331</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3227,19 +3232,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:09</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,12 +3254,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3269,7 +3269,7 @@
         <v>128884108</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,48 +3378,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128884103</v>
+        <v>128890094</v>
       </c>
       <c r="B28" t="n">
-        <v>80175</v>
+        <v>80013</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>385</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515108</v>
+        <v>515188</v>
       </c>
       <c r="R28" t="n">
-        <v>6981358</v>
+        <v>6981440</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3446,19 +3446,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3473,60 +3468,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128890094</v>
+        <v>128884103</v>
       </c>
       <c r="B29" t="n">
-        <v>80013</v>
+        <v>80175</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>385</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515188</v>
+        <v>515108</v>
       </c>
       <c r="R29" t="n">
-        <v>6981440</v>
+        <v>6981358</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3553,14 +3548,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3575,12 +3575,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
         <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>92247</v>
+        <v>92262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128884083</v>
       </c>
       <c r="B36" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4699,32 +4699,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128890045</v>
+        <v>128890022</v>
       </c>
       <c r="B41" t="n">
-        <v>80106</v>
+        <v>96950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515170</v>
+        <v>515029</v>
       </c>
       <c r="R41" t="n">
-        <v>6981451</v>
+        <v>6981199</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4799,7 +4799,7 @@
         <v>128884082</v>
       </c>
       <c r="B42" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,32 +4903,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128890022</v>
+        <v>128890031</v>
       </c>
       <c r="B43" t="n">
-        <v>96924</v>
+        <v>80050</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515029</v>
+        <v>515039</v>
       </c>
       <c r="R43" t="n">
-        <v>6981199</v>
+        <v>6981314</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5000,10 +5000,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128890031</v>
+        <v>128890045</v>
       </c>
       <c r="B44" t="n">
-        <v>80050</v>
+        <v>80106</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515039</v>
+        <v>515170</v>
       </c>
       <c r="R44" t="n">
-        <v>6981314</v>
+        <v>6981451</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
         <v>128890024</v>
       </c>
       <c r="B45" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5510,32 +5510,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890104</v>
+        <v>128890103</v>
       </c>
       <c r="B49" t="n">
-        <v>82990</v>
+        <v>98704</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515070</v>
+        <v>515126</v>
       </c>
       <c r="R49" t="n">
-        <v>6981365</v>
+        <v>6981385</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5612,32 +5612,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890103</v>
+        <v>128890104</v>
       </c>
       <c r="B50" t="n">
-        <v>98678</v>
+        <v>82990</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515126</v>
+        <v>515070</v>
       </c>
       <c r="R50" t="n">
-        <v>6981385</v>
+        <v>6981365</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5714,48 +5714,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128890034</v>
+        <v>128884086</v>
       </c>
       <c r="B51" t="n">
-        <v>91827</v>
+        <v>58097</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515231</v>
+        <v>515225</v>
       </c>
       <c r="R51" t="n">
-        <v>6981432</v>
+        <v>6981406</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5782,9 +5782,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5799,22 +5809,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890041</v>
+        <v>128890034</v>
       </c>
       <c r="B52" t="n">
-        <v>80146</v>
+        <v>91837</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5822,21 +5832,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5846,10 +5856,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515196</v>
+        <v>515231</v>
       </c>
       <c r="R52" t="n">
-        <v>6981428</v>
+        <v>6981432</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5908,10 +5918,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884080</v>
+        <v>128890041</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5919,37 +5929,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515239</v>
+        <v>515196</v>
       </c>
       <c r="R53" t="n">
-        <v>6981443</v>
+        <v>6981428</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5976,19 +5986,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6003,44 +6003,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884086</v>
+        <v>128884080</v>
       </c>
       <c r="B54" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515225</v>
+        <v>515239</v>
       </c>
       <c r="R54" t="n">
-        <v>6981406</v>
+        <v>6981443</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6125,7 +6125,7 @@
         <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>128890025</v>
       </c>
       <c r="B56" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>128890023</v>
       </c>
       <c r="B61" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128884104</v>
+        <v>128890027</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515104</v>
+        <v>515073</v>
       </c>
       <c r="R62" t="n">
-        <v>6981353</v>
+        <v>6981343</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6909,19 +6909,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6936,60 +6931,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128890082</v>
+        <v>128884104</v>
       </c>
       <c r="B63" t="n">
-        <v>79127</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515014</v>
+        <v>515104</v>
       </c>
       <c r="R63" t="n">
-        <v>6981245</v>
+        <v>6981353</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7016,14 +7011,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7038,60 +7038,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884099</v>
+        <v>128890082</v>
       </c>
       <c r="B64" t="n">
-        <v>80146</v>
+        <v>79127</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515158</v>
+        <v>515014</v>
       </c>
       <c r="R64" t="n">
-        <v>6981406</v>
+        <v>6981245</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7118,19 +7118,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7145,22 +7140,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884095</v>
+        <v>128884099</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7168,21 +7163,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7192,10 +7187,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515183</v>
+        <v>515158</v>
       </c>
       <c r="R65" t="n">
-        <v>6981391</v>
+        <v>6981406</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7227,7 +7222,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7237,12 +7232,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7269,7 +7259,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884113</v>
+        <v>128884095</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7304,10 +7294,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515021</v>
+        <v>515183</v>
       </c>
       <c r="R66" t="n">
-        <v>6981285</v>
+        <v>6981391</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7339,7 +7329,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7349,7 +7339,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7381,10 +7371,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128890027</v>
+        <v>128884113</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7392,37 +7382,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515073</v>
+        <v>515021</v>
       </c>
       <c r="R67" t="n">
-        <v>6981343</v>
+        <v>6981285</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7449,14 +7439,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7471,57 +7471,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890080</v>
+        <v>128890032</v>
       </c>
       <c r="B68" t="n">
-        <v>80012</v>
+        <v>91992</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515188</v>
+        <v>515210</v>
       </c>
       <c r="R68" t="n">
-        <v>6981440</v>
+        <v>6981426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,11 +7556,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7573,57 +7568,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890032</v>
+        <v>128890075</v>
       </c>
       <c r="B69" t="n">
-        <v>91997</v>
+        <v>105752</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>221725</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515210</v>
+        <v>515124</v>
       </c>
       <c r="R69" t="n">
-        <v>6981426</v>
+        <v>6981387</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7658,6 +7653,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På marken i gammal gransumpskog</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7670,44 +7670,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890077</v>
+        <v>128890097</v>
       </c>
       <c r="B70" t="n">
-        <v>83007</v>
+        <v>98704</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515057</v>
+        <v>515060</v>
       </c>
       <c r="R70" t="n">
-        <v>6981333</v>
+        <v>6981339</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7784,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890075</v>
+        <v>128890080</v>
       </c>
       <c r="B71" t="n">
-        <v>105726</v>
+        <v>80012</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221725</v>
+        <v>388</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515124</v>
+        <v>515188</v>
       </c>
       <c r="R71" t="n">
-        <v>6981387</v>
+        <v>6981440</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På marken i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890097</v>
+        <v>128890077</v>
       </c>
       <c r="B72" t="n">
-        <v>98678</v>
+        <v>83007</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515060</v>
+        <v>515057</v>
       </c>
       <c r="R72" t="n">
-        <v>6981339</v>
+        <v>6981333</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,10 +7988,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128890084</v>
+        <v>128884111</v>
       </c>
       <c r="B73" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7999,37 +7999,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>515029</v>
+        <v>515033</v>
       </c>
       <c r="R73" t="n">
-        <v>6981276</v>
+        <v>6981298</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8056,14 +8056,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8078,19 +8083,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128884111</v>
+        <v>128884094</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -8125,10 +8130,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>515033</v>
+        <v>515181</v>
       </c>
       <c r="R74" t="n">
-        <v>6981298</v>
+        <v>6981416</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -8160,7 +8165,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8170,7 +8175,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8197,48 +8202,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128884094</v>
+        <v>128890101</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>515181</v>
+        <v>515108</v>
       </c>
       <c r="R75" t="n">
-        <v>6981416</v>
+        <v>6981372</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8265,19 +8270,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:16</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>16 plantor på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8292,44 +8292,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128890101</v>
+        <v>128890084</v>
       </c>
       <c r="B76" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>515108</v>
+        <v>515029</v>
       </c>
       <c r="R76" t="n">
-        <v>6981372</v>
+        <v>6981276</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>16 plantor på marken i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8406,10 +8406,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128890037</v>
+        <v>128890085</v>
       </c>
       <c r="B77" t="n">
-        <v>80146</v>
+        <v>91837</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8417,34 +8417,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>515026</v>
+        <v>515034</v>
       </c>
       <c r="R77" t="n">
-        <v>6981261</v>
+        <v>6981293</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8479,6 +8479,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8491,19 +8496,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128884102</v>
+        <v>128890037</v>
       </c>
       <c r="B78" t="n">
         <v>80146</v>
@@ -8534,17 +8539,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>515111</v>
+        <v>515026</v>
       </c>
       <c r="R78" t="n">
-        <v>6981360</v>
+        <v>6981261</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8571,19 +8576,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8598,22 +8593,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128890085</v>
+        <v>128884102</v>
       </c>
       <c r="B79" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8621,37 +8616,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>515034</v>
+        <v>515111</v>
       </c>
       <c r="R79" t="n">
-        <v>6981293</v>
+        <v>6981360</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8678,14 +8673,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8700,60 +8700,60 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128890096</v>
+        <v>128884081</v>
       </c>
       <c r="B80" t="n">
-        <v>80106</v>
+        <v>91540</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>515014</v>
+        <v>515230</v>
       </c>
       <c r="R80" t="n">
-        <v>6981245</v>
+        <v>6981431</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8780,14 +8780,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8802,22 +8807,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128890099</v>
+        <v>128890093</v>
       </c>
       <c r="B81" t="n">
-        <v>98678</v>
+        <v>80013</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8825,21 +8830,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>385</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8849,10 +8854,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>515054</v>
+        <v>515053</v>
       </c>
       <c r="R81" t="n">
-        <v>6981308</v>
+        <v>6981314</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8889,7 +8894,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8916,32 +8921,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128890093</v>
+        <v>128890096</v>
       </c>
       <c r="B82" t="n">
-        <v>80013</v>
+        <v>80106</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>385</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8951,10 +8956,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>515053</v>
+        <v>515014</v>
       </c>
       <c r="R82" t="n">
-        <v>6981314</v>
+        <v>6981245</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8991,7 +8996,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp i gammal lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9120,10 +9125,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884081</v>
+        <v>128884091</v>
       </c>
       <c r="B84" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9131,21 +9136,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9155,10 +9160,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515230</v>
+        <v>515199</v>
       </c>
       <c r="R84" t="n">
-        <v>6981431</v>
+        <v>6981419</v>
       </c>
       <c r="S84" t="n">
         <v>4</v>
@@ -9190,7 +9195,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9200,7 +9205,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9227,7 +9232,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128884091</v>
+        <v>128890091</v>
       </c>
       <c r="B85" t="n">
         <v>80146</v>
@@ -9258,17 +9263,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515199</v>
+        <v>515069</v>
       </c>
       <c r="R85" t="n">
-        <v>6981419</v>
+        <v>6981349</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9295,19 +9300,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9322,19 +9322,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890091</v>
+        <v>128890038</v>
       </c>
       <c r="B86" t="n">
         <v>80146</v>
@@ -9365,14 +9365,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515069</v>
+        <v>515041</v>
       </c>
       <c r="R86" t="n">
-        <v>6981349</v>
+        <v>6981296</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9407,11 +9407,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9424,57 +9419,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890038</v>
+        <v>128890099</v>
       </c>
       <c r="B87" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515041</v>
+        <v>515054</v>
       </c>
       <c r="R87" t="n">
-        <v>6981296</v>
+        <v>6981308</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9509,6 +9504,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På marken 13 plantor i lövrik granskog</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -9521,12 +9521,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128884115</v>
+        <v>128884109</v>
       </c>
       <c r="B2" t="n">
-        <v>80106</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515019</v>
+        <v>515053</v>
       </c>
       <c r="R2" t="n">
-        <v>6981238</v>
+        <v>6981306</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128884109</v>
+        <v>128884101</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515053</v>
+        <v>515135</v>
       </c>
       <c r="R3" t="n">
-        <v>6981306</v>
+        <v>6981381</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884101</v>
+        <v>128884097</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515135</v>
+        <v>515184</v>
       </c>
       <c r="R4" t="n">
-        <v>6981381</v>
+        <v>6981392</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128884097</v>
+        <v>128884115</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515184</v>
+        <v>515019</v>
       </c>
       <c r="R6" t="n">
-        <v>6981392</v>
+        <v>6981238</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,7 +1310,7 @@
         <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>128884093</v>
       </c>
       <c r="B9" t="n">
-        <v>105752</v>
+        <v>105754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128890028</v>
+        <v>128884105</v>
       </c>
       <c r="B16" t="n">
-        <v>80012</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515039</v>
+        <v>515069</v>
       </c>
       <c r="R16" t="n">
-        <v>6981285</v>
+        <v>6981348</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,37 +2191,46 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890081</v>
+        <v>128890028</v>
       </c>
       <c r="B17" t="n">
         <v>80012</v>
@@ -2252,14 +2261,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515203</v>
+        <v>515039</v>
       </c>
       <c r="R17" t="n">
-        <v>6981449</v>
+        <v>6981285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,39 +2303,35 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128884105</v>
+        <v>128890081</v>
       </c>
       <c r="B18" t="n">
-        <v>80146</v>
+        <v>80012</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2334,37 +2339,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515069</v>
+        <v>515203</v>
       </c>
       <c r="R18" t="n">
-        <v>6981348</v>
+        <v>6981449</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2391,19 +2396,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,12 +2418,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2644,48 +2644,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128884089</v>
+        <v>128890095</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>92360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>2014</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515218</v>
+        <v>515145</v>
       </c>
       <c r="R21" t="n">
-        <v>6981412</v>
+        <v>6981384</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,19 +2712,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:09</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2739,22 +2734,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128884107</v>
+        <v>128890030</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,37 +2757,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515060</v>
+        <v>515032</v>
       </c>
       <c r="R22" t="n">
-        <v>6981336</v>
+        <v>6981265</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2819,19 +2814,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2846,44 +2831,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128884084</v>
+        <v>128884089</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2893,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515227</v>
+        <v>515218</v>
       </c>
       <c r="R23" t="n">
-        <v>6981418</v>
+        <v>6981412</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -2928,7 +2913,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2938,7 +2923,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2965,10 +2950,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128890095</v>
+        <v>128884107</v>
       </c>
       <c r="B24" t="n">
-        <v>92359</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2976,37 +2961,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515145</v>
+        <v>515060</v>
       </c>
       <c r="R24" t="n">
-        <v>6981384</v>
+        <v>6981336</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3033,14 +3018,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3055,22 +3045,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128890030</v>
+        <v>128884084</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,37 +3068,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515032</v>
+        <v>515227</v>
       </c>
       <c r="R25" t="n">
-        <v>6981265</v>
+        <v>6981418</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3135,9 +3125,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,12 +3152,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3269,7 +3269,7 @@
         <v>128884108</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,48 +3480,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128884103</v>
+        <v>128890088</v>
       </c>
       <c r="B29" t="n">
-        <v>80175</v>
+        <v>79512</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1797</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515108</v>
+        <v>515103</v>
       </c>
       <c r="R29" t="n">
-        <v>6981358</v>
+        <v>6981364</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3548,19 +3548,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3575,60 +3570,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128890088</v>
+        <v>128884103</v>
       </c>
       <c r="B30" t="n">
-        <v>79512</v>
+        <v>80175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1797</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515103</v>
+        <v>515108</v>
       </c>
       <c r="R30" t="n">
-        <v>6981364</v>
+        <v>6981358</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3655,14 +3650,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,12 +3677,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3692,7 +3692,7 @@
         <v>128890029</v>
       </c>
       <c r="B31" t="n">
-        <v>92262</v>
+        <v>92263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128890022</v>
+        <v>128884082</v>
       </c>
       <c r="B41" t="n">
-        <v>96950</v>
+        <v>91838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515029</v>
+        <v>515231</v>
       </c>
       <c r="R41" t="n">
-        <v>6981199</v>
+        <v>6981417</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4767,9 +4767,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4784,22 +4794,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128884082</v>
+        <v>128890022</v>
       </c>
       <c r="B42" t="n">
-        <v>91837</v>
+        <v>96951</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4807,37 +4817,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515231</v>
+        <v>515029</v>
       </c>
       <c r="R42" t="n">
-        <v>6981417</v>
+        <v>6981199</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4864,19 +4874,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,12 +4891,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5097,45 +5097,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890024</v>
+        <v>128890104</v>
       </c>
       <c r="B45" t="n">
-        <v>91540</v>
+        <v>82990</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515219</v>
+        <v>515070</v>
       </c>
       <c r="R45" t="n">
-        <v>6981419</v>
+        <v>6981365</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,6 +5170,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5182,12 +5187,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5510,45 +5515,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890103</v>
+        <v>128890024</v>
       </c>
       <c r="B49" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515126</v>
+        <v>515219</v>
       </c>
       <c r="R49" t="n">
-        <v>6981385</v>
+        <v>6981419</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5583,11 +5588,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>6 plantor på marken i gammal sumpgranskog</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5600,44 +5600,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128890104</v>
+        <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>82990</v>
+        <v>98705</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515070</v>
+        <v>515126</v>
       </c>
       <c r="R50" t="n">
-        <v>6981365</v>
+        <v>6981385</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>6 plantor på marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5714,48 +5714,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128884086</v>
+        <v>128890034</v>
       </c>
       <c r="B51" t="n">
-        <v>58097</v>
+        <v>91838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515225</v>
+        <v>515231</v>
       </c>
       <c r="R51" t="n">
-        <v>6981406</v>
+        <v>6981432</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5782,19 +5782,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5809,22 +5799,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890034</v>
+        <v>128890041</v>
       </c>
       <c r="B52" t="n">
-        <v>91837</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5832,21 +5822,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,10 +5846,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515231</v>
+        <v>515196</v>
       </c>
       <c r="R52" t="n">
-        <v>6981432</v>
+        <v>6981428</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5918,10 +5908,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128890041</v>
+        <v>128884080</v>
       </c>
       <c r="B53" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5929,37 +5919,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515196</v>
+        <v>515239</v>
       </c>
       <c r="R53" t="n">
-        <v>6981428</v>
+        <v>6981443</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5986,9 +5976,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6003,44 +6003,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884080</v>
+        <v>128884086</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515239</v>
+        <v>515225</v>
       </c>
       <c r="R54" t="n">
-        <v>6981443</v>
+        <v>6981406</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6125,7 +6125,7 @@
         <v>128890098</v>
       </c>
       <c r="B55" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128890023</v>
+        <v>128884104</v>
       </c>
       <c r="B61" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6755,37 +6755,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515081</v>
+        <v>515104</v>
       </c>
       <c r="R61" t="n">
-        <v>6981324</v>
+        <v>6981353</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,9 +6812,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6829,57 +6839,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128890027</v>
+        <v>128890082</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>79127</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515073</v>
+        <v>515014</v>
       </c>
       <c r="R62" t="n">
-        <v>6981343</v>
+        <v>6981245</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6916,7 +6926,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6931,22 +6941,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884104</v>
+        <v>128884099</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6954,21 +6964,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6978,10 +6988,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515104</v>
+        <v>515158</v>
       </c>
       <c r="R63" t="n">
-        <v>6981353</v>
+        <v>6981406</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7013,7 +7023,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7023,7 +7033,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7050,48 +7060,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128890082</v>
+        <v>128884095</v>
       </c>
       <c r="B64" t="n">
-        <v>79127</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515014</v>
+        <v>515183</v>
       </c>
       <c r="R64" t="n">
-        <v>6981245</v>
+        <v>6981391</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7118,14 +7128,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rikligt på lodyta</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7140,22 +7160,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884099</v>
+        <v>128884113</v>
       </c>
       <c r="B65" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7163,21 +7183,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7187,10 +7207,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515158</v>
+        <v>515021</v>
       </c>
       <c r="R65" t="n">
-        <v>6981406</v>
+        <v>6981285</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7222,7 +7242,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7232,7 +7252,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7259,10 +7284,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128884095</v>
+        <v>128890027</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7270,37 +7295,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515183</v>
+        <v>515073</v>
       </c>
       <c r="R66" t="n">
-        <v>6981391</v>
+        <v>6981343</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7327,24 +7352,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7359,22 +7374,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128884113</v>
+        <v>128890023</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7382,37 +7397,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515021</v>
+        <v>515081</v>
       </c>
       <c r="R67" t="n">
-        <v>6981285</v>
+        <v>6981324</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7439,24 +7454,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>nr 500</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7471,57 +7471,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890032</v>
+        <v>128890080</v>
       </c>
       <c r="B68" t="n">
-        <v>91992</v>
+        <v>80012</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515210</v>
+        <v>515188</v>
       </c>
       <c r="R68" t="n">
-        <v>6981426</v>
+        <v>6981440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,6 +7556,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7568,57 +7573,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890075</v>
+        <v>128890032</v>
       </c>
       <c r="B69" t="n">
-        <v>105752</v>
+        <v>91993</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221725</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515124</v>
+        <v>515210</v>
       </c>
       <c r="R69" t="n">
-        <v>6981387</v>
+        <v>6981426</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7653,11 +7658,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På marken i gammal gransumpskog</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7670,44 +7670,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128890097</v>
+        <v>128890077</v>
       </c>
       <c r="B70" t="n">
-        <v>98704</v>
+        <v>83007</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>515060</v>
+        <v>515057</v>
       </c>
       <c r="R70" t="n">
-        <v>6981339</v>
+        <v>6981333</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>91 plantor på marken i gammal lövrik granskog</t>
+          <t>På gammal gran i lövrik granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7784,32 +7784,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128890080</v>
+        <v>128890097</v>
       </c>
       <c r="B71" t="n">
-        <v>80012</v>
+        <v>98705</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>515188</v>
+        <v>515060</v>
       </c>
       <c r="R71" t="n">
-        <v>6981440</v>
+        <v>6981339</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>91 plantor på marken i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128890077</v>
+        <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>83007</v>
+        <v>105754</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>515057</v>
+        <v>515124</v>
       </c>
       <c r="R72" t="n">
-        <v>6981333</v>
+        <v>6981387</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gammal gran i lövrik granskog</t>
+          <t>På marken i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8205,7 +8205,7 @@
         <v>128890101</v>
       </c>
       <c r="B75" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>128890084</v>
       </c>
       <c r="B76" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>128890085</v>
       </c>
       <c r="B77" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8921,10 +8921,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128890096</v>
+        <v>128890087</v>
       </c>
       <c r="B82" t="n">
-        <v>80106</v>
+        <v>80174</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8932,21 +8932,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9023,48 +9023,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128890087</v>
+        <v>128884091</v>
       </c>
       <c r="B83" t="n">
-        <v>80174</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>515014</v>
+        <v>515199</v>
       </c>
       <c r="R83" t="n">
-        <v>6981245</v>
+        <v>6981419</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9091,14 +9091,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På lodyta</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9113,19 +9118,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128884091</v>
+        <v>128890091</v>
       </c>
       <c r="B84" t="n">
         <v>80146</v>
@@ -9156,17 +9161,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>515199</v>
+        <v>515069</v>
       </c>
       <c r="R84" t="n">
-        <v>6981419</v>
+        <v>6981349</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9193,19 +9198,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9220,19 +9220,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128890091</v>
+        <v>128890038</v>
       </c>
       <c r="B85" t="n">
         <v>80146</v>
@@ -9263,14 +9263,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>515069</v>
+        <v>515041</v>
       </c>
       <c r="R85" t="n">
-        <v>6981349</v>
+        <v>6981296</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9305,11 +9305,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9322,57 +9317,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890038</v>
+        <v>128890096</v>
       </c>
       <c r="B86" t="n">
-        <v>80146</v>
+        <v>80106</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515041</v>
+        <v>515014</v>
       </c>
       <c r="R86" t="n">
-        <v>6981296</v>
+        <v>6981245</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9407,6 +9402,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9419,12 +9419,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9434,7 +9434,7 @@
         <v>128890099</v>
       </c>
       <c r="B87" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>128890102</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884093</v>
+        <v>128884087</v>
       </c>
       <c r="B9" t="n">
-        <v>105754</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515174</v>
+        <v>515217</v>
       </c>
       <c r="R9" t="n">
-        <v>6981416</v>
+        <v>6981406</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128884087</v>
+        <v>128890036</v>
       </c>
       <c r="B10" t="n">
         <v>80146</v>
@@ -1547,17 +1547,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515217</v>
+        <v>515018</v>
       </c>
       <c r="R10" t="n">
-        <v>6981406</v>
+        <v>6981217</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,19 +1584,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,60 +1601,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128890036</v>
+        <v>128884093</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>105755</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515018</v>
+        <v>515174</v>
       </c>
       <c r="R11" t="n">
-        <v>6981217</v>
+        <v>6981416</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,9 +1681,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,12 +1708,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1805,12 +1805,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2009,12 +2009,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
         <v>128890100</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128884105</v>
+        <v>128890028</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>80012</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515069</v>
+        <v>515039</v>
       </c>
       <c r="R16" t="n">
-        <v>6981348</v>
+        <v>6981285</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,46 +2191,37 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128890028</v>
+        <v>128890081</v>
       </c>
       <c r="B17" t="n">
         <v>80012</v>
@@ -2261,14 +2252,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515039</v>
+        <v>515203</v>
       </c>
       <c r="R17" t="n">
-        <v>6981285</v>
+        <v>6981449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2303,35 +2294,39 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128890081</v>
+        <v>128884105</v>
       </c>
       <c r="B18" t="n">
-        <v>80012</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,37 +2334,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515203</v>
+        <v>515069</v>
       </c>
       <c r="R18" t="n">
-        <v>6981449</v>
+        <v>6981348</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2396,14 +2391,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,12 +2418,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2644,48 +2644,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128890095</v>
+        <v>128884089</v>
       </c>
       <c r="B21" t="n">
-        <v>92360</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2014</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515145</v>
+        <v>515218</v>
       </c>
       <c r="R21" t="n">
-        <v>6981384</v>
+        <v>6981412</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2712,14 +2712,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gråalslåga i gransumpskog</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2734,22 +2739,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128890030</v>
+        <v>128884107</v>
       </c>
       <c r="B22" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2757,37 +2762,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515032</v>
+        <v>515060</v>
       </c>
       <c r="R22" t="n">
-        <v>6981265</v>
+        <v>6981336</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2814,9 +2819,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2831,44 +2846,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128884089</v>
+        <v>128884084</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2878,10 +2893,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515218</v>
+        <v>515227</v>
       </c>
       <c r="R23" t="n">
-        <v>6981412</v>
+        <v>6981418</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -2913,7 +2928,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2923,7 +2938,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2950,10 +2965,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128884107</v>
+        <v>128890095</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>92360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,37 +2976,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515060</v>
+        <v>515145</v>
       </c>
       <c r="R24" t="n">
-        <v>6981336</v>
+        <v>6981384</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3018,19 +3033,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:40</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gråalslåga i gransumpskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3045,22 +3055,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128884084</v>
+        <v>128890030</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3068,37 +3078,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515227</v>
+        <v>515032</v>
       </c>
       <c r="R25" t="n">
-        <v>6981418</v>
+        <v>6981265</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3125,19 +3135,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,12 +3152,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3254,60 +3254,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128884108</v>
+        <v>128890088</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>79512</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1797</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515059</v>
+        <v>515103</v>
       </c>
       <c r="R27" t="n">
-        <v>6981319</v>
+        <v>6981364</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3334,24 +3334,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>nr 10</t>
+          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3366,60 +3356,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128890094</v>
+        <v>128884103</v>
       </c>
       <c r="B28" t="n">
-        <v>80013</v>
+        <v>80175</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>385</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515188</v>
+        <v>515108</v>
       </c>
       <c r="R28" t="n">
-        <v>6981440</v>
+        <v>6981358</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3446,14 +3436,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3468,60 +3463,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128890088</v>
+        <v>128884108</v>
       </c>
       <c r="B29" t="n">
-        <v>79512</v>
+        <v>98706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1797</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515103</v>
+        <v>515059</v>
       </c>
       <c r="R29" t="n">
-        <v>6981364</v>
+        <v>6981319</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3548,14 +3543,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark vid basen av grov gammal levande gran i gammal granskog</t>
+          <t>nr 10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3570,60 +3575,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128884103</v>
+        <v>128890094</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>80013</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>385</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515108</v>
+        <v>515188</v>
       </c>
       <c r="R30" t="n">
-        <v>6981358</v>
+        <v>6981440</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3650,19 +3655,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:31</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,12 +3677,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3774,12 +3774,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3871,12 +3871,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3968,12 +3968,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4167,12 +4167,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4687,12 +4687,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4809,7 +4809,7 @@
         <v>128890022</v>
       </c>
       <c r="B42" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4891,12 +4891,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4988,12 +4988,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5085,57 +5085,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128890104</v>
+        <v>128890024</v>
       </c>
       <c r="B45" t="n">
-        <v>82990</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515070</v>
+        <v>515219</v>
       </c>
       <c r="R45" t="n">
-        <v>6981365</v>
+        <v>6981419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,11 +5170,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5187,60 +5182,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128884117</v>
+        <v>128890104</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>82990</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515013</v>
+        <v>515070</v>
       </c>
       <c r="R46" t="n">
-        <v>6981204</v>
+        <v>6981365</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5267,19 +5262,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:12</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5294,22 +5284,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128890090</v>
+        <v>128884117</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5317,37 +5307,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
         <v>515013</v>
       </c>
       <c r="R47" t="n">
-        <v>6981245</v>
+        <v>6981204</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5374,14 +5364,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5396,19 +5391,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128884114</v>
+        <v>128890090</v>
       </c>
       <c r="B48" t="n">
         <v>80146</v>
@@ -5439,17 +5434,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515018</v>
+        <v>515013</v>
       </c>
       <c r="R48" t="n">
-        <v>6981240</v>
+        <v>6981245</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5476,19 +5471,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:55</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5503,22 +5493,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128890024</v>
+        <v>128884114</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5526,37 +5516,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515219</v>
+        <v>515018</v>
       </c>
       <c r="R49" t="n">
-        <v>6981419</v>
+        <v>6981240</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5583,9 +5573,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5600,12 +5600,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5615,7 +5615,7 @@
         <v>128890103</v>
       </c>
       <c r="B50" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5799,57 +5799,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128890041</v>
+        <v>128890098</v>
       </c>
       <c r="B52" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515196</v>
+        <v>515031</v>
       </c>
       <c r="R52" t="n">
-        <v>6981428</v>
+        <v>6981292</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5884,6 +5884,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>37 plantor på marken i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5896,22 +5901,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884080</v>
+        <v>128890041</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5919,37 +5924,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515239</v>
+        <v>515196</v>
       </c>
       <c r="R53" t="n">
-        <v>6981443</v>
+        <v>6981428</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5976,19 +5981,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6003,44 +5998,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884086</v>
+        <v>128884080</v>
       </c>
       <c r="B54" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6050,10 +6045,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515225</v>
+        <v>515239</v>
       </c>
       <c r="R54" t="n">
-        <v>6981406</v>
+        <v>6981443</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6085,7 +6080,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6095,7 +6090,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6122,48 +6117,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128890098</v>
+        <v>128884086</v>
       </c>
       <c r="B55" t="n">
-        <v>98705</v>
+        <v>58097</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515031</v>
+        <v>515225</v>
       </c>
       <c r="R55" t="n">
-        <v>6981292</v>
+        <v>6981406</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6190,14 +6185,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>37 plantor på marken i gammal granskog</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6212,12 +6212,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6309,12 +6309,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128884104</v>
+        <v>128890027</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6755,37 +6755,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515104</v>
+        <v>515073</v>
       </c>
       <c r="R61" t="n">
-        <v>6981353</v>
+        <v>6981343</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6812,19 +6812,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6839,57 +6834,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128890082</v>
+        <v>128890023</v>
       </c>
       <c r="B62" t="n">
-        <v>79127</v>
+        <v>91540</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6450</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515014</v>
+        <v>515081</v>
       </c>
       <c r="R62" t="n">
-        <v>6981245</v>
+        <v>6981324</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6924,11 +6919,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt på lodyta</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6941,22 +6931,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128884099</v>
+        <v>128884104</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6964,21 +6954,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6988,10 +6978,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515158</v>
+        <v>515104</v>
       </c>
       <c r="R63" t="n">
-        <v>6981406</v>
+        <v>6981353</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7023,7 +7013,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7033,7 +7023,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7060,48 +7050,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128884095</v>
+        <v>128890082</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>79127</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515183</v>
+        <v>515014</v>
       </c>
       <c r="R64" t="n">
-        <v>6981391</v>
+        <v>6981245</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7128,24 +7118,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>nr 500</t>
+          <t>Rikligt på lodyta</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7160,22 +7140,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884113</v>
+        <v>128884099</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7183,21 +7163,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7207,10 +7187,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515021</v>
+        <v>515158</v>
       </c>
       <c r="R65" t="n">
-        <v>6981285</v>
+        <v>6981406</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7242,7 +7222,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7252,12 +7232,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>nr 500</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7284,10 +7259,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128890027</v>
+        <v>128884095</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7295,37 +7270,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>515073</v>
+        <v>515183</v>
       </c>
       <c r="R66" t="n">
-        <v>6981343</v>
+        <v>6981391</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7352,14 +7327,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7374,22 +7359,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128890023</v>
+        <v>128884113</v>
       </c>
       <c r="B67" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7397,37 +7382,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>515081</v>
+        <v>515021</v>
       </c>
       <c r="R67" t="n">
-        <v>6981324</v>
+        <v>6981285</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7454,9 +7439,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7471,57 +7471,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128890080</v>
+        <v>128890032</v>
       </c>
       <c r="B68" t="n">
-        <v>80012</v>
+        <v>91993</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>Lager 16, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>515188</v>
+        <v>515210</v>
       </c>
       <c r="R68" t="n">
-        <v>6981440</v>
+        <v>6981426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7556,11 +7556,6 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7573,57 +7568,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128890032</v>
+        <v>128890080</v>
       </c>
       <c r="B69" t="n">
-        <v>91993</v>
+        <v>80012</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>515210</v>
+        <v>515188</v>
       </c>
       <c r="R69" t="n">
-        <v>6981426</v>
+        <v>6981440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7658,6 +7653,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7670,12 +7670,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7787,7 +7787,7 @@
         <v>128890097</v>
       </c>
       <c r="B71" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>128890075</v>
       </c>
       <c r="B72" t="n">
-        <v>105754</v>
+        <v>105755</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>128890101</v>
       </c>
       <c r="B75" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8593,12 +8593,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9317,44 +9317,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128890096</v>
+        <v>128890099</v>
       </c>
       <c r="B86" t="n">
-        <v>80106</v>
+        <v>98706</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>515014</v>
+        <v>515054</v>
       </c>
       <c r="R86" t="n">
-        <v>6981245</v>
+        <v>6981308</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På marken 13 plantor i lövrik granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9431,32 +9431,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128890099</v>
+        <v>128890096</v>
       </c>
       <c r="B87" t="n">
-        <v>98705</v>
+        <v>80106</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>515054</v>
+        <v>515014</v>
       </c>
       <c r="R87" t="n">
-        <v>6981308</v>
+        <v>6981245</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På marken 13 plantor i lövrik granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 41207-2025 artfynd.xlsx
+++ b/artfynd/A 41207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128884109</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128884101</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,48 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128884097</v>
+        <v>128890092</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515184</v>
+        <v>515067</v>
       </c>
       <c r="R4" t="n">
-        <v>6981392</v>
+        <v>6981353</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +957,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:19</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bark på sälglåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,60 +979,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128890092</v>
+        <v>128884097</v>
       </c>
       <c r="B5" t="n">
-        <v>80182</v>
+        <v>80148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster om Västra Värsjön, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515067</v>
+        <v>515184</v>
       </c>
       <c r="R5" t="n">
-        <v>6981353</v>
+        <v>6981392</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,14 +1059,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på sälglåga</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,12 +1086,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
         <v>128884115</v>
       </c>
       <c r="B6" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128890079</v>
+        <v>128890102</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515071</v>
+        <v>515229</v>
       </c>
       <c r="R7" t="n">
-        <v>6981351</v>
+        <v>6981403</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>50 plantor i i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128890102</v>
+        <v>128890079</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>91507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515229</v>
+        <v>515071</v>
       </c>
       <c r="R8" t="n">
-        <v>6981403</v>
+        <v>6981351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>50 plantor i i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,7 +1412,7 @@
         <v>128884087</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>128890036</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>128884093</v>
       </c>
       <c r="B11" t="n">
-        <v>105755</v>
+        <v>105759</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,45 +1720,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128890033</v>
+        <v>128890100</v>
       </c>
       <c r="B12" t="n">
-        <v>75031</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lager 16, Jmt</t>
+          <t>Öster om Västra Värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515018</v>
+        <v>515060</v>
       </c>
       <c r="R12" t="n">
-        <v>6981215</v>
+        <v>6981326</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1793,11 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>11 plantor i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1805,60 +1810,60 @@
       <c r="AT12"